--- a/CSV/Timelines.xlsx
+++ b/CSV/Timelines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1Data\1study\WebLearn\Timeline\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B284A5-2369-4ABE-A001-4B0A49D73476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910C55B6-5379-4BFB-9843-93336A176F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9750" yWindow="495" windowWidth="28800" windowHeight="15885" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21705" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
   </bookViews>
   <sheets>
     <sheet name="ThreeBody" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
   <si>
     <t>Year</t>
   </si>
@@ -230,6 +230,14 @@
   </si>
   <si>
     <t>掩体纪元</t>
+  </si>
+  <si>
+    <t>Month</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Day</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1184,397 +1192,428 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7075CE0F-CB4C-44E0-830B-E1E248B01C04}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.625" customWidth="1"/>
-    <col min="5" max="5" width="41.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="62.25" style="1" customWidth="1"/>
+    <col min="1" max="3" width="5.25" customWidth="1"/>
+    <col min="4" max="4" width="15.75" customWidth="1"/>
+    <col min="6" max="6" width="3.625" customWidth="1"/>
+    <col min="7" max="7" width="33.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="62.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1453</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1947</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1967</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1968</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>17</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1969</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1971</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>23</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1975</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1979</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>2</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G9" t="s">
+      <c r="I9" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1980</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>0</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1982</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>1</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1984</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
         <v>39</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2007</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
         <v>42</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>0</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G13" t="s">
+      <c r="I13" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2010</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>46</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <v>1</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G14" t="s">
+      <c r="I14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2015</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G15" t="s">
+      <c r="I15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>2205</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>52</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>0</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2208</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>55</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>0</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2270</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18">
+        <v>11</v>
+      </c>
+      <c r="C18">
+        <v>28</v>
+      </c>
+      <c r="D18" t="s">
         <v>58</v>
       </c>
-      <c r="D18">
+      <c r="F18">
         <v>0</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2274</v>
       </c>
-      <c r="B19" t="s">
+      <c r="D19" t="s">
         <v>62</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>0</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2400</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>66</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <v>1</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G20" t="s">
+      <c r="I20" t="s">
         <v>69</v>
       </c>
     </row>

--- a/CSV/Timelines.xlsx
+++ b/CSV/Timelines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1Data\1study\WebLearn\Timeline\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{910C55B6-5379-4BFB-9843-93336A176F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86713ECD-F007-4A49-BCE9-9B1FBB1C784B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21705" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
   </bookViews>
   <sheets>
     <sheet name="ThreeBody" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="146">
   <si>
     <t>Year</t>
   </si>
@@ -46,197 +46,566 @@
     <t>四维空间接触地球</t>
   </si>
   <si>
+    <t>中世纪</t>
+  </si>
+  <si>
+    <t>叶文洁出生</t>
+  </si>
+  <si>
+    <t>叶泰哲在批斗会上被打死</t>
+  </si>
+  <si>
+    <t>文革时代</t>
+  </si>
+  <si>
+    <t>红岸基地建成</t>
+  </si>
+  <si>
+    <t>红岸基地（雷达峰）建成</t>
+  </si>
+  <si>
+    <t>用于搜索地外文明的绝密国防工程。</t>
+  </si>
+  <si>
+    <t>叶文洁进入红岸</t>
+  </si>
+  <si>
+    <t>叶文洁被红岸基地吸收</t>
+  </si>
+  <si>
+    <t>三体世界收到信号</t>
+  </si>
+  <si>
+    <t>三体文明1379号监听站收到地球的消息，监听员发回了警告信息。</t>
+  </si>
+  <si>
+    <t>黄金时代</t>
+  </si>
+  <si>
+    <t>杨冬出生</t>
+  </si>
+  <si>
+    <t>叶文洁女儿杨冬出生</t>
+  </si>
+  <si>
+    <t>三体舰队启航</t>
+  </si>
+  <si>
+    <t>三体第一舰队向着地球的大致方向启航。</t>
+  </si>
+  <si>
+    <t>智子工程启动</t>
+  </si>
+  <si>
+    <t>三体制定杀死地球科学的计划</t>
+  </si>
+  <si>
+    <t>危机纪元</t>
+  </si>
+  <si>
+    <t>水滴攻击</t>
+  </si>
+  <si>
+    <t>三体水滴摧毁人类舰队</t>
+  </si>
+  <si>
+    <t>三体水滴到达太阳系，封死太阳。丁仪考察水滴，水滴启动，几乎全歼人类舰队。只有量子号和青铜时代号逃脱。</t>
+  </si>
+  <si>
+    <t>建立威慑</t>
+  </si>
+  <si>
+    <t>罗辑建立黑暗森林威慑</t>
+  </si>
+  <si>
+    <t>罗辑与三体对决，以雪地工程布置的核弹建立威慑。三体接受谈判，解除太阳封锁。罗辑成为执剑人。</t>
+  </si>
+  <si>
+    <t>威慑终结</t>
+  </si>
+  <si>
+    <t>程心接任执剑人</t>
+  </si>
+  <si>
+    <t>程心当选执剑人，16分钟后水滴摧毁引力波发射器，威慑终止。万有引力号和蓝色空间号启动引力波广播。</t>
+  </si>
+  <si>
+    <t>威慑纪元</t>
+  </si>
+  <si>
+    <t>三体世界毁灭</t>
+  </si>
+  <si>
+    <t>三体星系被光粒摧毁</t>
+  </si>
+  <si>
+    <t>10月，三体世界被光粒摧毁。云天明通过三个童话故事向程心传递情报。</t>
+  </si>
+  <si>
+    <t>广播纪元</t>
+  </si>
+  <si>
+    <t>太阳系毁灭</t>
+  </si>
+  <si>
+    <t>二向箔打击，太阳系二维化</t>
+  </si>
+  <si>
+    <t>5月19日，程心被唤醒。二向箔使三维空间向二维跌落，太阳系毁灭。程心乘坐星环号逃离。</t>
+  </si>
+  <si>
+    <t>掩体纪元</t>
+  </si>
+  <si>
+    <t>Month</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Day</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>16时，四维空间翘曲点与地球接触，接触点为正值君士坦丁堡战役的君士坦丁堡，吞掉了奥多修斯北部布拉赫内区的一座清真寺的塔尖。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>四维空间翘曲点接触地球</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>君士坦丁堡战役中，四维空间翘曲点与地球接触</t>
-  </si>
-  <si>
-    <t>16时，四维空间翘曲点与地球接触，接触点为正值君士坦丁堡战役的君士坦丁堡，吞掉了奥多修斯北部布拉赫内区的一座清真寺的塔尖。5月28日21时，四维空间翘曲点完全离开地球。</t>
-  </si>
-  <si>
-    <t>中世纪</t>
-  </si>
-  <si>
-    <t>叶文洁出生</t>
-  </si>
-  <si>
-    <t>叶文洁出生于1947年6月</t>
-  </si>
-  <si>
-    <t>叶泰哲之死</t>
-  </si>
-  <si>
-    <t>叶泰哲在批斗会上被打死</t>
-  </si>
-  <si>
-    <t>留下了崩溃的妻子绍琳和女儿叶文洁。这是叶文洁人生的转折点。</t>
-  </si>
-  <si>
-    <t>文革时代</t>
-  </si>
-  <si>
-    <t>红岸基地建成</t>
-  </si>
-  <si>
-    <t>红岸基地（雷达峰）建成</t>
-  </si>
-  <si>
-    <t>用于搜索地外文明的绝密国防工程。</t>
-  </si>
-  <si>
-    <t>叶文洁进入红岸</t>
-  </si>
-  <si>
-    <t>叶文洁被红岸基地吸收</t>
-  </si>
-  <si>
-    <t>叶文洁读了《寂静的春天》，帮白沐霖抄写举报信被诬陷，以戴罪立功为由进入红岸基地。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>四维空间翘曲点完全离开地球</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>四维空间离开地球</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>21时，四维空间翘曲点完全离开地球。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>君士坦丁堡陷落</t>
+  </si>
+  <si>
+    <t>傍晚，君士坦丁堡陷落。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶泰哲死亡</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶泰哲在批斗会上被打死，留下了崩溃的妻子绍琳和女儿叶文洁。
+这是叶文洁人生的转折点。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁读了《寂静的春天》，有了一个想法：人类真正的道德自觉是不可能的，就像他们不可能拔着自己的头发离开大地。
+她帮白沐霖抄写了发给中央的举报信，结果被诬陷是她写的，要被判反革命罪。
+同年，红岸基地以戴罪立功为由吸收叶文洁进入。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶得知红岸秘密</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>叶文洁发送信号</t>
-  </si>
-  <si>
-    <t>叶文洁向太阳发射信号</t>
-  </si>
-  <si>
-    <t>秋，叶文洁发现太阳是电波放大器，借试发射之机向太阳发射信号，8分钟后信号以光速飞向宇宙。</t>
-  </si>
-  <si>
-    <t>三体世界收到信号</t>
-  </si>
-  <si>
-    <t>1379号监听站收到地球消息</t>
-  </si>
-  <si>
-    <t>三体文明1379号监听站收到地球的消息，监听员发回了警告信息。</t>
-  </si>
-  <si>
-    <t>收到三体回复</t>
-  </si>
-  <si>
-    <t>叶文洁收到三体世界警告</t>
-  </si>
-  <si>
-    <t>10月21日凌晨，收到三体世界的警告回信。清晨，叶文洁回复希望三体来解决人类问题。下午杀死雷志成和杨卫宁。</t>
-  </si>
-  <si>
-    <t>黄金时代</t>
-  </si>
-  <si>
-    <t>杨冬出生</t>
-  </si>
-  <si>
-    <t>叶文洁女儿杨冬出生</t>
-  </si>
-  <si>
-    <t>1980年6月，杨冬出生。</t>
-  </si>
-  <si>
-    <t>三体舰队启航</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁得知了红岸的秘密</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1970年初夏，杨卫宁将红岸工程的真实情况（寻找地外文明）告诉叶文洁。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁使用太阳向宇宙发射信号</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1971年秋，叶文洁在杂志上发现，来自木星的电磁辐射与来自太阳的日凌干扰时间差16分42秒，刚好是从木星直接到地球和木星到太阳再到地球的时间差。所以她猜想太阳的“能量镜面”可以以数亿倍放大电磁辐射。但实验被雷志成政委以政治原因否决。
+叶文洁借试发射之机，使用12000兆赫向太阳发射信号。8分钟后，地球文明向太空发出的第一声能够被听到的啼鸣，以太阳为中心，以光速飞向整个宇宙。这时，在12000兆赫波段上，太阳是银河系中最亮的一颗星。
+但由于种种原因，红岸基地电台并未收到回波。所以叶文洁并不知道发射成功。同时，由于太阳在放大电波同时还叠加了一个正弦波，来自木星的电磁辐射波形与日凌干扰的波形看起来对不上，使叶文洁认为自己猜想有误。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁与杨卫宁组成家庭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁成家</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1971-1978年是叶文洁一生中最平静的一段时间，但也引起了她对人类恶的一面的理性思考。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体文明1379号监听站收到地球消息</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶收到三体回复</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁收到三体世界的警告信息</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>凌晨0点，在向太阳发射信息不到9年后，在叶文洁值夜班时，收到了来自三体世界的警告回信。
+在4个多小时中，叶文洁知道了三体世界的存在和他们星际移民的企图。
+清晨，叶文洁通过太阳向三体文明发送回信，表示希望他们来解决人类文明的问题。
+下午，雷志成也发现了三体文明的消息，但他不知道叶文洁已经回信。他威胁叶文洁对此事保密，想要成为第一个发现地外文明的人。
+叶文洁故意制造了设备故障，想在雷志成吊下悬崖去检修的时候将其杀掉。但杨卫宁也一起下去了，由于机会难得，她只得将两人一起杀死。
+叶文洁怀孕。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁收到三体回复</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>三体第一舰队启航</t>
-  </si>
-  <si>
-    <t>三体第一舰队向着地球的大致方向启航。</t>
-  </si>
-  <si>
-    <t>智子工程启动</t>
-  </si>
-  <si>
-    <t>三体制定杀死地球科学的计划</t>
-  </si>
-  <si>
-    <t>三体文明收到叶文洁回信，确定地球坐标。元首制定染色、神迹、智子工程计划。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体文明收到来自叶文洁的回信，确定地球坐标。
+三体文明元首制定杀死人类文明科学的计划：染色、神迹、智子工程。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>红岸基地停用</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体加速器建成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体文明用于制造智子的巨型加速器建成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体质子实验</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体文明进三次质子二维展开实验</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体文明对质子的第一次二维展开实验，失败，质子被减成一维。
+两天后，三体文明对质子的第二次二维展开实验，失败，质子只被减到三维。并且被高维中的智慧存在攻击。
+一天后，三体文明对质子的第三次二维展开实验，成功。开始在二维展开后的质子上蚀刻电路。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>智子试运行成功</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>智子第一次试运行，成功</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、3、4号智子建成，四个智子构成的量子阵列顺利建立。四个智子维度收缩至十一维。智子1号和2号被以光速发向地球。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>智子发向地球</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁退休</t>
+  </si>
+  <si>
+    <t>2个智子被以光速发向地球</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体舰队进入第一片星际尘埃云</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体舰队进入尘埃云</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体舰队进尘埃云</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁与伊文斯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1990年代初，叶文洁回到北京，在父亲叶泰哲曾工作过的清华大学教授天体物理学。
+半年后，叶文洁认识麦克麦克·伊文斯。
+3年后，叶文洁将三体文明的事告诉麦克·伊文斯。
+3年后，叶文洁来到第二红岸基地——“审判日”号轮船，成为地球三体运动最高统帅。地球三体运动诞生。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁与麦克·伊文斯</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>危机纪元开始</t>
-  </si>
-  <si>
-    <t>科学边界与科学家自杀</t>
-  </si>
-  <si>
-    <t>不到两个月内许多理论物理学家自杀。汪淼看到倒计时，宇宙背景辐射闪烁，ETO聚会，古筝行动夺取三体信息。</t>
-  </si>
-  <si>
-    <t>危机纪元</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>多位科学家自杀，危机纪元开始</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>古筝行动</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宇宙闪烁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>面壁计划启动</t>
-  </si>
-  <si>
-    <t>四位面壁者选定</t>
-  </si>
-  <si>
-    <t>中国太空军成立。特别联大通过117号决议宣布逃亡主义非法。面壁计划启动，罗辑、泰勒、雷迪亚兹、希恩斯成为面壁者。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>面壁计划启动，选定四位面壁者</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>宇宙背景辐射闪烁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007年X月
+11日，汪淼照的胶卷上出现倒计时，1200小时开始。无论是数码相机还是胶片相机，别人拍的都很正常，汪淼拍的都会出现倒计时。
+12日，倒计时直接显示在汪淼视网膜上，他停下了纳米项目后，倒计时停止并消失。
+14日，凌晨1点到5点，宇宙背景辐射闪烁。
+15日，晚上，汪淼在《三体》游戏中成功揭示了宇宙的基本结构。
+16日，凌晨，申玉菲被潘寒枪杀。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007年X月
+数天后，晚上，汪淼参加《三体》网友聚会，潘寒筛选出降临派的“同志”。
+数天后，ETO在化工场举行300多人，多为拯救派的聚会。叶文洁会上令杀手杀死潘寒。会议中途军队冲入，叶文洁被抓，过程中史强处理核弹时遭受到强烈辐射，患白血病。
+2-3天后，史强与汪淼参加制定夺取“审判日”号上的三体信息的会议。史强提出了用汪淼制造出的叫“飞刃”的纳米丝切割船体的方案，代号“古筝行动”。
+4天后，在巴拿马运河盖拉德水道，“古筝行动”成功实施，取得约28G被降临派截留的三体信息。
+3天后，三体世界与首次与地球叛军之外的人类进行了一次交流：在作战中心所有人的视网膜上出现了5个字“你们是虫子！”。此后中断了与地球的通讯。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国太空军正式成立</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国太空军成立</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010年，中国太空军正式成立，成立时包括章北海。之后，章北海在与父亲的交谈中，确立了人类必败的思想（基础理论决定一切）。
+特别联大通过117号决议，宣布逃亡主义为非法。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>NASA实验得出，阶梯计划的载荷只能在半公斤以下，维德提出只送大脑。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈勃二号装配完成。一周后，在三体行星方向上四光年处，发现三体舰队的尾迹（刷子）。约1000根，速度约100倍第三宇宙速度（1670km/s）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶梯计划只送大脑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶梯计划维德提出只送大脑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体舰队的尾迹</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体舰队尾迹</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体舰队在星际尘埃云的尾迹（刷子）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>由于人类文明即将开展面壁者计划，三体文明联系面壁者2号，告知其伊文斯命令的密码，让其继续执行杀死罗辑的任务。伪造交通事故进行刺杀，被罗辑幸运躲开。对罗辑的第二次狙击刺杀被防弹衣挡下。
+面壁计划启动。第一位是弗里德里克·泰勒，前美国国防部长；第二位是曼努尔·雷迪亚兹，委内瑞拉总统；第三位是比尔·希恩斯，科学和政治的综合素质极强；第四位是罗辑，人类在三体发来的信息中发现，他是被三体文明指名要消灭的唯一一个人类；
+ETO中，破壁人一号、二号和三号（希恩斯的妻子山杉惠子）也被选出，而罗辑，由于唯一一个知道其对三体文明威胁的人类——伊文斯已经死去，所以罗辑将直接与三体文明对决。
+罗辑找世外桃源享受，让史强找到庄颜后隐居；
+泰勒：研究宏原子核聚变，建立一支以球状闪电和宏原子核聚变为主要武器的，独立于地球主力的太空力量；在寻找赴死、牺牲精神；真实战略意图为用宏原子核聚变消灭地球太空军，使他们成为量子态，让量子幽灵去抵抗三体舰队。
+雷迪亚兹：要求研究2亿吨级以上的核弹，在某次看日出时患了恐日症；真实战略意图为用核弹减速水星，使其坠入太阳，毁灭太阳系，以此威慑三体文明。
+希恩斯：借助技术加快人脑的进化；真实战略意图为其是坚定的失败主义者和逃亡主义者，以思想刚印作为研究的最终目标，唯一目标是实现人类的逃亡。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>云天明接受阶梯计划</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>云接受阶梯计划</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三届人大常委会特别会议通过安乐死法。联合国启动群星计划。
+肺癌晚期的云天明决定安乐死，在这之前通过群星计划买下恒星DX3906送给了程心。
+程心得知云天明时无多日，将他推荐为阶梯计划候选人。
+在云天明安乐死前最后一刻，程心赶到叫停了安乐死。云天明接受了阶梯计划这个使命。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心使云天明接受阶梯计划的使命</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶梯计划实施</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空电梯天梯一号、二号、三号同时开始建造。
+罗辑和庄颜的孩子出生。
+阶梯计划实施。但在第997枚核弹爆炸后，一根帆索断了，球形舱偏航，人类丢失了它的信号。云天明的大脑以光速百分之一飞向太空深处。
+程心冬眠，以阶梯计划联络员的身份前往未来。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空电梯始建，阶梯计划实施</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰勒自杀</t>
+  </si>
+  <si>
+    <t>泰勒的破壁人出现，泰勒自杀。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>阶梯计划提出</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心提出阶梯计划并被采用</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心结束学业参加工作。很快进入行星防御理事会战略情报局（PIA）工作。她提出的阶梯计划——向三体发射达到光速百分之一的方案被采用。根据对阶梯计划的数次可行性测试，要想达到光速百分之一，探测器的质量上限一降再降，从1t到200kg，程心提出只送一个被冰冻的人。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在不到两个月时间里，许多理论物理学家先后自杀。自杀的学者大部分与“科学边界”有过联系。
+杨冬使用粒子加速器的实验被智子干扰，实验结果一片混乱。同时从母亲叶文洁电脑中得知了三体和ETO的事，随后也自杀。
+杨冬死后，叶文洁约见杨冬的高中同学罗辑，给予研究宇宙社会学的提示。三体世界得知此事后，让伊文斯杀死罗辑，同时，伊文斯教会了三体文明隐瞒杀死罗辑的原因。伊文斯将任务加密发给了面壁者2号，但暂未告知密码。
+伊文斯在与三体文明对话时，发现了三体人思维透明这一与人类的重大差异。这是伊文斯最后一次收到来自三体文明的信息。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>空天飞机出现</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>化学动力航天器的最后一代——空天飞机出现并投入大规模使用。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体舰队进入第二片尘埃云</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体舰队进入第二片星际尘埃</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>罗辑发出咒语</t>
-  </si>
-  <si>
-    <t>黑暗森林法则初现</t>
-  </si>
-  <si>
-    <t>罗辑看到宇宙真相，称黑暗森林法则。感染基因导弹，冬眠前通过太阳向宇宙发射187J3X1恒星坐标。</t>
-  </si>
-  <si>
-    <t>水滴攻击</t>
-  </si>
-  <si>
-    <t>三体水滴摧毁人类舰队</t>
-  </si>
-  <si>
-    <t>三体水滴到达太阳系，封死太阳。丁仪考察水滴，水滴启动，几乎全歼人类舰队。只有量子号和青铜时代号逃脱。</t>
-  </si>
-  <si>
-    <t>建立威慑</t>
-  </si>
-  <si>
-    <t>罗辑建立黑暗森林威慑</t>
-  </si>
-  <si>
-    <t>罗辑与三体对决，以雪地工程布置的核弹建立威慑。三体接受谈判，解除太阳封锁。罗辑成为执剑人。</t>
-  </si>
-  <si>
-    <t>威慑终结</t>
-  </si>
-  <si>
-    <t>程心接任执剑人</t>
-  </si>
-  <si>
-    <t>程心当选执剑人，16分钟后水滴摧毁引力波发射器，威慑终止。万有引力号和蓝色空间号启动引力波广播。</t>
-  </si>
-  <si>
-    <t>威慑纪元</t>
-  </si>
-  <si>
-    <t>三体世界毁灭</t>
-  </si>
-  <si>
-    <t>三体星系被光粒摧毁</t>
-  </si>
-  <si>
-    <t>10月，三体世界被光粒摧毁。云天明通过三个童话故事向程心传递情报。</t>
-  </si>
-  <si>
-    <t>广播纪元</t>
-  </si>
-  <si>
-    <t>太阳系毁灭</t>
-  </si>
-  <si>
-    <t>二向箔打击，太阳系二维化</t>
-  </si>
-  <si>
-    <t>5月19日，程心被唤醒。二向箔使三维空间向二维跌落，太阳系毁灭。程心乘坐星环号逃离。</t>
-  </si>
-  <si>
-    <t>掩体纪元</t>
-  </si>
-  <si>
-    <t>Month</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Day</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑暗森林法则</t>
+  </si>
+  <si>
+    <t>罗辑看到了宇宙的真相，称其为黑暗森林法则</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰勒的破壁人出现。三体人不怕量子幽灵。泰勒自杀。
+于雷迪亚兹和希恩斯的下一步研究需要更高计算力的计算机，所以都选择进入冬眠。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>PDC从罗辑身边带走了庄颜和孩子，在末日等待罗辑。
+之后，罗辑看到了宇宙的真相，称其为“黑暗森林法则”，并躲入地堡中。同时，三体向ETO第二次发出了消灭罗辑的指令，并发射10个水滴探测器以更快的速度驶向地球。
+一周后，ETO散播针对罗辑的基因导弹病毒。
+一周后，在PDC会议上，罗辑公布了自己要用太阳向宇宙中发射的咒语——187J3X1恒星的位置信息。
+罗辑感染了基因导弹，无法医治，被紧急冬眠。
+两周后，罗辑的咒语通过太阳以光速飞向宇宙。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑感染了基因导弹，无法医治，被紧急冬眠。
+两周后，罗辑的咒语通过太阳以光速飞向宇宙。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑的咒语通过太阳以光速飞向宇宙</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>技术突破</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>天梯投入使用，可控核聚变重大突破</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体舰队的第二个尾迹</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体舰队在第2片星际尘埃上的航迹被发现，同时发现了三体舰队发射水滴探测器的事实。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>天梯一号、二号、三号投入正式使用。
+可控核聚变取得重大突破。
+中国开始计划经济，分发粮票等。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>章北海暗杀老航天人</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>章北海暗杀</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>章北海在太空中用陨石做成的子弹伪装成陨石雨，暗杀了反对研究无工质飞船引擎的三名老航天人。促使后期研究方向定为无工质引擎。
+章北海带着常伟思的信，与特遣队一起冬眠。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>章北海暗杀反对研究无工质引擎的老航天人</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>史晓明出狱</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -244,7 +613,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,6 +773,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -586,7 +963,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -701,6 +1078,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -830,11 +1376,68 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1192,429 +1795,931 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7075CE0F-CB4C-44E0-830B-E1E248B01C04}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="5.25" customWidth="1"/>
-    <col min="4" max="4" width="15.75" customWidth="1"/>
-    <col min="6" max="6" width="3.625" customWidth="1"/>
+    <col min="1" max="1" width="4.75" style="14" customWidth="1"/>
+    <col min="2" max="2" width="3.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="2.75" style="15" customWidth="1"/>
+    <col min="4" max="4" width="15.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="33.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="62.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="64.75" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="16"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="11">
+        <v>1453</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="12">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="14">
+        <v>1453</v>
+      </c>
+      <c r="B3" s="1">
+        <v>5</v>
+      </c>
+      <c r="C3" s="15">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <v>1453</v>
+      </c>
+      <c r="B4" s="1">
+        <v>5</v>
+      </c>
+      <c r="C4" s="15">
+        <v>29</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8">
+        <v>1947</v>
+      </c>
+      <c r="B5" s="5">
+        <v>6</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="14">
+        <v>1967</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="14">
+        <v>1968</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="14">
+        <v>1969</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="14">
+        <v>1970</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="14">
+        <v>1971</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="14">
+        <v>1973</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>1975</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="11">
+        <v>1979</v>
+      </c>
+      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="C13" s="12">
+        <v>21</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="I13" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="14">
+        <v>1980</v>
+      </c>
+      <c r="B14" s="1">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="14">
+        <v>1982</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="1">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="14">
+        <v>1984</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="14">
+        <v>1987</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="14">
+        <v>1988</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="14">
+        <v>1990</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="14">
+        <v>1992</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="14">
+        <v>1995</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="14">
+        <v>1999</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="14">
+        <v>2004</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <v>2006</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" s="4"/>
+      <c r="I24" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="14">
+        <v>2007</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+      <c r="A26" s="14">
+        <v>2007</v>
+      </c>
+      <c r="B26" s="1">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D26" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="114" x14ac:dyDescent="0.2">
+      <c r="A27" s="14">
+        <v>2007</v>
+      </c>
+      <c r="B27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="14">
+        <v>2007</v>
+      </c>
+      <c r="B28" s="1">
+        <v>7</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A29" s="14">
+        <v>2010</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="14">
+        <v>2010</v>
+      </c>
+      <c r="B30" s="1">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="292.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="14">
+        <v>2010</v>
+      </c>
+      <c r="B31" s="1">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="1">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="14">
+        <v>2010</v>
+      </c>
+      <c r="B32" s="1">
+        <v>7</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="14">
+        <v>2011</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="14">
+        <v>2014</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="14">
+        <v>2015</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="14">
+        <v>2015</v>
+      </c>
+      <c r="B36" s="1">
+        <v>2</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="14">
+        <v>2015</v>
+      </c>
+      <c r="B37" s="1">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="A38" s="14">
+        <v>2015</v>
+      </c>
+      <c r="B38" s="1">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="D38" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="14">
+        <v>2015</v>
+      </c>
+      <c r="B39" s="1">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1453</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
+      <c r="D39" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A40" s="14">
+        <v>2019</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A41" s="14">
+        <v>2019</v>
+      </c>
+      <c r="B41" s="1">
+        <v>2</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A42" s="14">
+        <v>2019</v>
+      </c>
+      <c r="B42" s="1">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2">
+      <c r="D42" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" s="14">
+        <v>2026</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A44" s="14">
+        <v>2205</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>1947</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G44" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A45" s="14">
+        <v>2208</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="14">
+        <v>2270</v>
+      </c>
+      <c r="B46" s="1">
         <v>11</v>
       </c>
-      <c r="F3">
+      <c r="C46" s="15">
+        <v>28</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="1">
         <v>0</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>1967</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4">
+      <c r="G46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" s="14">
+        <v>2274</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F47" s="1">
         <v>0</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>1968</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>1969</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6">
+      <c r="G47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="14">
+        <v>2400</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1971</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7">
-        <v>2</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>1975</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>1979</v>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>1980</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1982</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>1984</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>2007</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="G48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I48" s="16" t="s">
         <v>44</v>
-      </c>
-      <c r="I13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>2010</v>
-      </c>
-      <c r="D14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>2015</v>
-      </c>
-      <c r="D15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>2205</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2208</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>2270</v>
-      </c>
-      <c r="B18">
-        <v>11</v>
-      </c>
-      <c r="C18">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>2274</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A20">
-        <v>2400</v>
-      </c>
-      <c r="D20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I20" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/CSV/Timelines.xlsx
+++ b/CSV/Timelines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1Data\1study\WebLearn\Timeline\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86713ECD-F007-4A49-BCE9-9B1FBB1C784B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A1A23E-60E5-403D-A99E-4132D252C3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
   </bookViews>
   <sheets>
     <sheet name="ThreeBody" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="340">
   <si>
     <t>Year</t>
   </si>
@@ -106,55 +106,13 @@
     <t>水滴攻击</t>
   </si>
   <si>
-    <t>三体水滴摧毁人类舰队</t>
-  </si>
-  <si>
-    <t>三体水滴到达太阳系，封死太阳。丁仪考察水滴，水滴启动，几乎全歼人类舰队。只有量子号和青铜时代号逃脱。</t>
-  </si>
-  <si>
-    <t>建立威慑</t>
-  </si>
-  <si>
-    <t>罗辑建立黑暗森林威慑</t>
-  </si>
-  <si>
-    <t>罗辑与三体对决，以雪地工程布置的核弹建立威慑。三体接受谈判，解除太阳封锁。罗辑成为执剑人。</t>
-  </si>
-  <si>
-    <t>威慑终结</t>
-  </si>
-  <si>
-    <t>程心接任执剑人</t>
-  </si>
-  <si>
-    <t>程心当选执剑人，16分钟后水滴摧毁引力波发射器，威慑终止。万有引力号和蓝色空间号启动引力波广播。</t>
-  </si>
-  <si>
     <t>威慑纪元</t>
   </si>
   <si>
-    <t>三体世界毁灭</t>
-  </si>
-  <si>
     <t>三体星系被光粒摧毁</t>
   </si>
   <si>
-    <t>10月，三体世界被光粒摧毁。云天明通过三个童话故事向程心传递情报。</t>
-  </si>
-  <si>
     <t>广播纪元</t>
-  </si>
-  <si>
-    <t>太阳系毁灭</t>
-  </si>
-  <si>
-    <t>二向箔打击，太阳系二维化</t>
-  </si>
-  <si>
-    <t>5月19日，程心被唤醒。二向箔使三维空间向二维跌落，太阳系毁灭。程心乘坐星环号逃离。</t>
-  </si>
-  <si>
-    <t>掩体纪元</t>
   </si>
   <si>
     <t>Month</t>
@@ -254,10 +212,6 @@
   </si>
   <si>
     <t>叶收到三体回复</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁收到三体世界的警告信息</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -393,15 +347,6 @@
 14日，凌晨1点到5点，宇宙背景辐射闪烁。
 15日，晚上，汪淼在《三体》游戏中成功揭示了宇宙的基本结构。
 16日，凌晨，申玉菲被潘寒枪杀。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2007年X月
-数天后，晚上，汪淼参加《三体》网友聚会，潘寒筛选出降临派的“同志”。
-数天后，ETO在化工场举行300多人，多为拯救派的聚会。叶文洁会上令杀手杀死潘寒。会议中途军队冲入，叶文洁被抓，过程中史强处理核弹时遭受到强烈辐射，患白血病。
-2-3天后，史强与汪淼参加制定夺取“审判日”号上的三体信息的会议。史强提出了用汪淼制造出的叫“飞刃”的纳米丝切割船体的方案，代号“古筝行动”。
-4天后，在巴拿马运河盖拉德水道，“古筝行动”成功实施，取得约28G被降临派截留的三体信息。
-3天后，三体世界与首次与地球叛军之外的人类进行了一次交流：在作战中心所有人的视网膜上出现了5个字“你们是虫子！”。此后中断了与地球的通讯。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -479,13 +424,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>太空电梯天梯一号、二号、三号同时开始建造。
-罗辑和庄颜的孩子出生。
-阶梯计划实施。但在第997枚核弹爆炸后，一根帆索断了，球形舱偏航，人类丢失了它的信号。云天明的大脑以光速百分之一飞向太空深处。
-程心冬眠，以阶梯计划联络员的身份前往未来。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>太空电梯始建，阶梯计划实施</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -592,10 +530,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>章北海暗杀</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>章北海在太空中用陨石做成的子弹伪装成陨石雨，暗杀了反对研究无工质飞船引擎的三名老航天人。促使后期研究方向定为无工质引擎。
 章北海带着常伟思的信，与特遣队一起冬眠。</t>
     <phoneticPr fontId="18" type="noConversion"/>
@@ -606,6 +540,926 @@
   </si>
   <si>
     <t>史晓明出狱</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007年X月
+2-3天后，史强与汪淼参加制定夺取“审判日”号上的三体信息的会议。史强提出了用汪淼制造出的叫“飞刃”的纳米丝切割船体的方案，代号“古筝行动”。
+4天后，在巴拿马运河盖拉德水道，“古筝行动”成功实施，取得约28G被降临派截留的三体信息。
+3天后，三体世界与首次与地球叛军之外的人类进行了一次交流：在作战中心所有人的视网膜上出现了5个字“你们是虫子！”。此后中断了与地球的通讯。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2007年X月
+数天后，晚上，汪淼参加《三体》网友聚会，潘寒筛选出降临派的“同志”。
+数天后，ETO在化工场举行300多人，多为拯救派的聚会。叶文洁会上令杀手杀死潘寒。会议中途军队冲入，叶文洁被抓，过程中史强处理核弹时遭受到强烈辐射，患白血病。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁被抓</t>
+  </si>
+  <si>
+    <t>叶文洁在ETO聚会杀死潘寒，被抓</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空电梯始建</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空电梯天梯开始建造</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太空电梯天梯一号、二号、三号同时开始建造。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑和庄颜的孩子出生。
+阶梯计划实施。但在第997枚核弹爆炸后，一根帆索断了，球形舱偏航，人类丢失了它的信号。云天明的大脑以光速百分之一飞向太空深处。
+程心冬眠，以阶梯计划联络员的身份前往未来。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>章北海暗杀老航天</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>常伟思退役</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷迪亚兹和希恩斯被唤醒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷和希被唤醒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷迪亚兹被砸死</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷迪亚兹被人民用石头砸死</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>水星实验在水星并不深的地层中进行，恒星型氢弹的巨大威力给主防御的领导者们留下了深刻的印象。
+10小时后，雷迪亚兹的破壁人出现。三体文明不怕，因为人类不可能造出足够多的核弹。
+PDC会议中，雷迪亚兹谎称自己身上有反触发系统成功脱身回国。6小时后，雷迪亚兹回到了自己的国家，被自己的人民用石头砸死。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷迪亚兹和希恩斯被唤醒。
+希恩斯在人脑中发现了思维做出判断的机制，通过对部分神经元的某一部分施加影响，可以使大脑不经思维就做出判断，相信某个信息为真或者伪。
+雷迪亚兹制造出了人类最大的氢弹，以建造日后的水星基地为由，要求在水星的地下进行试验。
+信念中心建成，太空军可以自愿接受人类必胜的思想钢印。但希恩斯隐蔽地修改了思想钢印机器程序中的一个正负号，使对命题判断为伪（人类必败）。
+希恩斯和山杉惠子进入冬眠。山杉惠子在冬眠前最后一刻思考出了希恩斯的计划，但已经无法呼叫冬眠停止。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大低谷开始</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大低谷结束</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人民生活水平恢复到黄金时代的水平</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人民生活水平恢复到黄金时代的水平。一切开始飞快进步，技术障碍一个个被突破。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界人口从83亿降低到35亿。
+太空武装力量到了崩溃的边缘，增援特遣队对稳定局势发挥了巨大作用。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大低谷开始，人口暴降</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>史强妻子去世</t>
+  </si>
+  <si>
+    <t>章北海妻子去世</t>
+  </si>
+  <si>
+    <t>章北海女儿去世</t>
+  </si>
+  <si>
+    <t>大低谷</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人类社会再次宣布进入战争状态，开始建造太空舰队。太空舰队成为独立国家。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始建造太空舰队</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>开始建造太空舰队，成为独立国家</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>187J3X1恒星被光粒摧毁</t>
+  </si>
+  <si>
+    <t>187J3X1被摧毁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>丁仪被唤醒</t>
+  </si>
+  <si>
+    <t>丁仪被唤醒，在北京大学物理系任教。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体舰队在第5片星际尘埃上的航迹被发现，队形变得稀稀拉拉，一大半早就停止了加速。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体舰队的第五个尾迹</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人类观测到187J3X1恒星被摧毁，但没人注意。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>观测到187J3X1被摧毁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑被唤醒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑、希恩斯和山杉惠子被唤醒，面壁计划结束</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑、希恩斯和山杉惠子被唤醒，参加面壁计划的最后一次听证会，宣布面壁计划结束。会后，山杉惠子公开自己破壁人身份，解读了希恩斯的计划。
+罗辑与史强进入城市后，潜伏了一个多世纪的针对罗辑的KILLER杀人病毒被唤醒，罗辑多次遭到暗杀，被迫到地上生活。
+史强在地上见到了儿子史晓明，两人现仅相差5岁。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>章北海逃离</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>增援未来的章北海被唤醒，为了审查钢印族，代替东方延绪成为了“自然选择”号的代理舰长。
+随后，章北海驾驶“自然选择”号，使用前进四逃离。人类舰队派了4艘战舰追击，分别为“蓝色空间”号、“企业”号、“深空”号和“终极规律”号。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>章北海被唤醒，驾驶“自然选择”号逃离</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人类发现了187J3X1恒星被摧毁，人类意识到罗辑的咒语生效，将其视为救世主。罗辑向史强解释了宇宙的黑暗森林法则。
+罗辑恢复了面壁者身份，但太阳已经被封锁，地球不能再发射恒星级电波。
+罗辑加入雪地工程，表面上是在太阳系内制作尘埃云对水滴进行预测，实际上他对每个核弹进行精确位置排布，使其爆炸后，从远方观察，太阳将在可见光等波段闪烁，发出三体世界坐标。当然，同时地球坐标也会暴露。罗辑要以此对三体世界进行威慑。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑被视为救世主</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现187J3X1被摧毁，罗辑的咒语生效，视其为救世主</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体水滴摧毁人类舰队，封锁太阳</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>处在太阳系遥远两侧的两个星舰地球几乎同时发生了黑暗战役，其中“青铜时代”号在全舰投票中，有94%（1670人）赞成攻击。“蓝色空间”号和“青铜时代”号活了下来，开始收集其它战舰的资源。
+在“青铜时代”号加速离开一年后，“蓝色空间”号也加速离开。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>水滴到达太阳系</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体舰队在第7片星际尘埃上的航迹被发现，绝大部分战舰都进入减速状态。有一艘战舰没有减速，人类文明认为是来谈判的。
+联合舰队从木星基地起航，共2015艘恒星级战舰组成联合舰队，统一出击，拦截三体水滴探测器，由丁仪首次接触水滴探测器。在丁仪的建议下，舰队同意在考察队出发后让“量子”号和“青铜时代”号进入深水状态。
+5个小时后，“螳螂”号捕获了水滴。
+考察队接触后发现，水滴表面绝对光滑。之后，水滴启动，使用最原始的撞击方式，在30多分钟后，几乎全歼了人类舰队。只有已经提前进入深水状态的“量子”号和“青铜时代”号成功地逃脱了水滴的攻击。
+至此，人类太空舰队仅剩7艘星际战舰：“自然选择”号和追击舰“蓝色空间”号、“企业”号、“深空”号、“终极规律”号，和从水滴攻击中成功逃脱的“量子”号和“青铜时代”号。两行人沿着几乎相反的方向飞离太阳系。
+十多个小时后，水滴到达地球，封死了太阳。
+人类集体精神崩溃，逃亡主义迅速复活。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>史强被唤醒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体水滴探测器到达太阳系。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>史强被唤醒，白血病已被治好</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星舰地球黑暗战役</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>两个星舰地球发生黑暗战役，“蓝色空间”号和“青铜时代”号活了下来</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑被视为骗子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪地工程陷入停顿。
+随着时间的推移，罗辑在公众眼中的形象渐渐衰落，成为了个大骗子。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪地工程陷入停顿，罗辑被视为骗子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>建立威慑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑建立黑暗森林威慑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人类得知宇宙的黑暗森林状态</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人类得知黑暗森林</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11月初，人类得知宇宙的黑暗森林状态，对电磁发射进行严格管制。
+人类政府令“青铜时代”号和“蓝色空间”号立刻返航。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑与三体文明再次进行对决，告知三体世界自己的计划。
+三体文明接受谈判，解除对太阳的封锁，让水滴和三体舰队改变航向。并将与三体世界的谈判权给了人类政府，但由于威慑度的问题，威慑控制权马上交还给了罗辑，并称其为“执剑人”。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>青铜时代号返航</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“青铜时代”号返航。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>引力发射器减少</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>引力发射器减少到四个</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>主张彻底消灭三体世界的极端组织“地球之子”企图夺取南极大陆的引力波发射器，差点成功。
+在三体世界的压力下，地球将引力发射器减少到四个，分别位于亚洲、北美、欧洲和“万有引力”号飞船。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“青铜时代”号在前来迎接的“万有引力”号的伴随下到达地球，随后全体人员都因谋杀罪和反人类罪被逮捕。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>青铜时代号到达</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>青铜时代号到达地球，全体人员被逮捕</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>对“青铜时代”号进行审判。随后，“青铜时代”号的军官拼死向“蓝色空间”号发出了警告信息。
+“蓝色空间”号加速逃离，“万有引力”号和2个水滴立刻起航追击。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>警告蓝色空间号</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“青铜时代”号军官拼死向“蓝色空间”号发送警告</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体取得云天明大脑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体取得云的大脑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体第一舰队截获阶梯飞行器，取得云天明大脑。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“蓝色空间”号停止加速。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色空间停止加速</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体可光速行驶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体文明制造出能够光速行驶的第二舰队。
+猜测人类文明将对黑暗森林威慑心态转变，很可能会选择低威慑度的执剑人，所以冒险派出第二支舰队。
+为了防止曲率引擎产生的加速痕迹出现在三体星球附近，第二舰队将在穿过第一片星际尘埃云后再进入光速。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体文明制造出能够光速行驶的第二舰队</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体舰队进入光速</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体第二舰队穿过第一片星际尘埃云，穿过后立刻进入光速。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体第二舰队穿过星际尘埃云后立刻进入光速</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“蓝色空间”号投降</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色空间号投降</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“蓝色空间”号投降，两舰同时开始减速</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“蓝色空间”号与“万有引力”号距离15个天文单位时，“蓝色空间”号投降，两舰同时开始减速。“万有引力”号全舰开始苏醒。
+两舰开始接触四维空泡，出现异常现象。在“万有引力”号上，被看作心理问题忽略。在“蓝色空间”号上则进行研究。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>由于发现DX3906有一个与地球十分相似的类地行星，所以程心被唤醒。
+维德伪造艾AA电话，刺杀程心，失败。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心被唤醒</t>
+  </si>
+  <si>
+    <t>程心被唤醒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心被唤醒，维德刺杀程心失败</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270年下半年，“蓝色空间”号通过四维空间翘曲点分多批向“万有引力”号飞船投放60多名陆战队员和军官。并使用小型穿梭机杀死了水滴。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心以压倒性优势当选“执剑人”。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心当选执剑人</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“万有引力”号距“蓝色空间”号仅3个天文单位。
+三体文明给与“万有引力”号随行的两个水滴发出指令，在五个月后威慑控制权移交时立刻摧毁“万有引力”号。
+与“万有引力”和“蓝色空间”同行的两个水滴进入智子盲区，与地球的实时通信中断。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“魔戒”坠入三维空间，出现了长度1亿3000万千米的线。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>威慑后</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>威慑纪元</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“万有引力”号和“蓝色空间”号退出四维碎块。并发现四维碎块本身在缩小。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现四维碎块缩小</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现四维碎块本身在缩小</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“魔戒”坠入三维空间</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔戒坠入三维空间</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>11月28日
+16点10分，罗辑将威慑控制权移交给程心。
+16:17:34，水滴来袭地球。同时水滴攻击“万有引力”号和“蓝色空间”号。
+半分钟后，水滴没有击中“万有引力”号和“蓝色空间”号。“万有引力”号的指挥官们发现水滴死了，“蓝色空间”号通过四维空间翘曲点推偏水滴，救了两舰。
+16:27:58，地球上所有引力波发射器被摧毁，太阳被封锁，地球的黑暗森林威慑终止。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“万有引力”号被“蓝色空间”号占领。
+21点，两舰发现三体第二舰队正在以光速驶向地球。两舰猜测地球方已发生事变，且引力波广播没有启动。
+两舰进行全民公决后，启动了引力波发射器。
+11月29日
+“蓝色空间”号将四维空间翘曲点的存在告诉“万有引力”号船员。
+派出探险队进入四维空间对四维物体“魔戒”进行探测。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>引力波发射器启动</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“万有引力”号启动了引力波发射器</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>地球观测到三体世界派出的第二支舰队，穿过第1片尘埃云。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体第二舰队</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体第二舰队穿过第1片尘埃云</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>地球观测到三体第二舰队，穿过第2片尘埃云，发现三体舰队达到了光速。
+三体舰队到达距太阳6000个天文单位处，脱离光速至光速的15%，使用常规推进器减速。
+智子命令人类一年内移民到保留地——澳大利亚和火星，全人类移民开始。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体第二舰队达到光速</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体达到光速</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界人口的一半，21亿人已经迁移到澳大利亚。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>21亿人迁至澳大利亚</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>21亿人至澳大利亚</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>发现三体第二舰队以光速穿过第2片尘埃云，全人类移民开始。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>堪培拉惨案发生。饥饿的移民大军与堪培拉军队发生冲突，十多天的混乱后，死亡50多万人，几千万人完全断绝了食物和饮水供应。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>堪培拉惨案</t>
+  </si>
+  <si>
+    <t>饥饿的移民大军与堪培拉军队发生冲突</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>澳大利亚人数达到34亿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>34亿人于澳大利亚</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大移民完成。此时澳大利亚41亿6000有万人，火星基地100万人，地球治安军500万人，200万地球抵抗运动成员等。
+治安军开始打击电力系统、港口和大型运输设备。
+智子宣布，澳大利亚必须处于低技术的农业社会，禁止使用包括电力在内的任何现代技术。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大移民完成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>去澳大利亚的大移民完成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体文明得知了“万有引力”号启动了引力波广播，决定放弃地球。
+三体第二舰队转向，所有水滴撤离。
+人类开始从澳大利亚疏散。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体得知引力波广播启动</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>得知引力波启动</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体得知引力波广播启动，放弃地球，人类从澳大利亚疏散</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太阳系毁灭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>大疏散完成</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心视网膜剥离坏死，克隆培育需要5年左右，所以程心短期冬眠。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心短期冬眠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心视网膜剥离坏死，短期冬眠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>各大城市的伤痕完全消失</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>城市伤痕完全消失</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>10月，三体世界被光粒摧毁，发射光粒的是某个宇宙飞行器。。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体星系毁灭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>罗辑从智子口中问出，有可能向宇宙发布避免黑暗森林打击的安全声明。
+之后，智子告诉程心，云天明要见她。
+三天后，在地日拉格朗日点，程心通过智子会见了云天明。会见中，云天明讲了三个他编的藏有海量信息的童话故事：《国王的新画师》、《饕餮海》和《深水王子》。
+联合国成立情报解读委员会（IDC），开始解读云天明的三个童话故事。
+掩体计划得到空前关注。
+云天明情报中，曲率驱动和降低光速（黑域）以达到安全声明的隐喻被解读，但针眼画师的画这个隐喻最终都未被成功解读。此隐喻的是对于太阳系这种多行星星系，将会使用二向箔进行降维黑暗森林打击。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心被唤醒，视力恢复。
+人类观测到三体世界被摧毁。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>云天明的三个童话</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>云天明对程心讲了三个藏有海量信息的童话故事</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>曲率飞船研究被禁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>得知曲率飞船进入光速会留下航迹，曲率研究被禁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心将自己星环公司的移交给维德，进行曲率驱动研究。条件是若在研制光速飞船过程中有可能危害人类生命，必须唤醒程心。
+程心与艾AA进入冬眠。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>林格-斐兹罗观测站在三体恒星残骸处和三体第二舰队进入光速的位置，发现了“肥皂泡”，得知曲率驱动飞船在进入光速的加速阶段会留下航迹。曲率驱动的研究被完全禁止。
+两天后，关于曲率驱动航迹的警告被误传，人们以为是打击警告，产生动乱，死亡1万多人。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心冬眠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心将星环公司交给维德，与艾AA进入冬眠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑洞项目开始。使用环日加速器和木卫十三制作了一个微型黑洞。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩体纪元</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑洞项目开始</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用环日加速器制作了一个微型黑洞</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环集团公开宣布研制曲率飞船的计划，与联邦政府摩擦不断。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环集团公开研制曲率飞船计划</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环公开曲率计划</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑洞项目研究者高Way主动进入微型黑洞</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>高Way主动进入微型黑洞</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>高Way进入黑洞</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心命令星环集团投降</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心命令星环投降</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环集团宣布脱离太阳系联邦独立，与太阳系政府间的冲突升级。星环集团决定使用反物质子弹进行威慑。
+9日，程心在木星背面的亚洲一号太空城被唤醒。
+程心命令星环集团投降。星环集团向联邦政府投降。
+一周后，星环集团被宣布为非法，维德等人被逮捕。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>维德被执行死刑。
+程心进入冬眠，预定在打击之后唤醒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>维德被执行死刑，程心进入冬眠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心被唤醒，命令星环集团投降</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>维德死刑 程心冬眠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环集团的残余力量在水星秘密基地恢复了空间曲率驱动的研究。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环集团在水星秘密基地恢复曲率引擎研究</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环集团恢复曲率引擎研究</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环恢复曲率研究</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环集团发现了曲率驱动尾迹可以降低光速，可以制作黑域，所以与联邦政府达成了合作。
+这里原文时间出入很大：程心逃亡时罗辑告诉他，韦德死后35年水星基地恢复，韦德死于掩体纪元11年，那么掩体纪元46年才开始进行研究。而后又说进行了半个世纪的研究，但是后面我们知道太阳系在掩体纪元67年就毁灭了，时间出入很大，这里只能压缩研究时间以对齐主要时间轴。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环集团发现曲率尾迹可降低光速制作黑域，与政府达成合作</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星环发现黑域制法</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩体纪元11年</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩体纪元46年</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩体纪元67年</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>一艘智慧飞船以接近光速的速度从奥尔特星云外侧掠过，对太阳系发射了二向箔。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>一艘智慧飞船对太阳系发射了二向箔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞船发射二向箔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三套曲率引擎制造完成。其中第一套引擎已经经过3年测试完，第二和三套进行测试。
+第一套曲率引擎被安装在星环号上。
+太阳系预警系统发现了此不明智慧飞船，并发现其向太阳系发射的东西。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>曲率引擎完成测试</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>3套曲率引擎制造完成。第1套测试完被安装在星环号上</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>位于银河系猎户旋臂的歌者发现了与三体世界交流的太阳系，也打出了二向箔。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>距太阳150个天文单位的二向箔减速至光速千分之一，人类出动飞船进行拦截。
+二向箔的封装力场完全蒸发，三维空间开始向二维跌落，逃逸速度为光速，人类文明无生还希望。
+5月19日，程心被唤醒。
+太阳系联邦政府正式向国际社会发布黑暗森林打击警报。
+程心与艾AA乘坐星环号到冥王星，运出部分文物。
+太阳系星球开始坠入二维。
+程心与艾AA被告知星环号可进行光速航行。罗辑令飞船AI进入光速飞行，程心和艾AA以光速逃离了太阳系，目标为程心的星星——287光年外的DX3906。
+太阳系毁灭。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>歌者打出了二向箔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>歌者文明发现与三体交流的太阳系，也打出了二向箔</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>二向箔打击，太阳系二维化，程心与艾AA逃跑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>银河纪元</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>星舰文明到新世界</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2400年代，“万有引力”号和“蓝色空间”号到达新世界</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2500年代，人类新世界制造出曲率光速飞船。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>人类新文明制造出曲率光速飞船</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心和艾AA到达（程心参考系约10天）。见到等待她们的关一帆。
+发现有5艘不明宇宙飞船在DX3906的第一颗行星——“灰星”表面降落，关一帆与程心一起去探察。
+4天后，到达“灰星”，在其表面上发现了那5艘飞船留下的光速为0的航迹——死线。两人马上回返。
+4天后，云天明来到DX3906。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心到达DX3906</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心和艾AA到达DX3906，见到关一帆</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>新文明达到光速</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心坠入黑域</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心和关一帆坠入黑域</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑域纪元</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在程心和关一帆乘坐穿梭机着陆过程中，死线扩散了（有可能因为云天明飞船的扰动），穿梭机被困，以光速绕行星运动。
+DX3906被黑域包裹。
+关一帆开始初始化神经元计算机，以控制飞船脱离光速。
+18903729地球年后，飞船脱离光速。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>掩体纪元66年</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶文洁收到三体世界的警告信息，并回复</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“蓝色空间”号杀死水滴</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝色空间杀死水滴</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>“蓝色空间”号通过四维空间翘曲点杀死了水滴</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体令水滴在威慑控制权移交时摧毁“万有引力”号。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体计划摧毁“万有引力”号</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>三体预定水滴攻击</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心接手 水滴进攻</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心接手执剑人，水滴进攻，威慑终结</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1795,18 +2649,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7075CE0F-CB4C-44E0-830B-E1E248B01C04}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.75" style="14" customWidth="1"/>
-    <col min="2" max="2" width="3.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.75" style="15" customWidth="1"/>
+    <col min="2" max="2" width="3.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4" style="15" customWidth="1"/>
     <col min="4" max="4" width="15.75" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="3.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="33.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="64.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="16"/>
+    <col min="9" max="9" width="11.875" style="16" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1815,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>1</v>
@@ -1850,19 +2704,19 @@
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>8</v>
@@ -1879,16 +2733,16 @@
         <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="I3" s="16" t="s">
         <v>8</v>
@@ -1905,13 +2759,13 @@
         <v>29</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="I4" s="16" t="s">
         <v>8</v>
@@ -1941,7 +2795,7 @@
         <v>1967</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1950,7 +2804,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="I6" s="16" t="s">
         <v>11</v>
@@ -1990,7 +2844,7 @@
         <v>16</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="I8" s="16" t="s">
         <v>11</v>
@@ -2001,16 +2855,16 @@
         <v>1970</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="I9" s="16" t="s">
         <v>11</v>
@@ -2021,16 +2875,16 @@
         <v>1971</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F10" s="1">
         <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="I10" s="16" t="s">
         <v>11</v>
@@ -2041,13 +2895,16 @@
         <v>1973</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>65</v>
+        <v>51</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>11</v>
@@ -2067,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>18</v>
@@ -2087,19 +2944,19 @@
         <v>21</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F13" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>331</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="I13" s="13" t="s">
         <v>19</v>
@@ -2130,13 +2987,13 @@
         <v>1982</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>23</v>
@@ -2159,7 +3016,7 @@
         <v>25</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="I16" s="16" t="s">
         <v>19</v>
@@ -2170,7 +3027,10 @@
         <v>1987</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>74</v>
+        <v>59</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
       </c>
       <c r="I17" s="16" t="s">
         <v>19</v>
@@ -2181,10 +3041,13 @@
         <v>1988</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>75</v>
+        <v>60</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="I18" s="16" t="s">
         <v>19</v>
@@ -2195,13 +3058,16 @@
         <v>1990</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>77</v>
+        <v>62</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="I19" s="16" t="s">
         <v>19</v>
@@ -2212,10 +3078,13 @@
         <v>1992</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>80</v>
+        <v>65</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="I20" s="16" t="s">
         <v>19</v>
@@ -2226,13 +3095,16 @@
         <v>1995</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>83</v>
+        <v>68</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>19</v>
@@ -2243,13 +3115,16 @@
         <v>1999</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>89</v>
+        <v>74</v>
+      </c>
+      <c r="F22" s="1">
+        <v>5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>19</v>
@@ -2260,7 +3135,10 @@
         <v>2004</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>84</v>
+        <v>69</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
       </c>
       <c r="I23" s="16" t="s">
         <v>19</v>
@@ -2273,14 +3151,16 @@
       <c r="B24" s="4"/>
       <c r="C24" s="18"/>
       <c r="D24" s="20" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
       <c r="G24" s="20" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="H24" s="4"/>
       <c r="I24" s="19" t="s">
@@ -2292,16 +3172,16 @@
         <v>2007</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="F25" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="I25" s="16" t="s">
         <v>26</v>
@@ -2312,16 +3192,22 @@
         <v>2007</v>
       </c>
       <c r="B26" s="1">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>121</v>
+        <v>104</v>
+      </c>
+      <c r="F26" s="1">
+        <v>3</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>123</v>
+        <v>106</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="114" x14ac:dyDescent="0.2">
@@ -2329,397 +3215,1930 @@
         <v>2007</v>
       </c>
       <c r="B27" s="1">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>95</v>
+        <v>80</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="I27" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="156.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A28" s="14">
         <v>2007</v>
       </c>
       <c r="B28" s="1">
-        <v>7</v>
+        <v>-6</v>
+      </c>
+      <c r="C28" s="15">
+        <v>-15</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>94</v>
+        <v>130</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="I28" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A29" s="14">
-        <v>2010</v>
+        <v>2007</v>
+      </c>
+      <c r="B29" s="1">
+        <v>-7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>102</v>
+        <v>79</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="I29" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A30" s="14">
         <v>2010</v>
       </c>
-      <c r="B30" s="1">
-        <v>5</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>107</v>
+        <v>85</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F30" s="1">
+        <v>1</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="I30" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="292.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="14">
         <v>2010</v>
       </c>
       <c r="B31" s="1">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F31" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="I31" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="267" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="14">
         <v>2010</v>
       </c>
       <c r="B32" s="1">
+        <v>-6</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" s="1">
         <v>7</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="I32" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14">
+        <v>2010</v>
+      </c>
+      <c r="B33" s="1">
+        <v>-7</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="14">
         <v>2011</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14">
-        <v>2014</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>116</v>
+      <c r="D34" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="1">
+        <v>3</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>117</v>
+        <v>98</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="14">
-        <v>2015</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>125</v>
+        <v>2014</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" s="3"/>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="14">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B36" s="1">
-        <v>2</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>88</v>
+        <v>-3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="14">
         <v>2015</v>
       </c>
-      <c r="B37" s="1">
-        <v>3</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>120</v>
+      <c r="D37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="128.25" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="14">
         <v>2015</v>
       </c>
       <c r="B38" s="1">
-        <v>4</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>130</v>
+        <v>-2</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>73</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="I38" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="14">
         <v>2015</v>
       </c>
       <c r="B39" s="1">
+        <v>-3</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F39" s="1">
         <v>5</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="G39" s="1" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A40" s="14">
-        <v>2019</v>
+        <v>2015</v>
+      </c>
+      <c r="B40" s="1">
+        <v>-4</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>136</v>
+        <v>113</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>140</v>
+        <v>116</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="14">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B41" s="1">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
+      </c>
+      <c r="F41" s="1">
+        <v>7</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>139</v>
+        <v>117</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A42" s="14">
         <v>2019</v>
       </c>
-      <c r="B42" s="1">
-        <v>3</v>
-      </c>
       <c r="D42" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>142</v>
+        <v>119</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="14">
-        <v>2026</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+        <v>2019</v>
+      </c>
+      <c r="B43" s="1">
+        <v>-2</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A44" s="14">
-        <v>2205</v>
+        <v>2019</v>
+      </c>
+      <c r="B44" s="1">
+        <v>-3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>27</v>
+        <v>124</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="F44" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="I44" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="14">
-        <v>2208</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>30</v>
+        <v>2026</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
       </c>
-      <c r="G45" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I45" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="128.25" x14ac:dyDescent="0.2">
       <c r="A46" s="14">
+        <v>2027</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" s="1">
+        <v>3</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A47" s="14">
+        <v>2027</v>
+      </c>
+      <c r="B47" s="1">
+        <v>-4</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F47" s="1">
+        <v>5</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" s="14">
+        <v>2027</v>
+      </c>
+      <c r="B48" s="1">
+        <v>-6</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A49" s="14">
+        <v>2040</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F49" s="1">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" s="14">
+        <v>2041</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="3"/>
+      <c r="I50" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" s="14">
+        <v>2047</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="3"/>
+      <c r="I51" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" s="14">
+        <v>2081</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3"/>
+      <c r="I52" s="16" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A53" s="14">
+        <v>2100</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F53" s="1">
+        <v>3</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" s="14">
+        <v>2140</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F54" s="1">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I54" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A55" s="14">
+        <v>2154</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F55" s="1">
+        <v>3</v>
+      </c>
+      <c r="H55" s="3"/>
+      <c r="I55" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" s="14">
+        <v>2198</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E56" s="7"/>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I56" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A57" s="14">
+        <v>2201</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57" s="1">
+        <v>1</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I57" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+      <c r="A58" s="14">
+        <v>2204</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E58" s="7"/>
+      <c r="F58" s="1">
+        <v>1</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I58" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" s="14">
+        <v>2205</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E59" s="7"/>
+      <c r="F59" s="1">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I59" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" s="14">
+        <v>2205</v>
+      </c>
+      <c r="B60" s="1">
+        <v>-1</v>
+      </c>
+      <c r="C60" s="15">
+        <v>-15</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="E60" s="7"/>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="67.5" x14ac:dyDescent="0.2">
+      <c r="A61" s="14">
+        <v>2205</v>
+      </c>
+      <c r="B61" s="1">
+        <v>-2</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E61" s="7"/>
+      <c r="F61" s="1">
+        <v>3</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I61" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="54" x14ac:dyDescent="0.2">
+      <c r="A62" s="14">
+        <v>2205</v>
+      </c>
+      <c r="B62" s="1">
+        <v>-5</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="7"/>
+      <c r="F62" s="1">
+        <v>5</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I62" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="199.5" x14ac:dyDescent="0.2">
+      <c r="A63" s="14">
+        <v>2205</v>
+      </c>
+      <c r="B63" s="1">
+        <v>-6</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="1">
+        <v>7</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I63" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A64" s="14">
+        <v>2205</v>
+      </c>
+      <c r="B64" s="1">
+        <v>-7</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F64" s="1">
+        <v>3</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I64" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+      <c r="A65" s="14">
+        <v>2205</v>
+      </c>
+      <c r="B65" s="1">
+        <v>-8</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F65" s="1">
+        <v>5</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="I65" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="14">
+        <v>2206</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F66" s="1">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="I66" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+      <c r="A67" s="11">
+        <v>2208</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2">
+        <v>7</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I67" s="13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A68" s="14">
+        <v>2208</v>
+      </c>
+      <c r="B68" s="1">
+        <v>11</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F68" s="1">
+        <v>5</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I68" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" s="14">
+        <v>2209</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I69" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+      <c r="A70" s="14">
+        <v>2214</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I70" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A71" s="14">
+        <v>2220</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F71" s="1">
+        <v>1</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I71" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A72" s="14">
+        <v>2221</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A73" s="14">
+        <v>2240</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F73" s="1">
+        <v>3</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I73" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A74" s="14">
+        <v>2246</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="I74" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A75" s="14">
+        <v>2265</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E75" s="7"/>
+      <c r="F75" s="1">
+        <v>3</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I75" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A76" s="14">
+        <v>2266</v>
+      </c>
+      <c r="B76" s="1">
+        <v>-12</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" s="7"/>
+      <c r="F76" s="1">
+        <v>1</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="I76" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+      <c r="A77" s="14">
+        <v>2269</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I77" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A78" s="14">
         <v>2270</v>
       </c>
-      <c r="B46" s="1">
+      <c r="D78" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E78" s="7"/>
+      <c r="F78" s="1">
+        <v>3</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="I78" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A79" s="14">
+        <v>2270</v>
+      </c>
+      <c r="B79" s="1">
+        <v>-6</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I79" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A80" s="14">
+        <v>2270</v>
+      </c>
+      <c r="B80" s="1">
+        <v>-8</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="F80" s="1">
+        <v>3</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I80" s="16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A81" s="14">
+        <v>2270</v>
+      </c>
+      <c r="B81" s="1">
         <v>11</v>
       </c>
-      <c r="C46" s="15">
+      <c r="D81" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E81" s="7"/>
+      <c r="F81" s="1">
+        <v>3</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I81" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F46" s="1">
+    </row>
+    <row r="82" spans="1:9" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="17">
+        <v>2270</v>
+      </c>
+      <c r="B82" s="4">
+        <v>11</v>
+      </c>
+      <c r="C82" s="18">
+        <v>-15</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4">
+        <v>7</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I82" s="19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A83" s="11">
+        <v>2270</v>
+      </c>
+      <c r="B83" s="2">
+        <v>11</v>
+      </c>
+      <c r="C83" s="12">
+        <v>28</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2">
+        <v>6</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A84" s="14">
+        <v>2270</v>
+      </c>
+      <c r="B84" s="1">
+        <v>12</v>
+      </c>
+      <c r="C84" s="15">
+        <v>2</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F84" s="1">
         <v>0</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I46" s="16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="14">
+      <c r="H84" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="I84" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A85" s="14">
+        <v>2270</v>
+      </c>
+      <c r="B85" s="1">
+        <v>12</v>
+      </c>
+      <c r="C85" s="15">
+        <v>24</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F85" s="1">
+        <v>0</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="I85" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A86" s="14">
+        <v>2271</v>
+      </c>
+      <c r="B86" s="1">
+        <v>1</v>
+      </c>
+      <c r="C86" s="15">
+        <v>5</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I86" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+      <c r="A87" s="14">
+        <v>2271</v>
+      </c>
+      <c r="B87" s="1">
+        <v>1</v>
+      </c>
+      <c r="C87" s="15">
+        <v>8</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F87" s="1">
+        <v>5</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I87" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A88" s="14">
+        <v>2271</v>
+      </c>
+      <c r="B88" s="1">
+        <v>7</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F88" s="1">
+        <v>3</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I88" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A89" s="14">
+        <v>2271</v>
+      </c>
+      <c r="B89" s="1">
+        <v>8</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="I89" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" s="14">
+        <v>2271</v>
+      </c>
+      <c r="B90" s="1">
+        <v>10</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="F90" s="1">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I90" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A91" s="14">
+        <v>2272</v>
+      </c>
+      <c r="B91" s="1">
+        <v>1</v>
+      </c>
+      <c r="C91" s="15">
+        <v>5</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I91" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="17">
+        <v>2272</v>
+      </c>
+      <c r="B92" s="4">
+        <v>1</v>
+      </c>
+      <c r="C92" s="18">
+        <v>11</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F92" s="4">
+        <v>5</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="I92" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A93" s="14">
+        <v>2272</v>
+      </c>
+      <c r="B93" s="1">
+        <v>5</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="F93" s="1">
+        <v>0</v>
+      </c>
+      <c r="I93" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A94" s="14">
+        <v>2273</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="F94" s="1">
+        <v>3</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="I94" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A95" s="14">
         <v>2274</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F47" s="1">
+      <c r="D95" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F95" s="1">
         <v>0</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I47" s="16" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="14">
+      <c r="G95" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I95" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" s="14">
+        <v>2274</v>
+      </c>
+      <c r="B96" s="1">
+        <v>10</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F96" s="1">
+        <v>5</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="I96" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A97" s="14">
+        <v>2279</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F97" s="1">
+        <v>1</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="I97" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A98" s="14">
+        <v>2279</v>
+      </c>
+      <c r="B98" s="1">
+        <v>-6</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F98" s="1">
+        <v>7</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="I98" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A99" s="14">
+        <v>2280</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F99" s="1">
+        <v>3</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I99" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="14">
+        <v>2280</v>
+      </c>
+      <c r="B100" s="1">
+        <v>-6</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F100" s="1">
+        <v>5</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I100" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A101" s="11">
+        <v>2333</v>
+      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2">
+        <v>0</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I101" s="13" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A102" s="14">
+        <v>2337</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F102" s="1">
+        <v>3</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I102" s="16" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A103" s="14">
+        <v>2339</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F103" s="1">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I103" s="16" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A104" s="14">
+        <v>2343</v>
+      </c>
+      <c r="B104" s="1">
+        <v>5</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F104" s="1">
+        <v>5</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I104" s="16" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A105" s="14">
+        <v>2343</v>
+      </c>
+      <c r="B105" s="1">
+        <v>5</v>
+      </c>
+      <c r="C105" s="15">
+        <v>19</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F105" s="1">
+        <v>3</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="I105" s="16" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A106" s="14">
+        <v>2378</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F106" s="1">
+        <v>3</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I106" s="16" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A107" s="14">
+        <v>2390</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I107" s="16" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A108" s="14">
+        <v>2397</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F108" s="1">
+        <v>1</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I108" s="16" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+      <c r="A109" s="14">
+        <v>2399</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="F109" s="1">
+        <v>3</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="I109" s="16" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A110" s="14">
         <v>2400</v>
       </c>
-      <c r="D48" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F48" s="1">
+      <c r="D110" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F110" s="1">
         <v>1</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I48" s="16" t="s">
-        <v>44</v>
+      <c r="G110" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I110" s="16" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="142.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="17">
+        <v>2400</v>
+      </c>
+      <c r="B111" s="4">
+        <v>5</v>
+      </c>
+      <c r="C111" s="18">
+        <v>19</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4">
+        <v>7</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="I111" s="19" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A112" s="14">
+        <v>2400</v>
+      </c>
+      <c r="B112" s="1">
+        <v>-10</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="F112" s="1">
+        <v>0</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I112" s="16" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A113" s="14">
+        <v>2500</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F113" s="1">
+        <v>0</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="I113" s="16" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A114" s="14">
+        <v>2687</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F114" s="1">
+        <v>5</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="I114" s="16" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A115" s="14">
+        <v>2687</v>
+      </c>
+      <c r="B115" s="1">
+        <v>-2</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F115" s="1">
+        <v>3</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I115" s="16" t="s">
+        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/CSV/Timelines.xlsx
+++ b/CSV/Timelines.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1Data\1study\WebLearn\Timeline\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A1A23E-60E5-403D-A99E-4132D252C3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83274988-319D-40B1-9C0B-082DF2E203A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21705" activeTab="1" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
   </bookViews>
   <sheets>
     <sheet name="ThreeBody" sheetId="1" r:id="rId1"/>
+    <sheet name="Physics" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="398">
   <si>
     <t>Year</t>
   </si>
@@ -1460,6 +1461,249 @@
   </si>
   <si>
     <t>程心接手执剑人，水滴进攻，威慑终结</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>赫兹实验证实了电磁波的存在</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>赫兹发现电磁波</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>伦琴（Wilhelm Konrad Rontgen）发现了X射线。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>伦琴发现了X射线</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>伦琴发现X射线</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>贝克勒尔发现了铀元素的放射现象</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>贝克勒尔发现放射</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>贝克勒尔发现放射现象</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>J.J.汤姆逊（Joseph John Thomsom）在研究了阴极射线后认为它是一种带负电的粒子流。电子被发现。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>J.J.汤姆逊发现电子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>J.J.汤姆逊通过研究阴极射线发现电子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢瑟福（Ernest Rutherford）发现了元素的嬗变现象。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢瑟福发现元素的嬗变现象</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>卢瑟福发现嬗变</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>在赫兹观察电磁波产生的电火花的时候，发现了一个奇怪的现象：当没有光照射到接收器的时候，接收器的电火花所能跨越的最大距离一下子就缩小了。换句话说，没有光照时，两个小球必须靠得更近才能产生火花。假如我们重新让光（特别是高频光）照射接收器，则电火花的出现又变得容易起来。赫兹对此百思不得其解，他自己也不知道，他已经亲手触摸到了“量子”这个还在沉睡的幽灵，虽然还没能将其唤醒，却已经给刚刚到达繁盛的电磁场论安排了一个可怕的诅咒。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迈克尔逊-莫雷实验失败，没有证明以太的存在</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迈克尔逊-莫雷实验失败，没有证明以太的存在，几乎可以说是否定了牛顿的绝对空间论。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理学的两朵乌云</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>开尔文在演讲中提出“物理学的两朵乌云”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>实验证明以太失败</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>迈克尔逊-莫雷实验证明以太失败</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>开尔文在演讲《在热和光动力理论上空的19世纪乌云》的第一段说：
+“动力学理论断言，热和光都是运动的方式。但现在这一理论的优美性和明晰性却被两朵乌云遮蔽，显得黯然失色了······”（The beauty and clearness of the dynamical theory, which asserts heat and light to be modes of motion, is at present obscured by two clouds...）
+第一朵乌云最终导致了相对论革命的爆发。
+第二朵乌云最终导致了量子论革命的爆发。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>贝克勒尔（Antoine Herni Becquerel）意外发现了铀元素的放射现象。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普朗克黑体公式</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普朗克无意中凑出黑体公式</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1900年10月19日，普朗克用纯数学的方法侥幸拼凑出了普朗克黑体公式。
+普朗克经过紧张的几个星期的工作，发现了一个完全意想不到的情况：如果要使这个方程成立，就必须做一个假定：
+假定能量在发射和吸收的时候，不是连续不断的，而是分成一份一份的。
+正是这个假定，推翻了自牛顿以来200多年，曾被认为是坚不可摧的经典世界。
+普朗克发现，能量的传输也必须遵照这种货币式的方法，一次至少要传输一个确定的量，不可以无限细分。能量的传输，必须有一个最小的基本单位，能量只能以这个单位一份份地发出，而不能出现一半或四分之一这种情况。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>量子的诞辰</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普朗克发布了论文《黑体光谱中的能量分布》，其中描述了自己的发现。他将能量的最小单位称为“能量子”（Energieelement），随后又改称其为“量子”（Elementarquantum）。一切的能量传输，都只能以这个量为基本单位，只能传输任意整数个量子。
+最小的能量单位：E=h·ν，ν是频率，h是普朗克常数。
+一场前所未有的革命已经到来，一场最为反叛和彻底的革命，也是最具有传奇和史诗色彩的革命。一切都是从这个叫作马克斯·普朗克的男人那里开始的。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>普朗克发布了论文，提出“量子”</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1905年3月17日，爱因斯坦写出了一篇关于辐射的论文“关于光的产生和转化的一个启发性观点”(A Heuristic Interpretation of the Rediation and Transformation of Light)。
+他通过E=h·ν发现，提高频率，正是提高单个量子的能量，而更高能量的量子，正好能够打击出更高能量的电子。提高光强，只是增加量子的数量罢了所以相应的结果自然是打击出更多电子。一切突然显得顺理成章起来。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>光量子被提出</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>狭义相对论</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱因斯坦发布论文，提出狭义相对论</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱因斯坦发布题为《论运动物体的电动力学》论文，提出狭义相对论。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>质能方程</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱因斯坦提出质能方程E=mc²</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱因斯坦提出光量子，解释光电效应</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>康普顿效应</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>康普顿效应发现，证明光是量子现象</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1923年，康普顿在研究X射线被自由电子散射的时候，发现散射出来的X射线分为两个部分，一部分和入射射线波长相同，另一部分波长更长。只有用光量子假设，才可以对此现象进行完美解释。
+第三次波战争全面爆发。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>光的双缝干涉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1807年，托马斯·杨出版了《自然哲学讲义》，其中描述了光的双缝干涉实验。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1690年，惠更斯出版《光论》(Traite de la Lumiere)，标志光的波动说达到一个兴盛的顶点。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>惠更斯出版《光论》，支持光的波动说</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>惠更斯《光论》</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1704年，牛顿出版《光学》(Opticks)，从粒子角度解释光的种种现象。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛顿出版《光学》，从粒子角度解释光</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>牛顿《光学》</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>托马斯·杨通过光的双缝干涉证明光的波动性</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1819年，菲涅尔论文使用光的波动观点解释了光的衍射问题，泊松发现与其理论一致的圆盘衍射亮斑。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>菲涅尔与泊松亮斑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>菲涅尔使用波动观点预测泊松亮斑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1850年5月6日，傅科测出光在水中的传播速度小于真空中的速度，宣判了光的粒子说的死刑。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>光粒子说的死刑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>光在水中速度小于真空，宣判光粒子说的死刑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1861年，麦克斯韦在《论物理力线》中预言光其实只是电磁波的一种。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦克斯韦在预言光只是电磁波的一种</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>光为电磁波的预言</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2230,7 +2474,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2292,6 +2536,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5145,4 +5407,386 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EFCE5F-2013-44CD-9DFE-6E90EE4F7B11}">
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.75" style="14" customWidth="1"/>
+    <col min="2" max="2" width="4.25" style="26" customWidth="1"/>
+    <col min="3" max="3" width="3.625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="16" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="56.125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="25" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="14">
+        <v>1690</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="H2" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="I2" s="26"/>
+    </row>
+    <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="14">
+        <v>1704</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>385</v>
+      </c>
+      <c r="I3" s="26"/>
+    </row>
+    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="14">
+        <v>1807</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>380</v>
+      </c>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="H4" s="26" t="s">
+        <v>381</v>
+      </c>
+      <c r="I4" s="26"/>
+    </row>
+    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>1819</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="H5" s="26" t="s">
+        <v>389</v>
+      </c>
+      <c r="I5" s="26"/>
+    </row>
+    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="14">
+        <v>1850</v>
+      </c>
+      <c r="B6" s="26">
+        <v>5</v>
+      </c>
+      <c r="C6" s="15">
+        <v>6</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="I6" s="26"/>
+    </row>
+    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="14">
+        <v>1861</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26" t="s">
+        <v>396</v>
+      </c>
+      <c r="H7" s="26" t="s">
+        <v>395</v>
+      </c>
+      <c r="I7" s="26"/>
+    </row>
+    <row r="8" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="14">
+        <v>1886</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>359</v>
+      </c>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="H8" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="I8" s="26"/>
+    </row>
+    <row r="9" spans="1:9" ht="114" x14ac:dyDescent="0.2">
+      <c r="A9" s="14">
+        <v>1887</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="14">
+        <v>1895</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="14">
+        <v>1896</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="14">
+        <v>1897</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="14">
+        <v>1899</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="114" x14ac:dyDescent="0.2">
+      <c r="A14" s="14">
+        <v>1900</v>
+      </c>
+      <c r="B14" s="26">
+        <v>4</v>
+      </c>
+      <c r="C14" s="15">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="171" x14ac:dyDescent="0.2">
+      <c r="A15" s="14">
+        <v>1900</v>
+      </c>
+      <c r="B15" s="26">
+        <v>10</v>
+      </c>
+      <c r="C15" s="15">
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="114" x14ac:dyDescent="0.2">
+      <c r="A16" s="14">
+        <v>1900</v>
+      </c>
+      <c r="B16" s="26">
+        <v>12</v>
+      </c>
+      <c r="C16" s="15">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="14">
+        <v>1905</v>
+      </c>
+      <c r="B17" s="26">
+        <v>3</v>
+      </c>
+      <c r="C17" s="15">
+        <v>17</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="14">
+        <v>1905</v>
+      </c>
+      <c r="B18" s="26">
+        <v>6</v>
+      </c>
+      <c r="C18" s="15">
+        <v>30</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="14">
+        <v>1905</v>
+      </c>
+      <c r="B19" s="26">
+        <v>9</v>
+      </c>
+      <c r="C19" s="15">
+        <v>27</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="57" x14ac:dyDescent="0.2">
+      <c r="A20" s="14">
+        <v>1923</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CSV/Timelines.xlsx
+++ b/CSV/Timelines.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1Data\1study\WebLearn\Timeline\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83274988-319D-40B1-9C0B-082DF2E203A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B30100-3EF9-4C6F-844E-7C37D6E4866A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21705" activeTab="1" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="425">
   <si>
     <t>Year</t>
   </si>
@@ -1189,10 +1189,6 @@
   <si>
     <t>林格-斐兹罗观测站在三体恒星残骸处和三体第二舰队进入光速的位置，发现了“肥皂泡”，得知曲率驱动飞船在进入光速的加速阶段会留下航迹。曲率驱动的研究被完全禁止。
 两天后，关于曲率驱动航迹的警告被误传，人们以为是打击警告，产生动乱，死亡1万多人。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心冬眠</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -1704,6 +1700,122 @@
   </si>
   <si>
     <t>光为电磁波的预言</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一届索尔维会议</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一届索尔维会议在比利时布鲁塞尔召开。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>第一届索尔维会议在布鲁塞尔召开</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴尔末公式</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴尔末发现氢原子光谱线的规律，总结出了巴尔末公式。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>巴尔末发现氢原子光谱线的规律</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>玻尔在汉森（Hans Marius Hansen）的提示下关注了原子的光谱问题，结果在描述原子光谱问题的巴尔末公式中，玻尔取得了量子论决定性的突破。
+巴尔末公式里的n只能是整数，这正是量子化的表述。玻尔做出了推断：电子的能级不是连续而任意的，而是有一定条件。量子化理论必须成为原子理论的主宰。
+1913年3月-9月，三篇题为“论原子和分子的构造”、“单原子核体系”和“多原子核体系”被发表。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>玻尔提出电子能级不连续</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>电子能级不连续</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>。1922年，奥托·斯特恩（Otto Stern）和沃尔特·盖拉赫（Walther Gerlach）进行了斯特恩-盖拉赫实验，证明电子在空间中的运动方向也是不连续的。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>斯特恩-盖拉赫实验证明电子运动方向也不连续</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>电子运动方向不连续</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>电子运动不连续</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>对于拥有众多电子的重元素来说，为什么它的一些电子能够长期地占据外层电子轨道，而不会失去能量落到低层轨道上去？
+1925年，年轻的泡利对此做出了解答：没有两个电子可以享有同样的状态，而一层轨道能够包容的不同状态数目是有限的。也就是说，一个轨道有一定的容量。当电子填满了一个轨道后，其它电子便无法加入到这个轨道中。这就是“不相容原理”（The Exclusion Principle）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>泡利不相容原理</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>泡利不相容原理解释稳定的最外层电子</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1927年，戴维逊和革末通过实验精确地证明了电子的波动性。同年，G.P.汤姆逊进一步证明了电子的波动性。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>电子波动性被证实</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1923年，德布罗意发现，电子在前进的时候，本身总是伴随一个波，并将此作为博士论文提交。在博士答辩中，他做出预言，电子在通过一个小孔或晶体的时候，会出现一个可观测的衍射现象。
+这是颁发过的含金量最高的学位之一。德布罗意是有史以来第一个仅凭借博士论文就直接获取诺贝尔奖的例子。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>德布罗意波</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>德布罗意发现电子在前进时会伴随一个波</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1925年4月27日，海森堡回到哥廷根。他认为，物理学应该有坚固的基础，只能从一些直接可以被实验观察和检验的东西出发。对于原子光谱能级的问题，我们观测不到能量，只能观测到能量差，因此一切理论应该从能量差中出发进行研究。他基于此，建立起了新的量子力学——矩阵式。（海森堡对“矩阵”这个东西毫不知情，他实际上不知不觉地重新发明了矩阵这个东西。）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>海森堡矩阵力学</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>海森堡基于能量差提出矩阵力学</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>电子自旋被证明</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1925年秋天，电子自旋被证明。电子的自旋并不能被相像成传统行星的那种自旋，它具有1/2的量子数，也就是说，它要转两圈才露出同一个面孔，这里面的意义只能由数学来把握。</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心交出星环 冬眠</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>观测到187J3X1摧毁</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -2474,7 +2586,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2538,23 +2650,17 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2915,9 +3021,9 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.75" style="14" customWidth="1"/>
-    <col min="2" max="2" width="3.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="4" style="15" customWidth="1"/>
-    <col min="4" max="4" width="15.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="3.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="33.125" style="1" customWidth="1"/>
@@ -3215,7 +3321,7 @@
         <v>7</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>55</v>
@@ -3926,7 +4032,7 @@
         <v>140</v>
       </c>
       <c r="F47" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>142</v>
@@ -4113,14 +4219,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="27" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="14">
         <v>2204</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E58" s="7"/>
+      <c r="E58" s="7" t="s">
+        <v>424</v>
+      </c>
       <c r="F58" s="1">
         <v>1</v>
       </c>
@@ -4568,16 +4676,16 @@
         <v>-6</v>
       </c>
       <c r="D79" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="F79" s="1">
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>225</v>
@@ -4594,16 +4702,16 @@
         <v>-8</v>
       </c>
       <c r="D80" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E80" s="7" t="s">
         <v>332</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>333</v>
       </c>
       <c r="F80" s="1">
         <v>3</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>222</v>
@@ -4644,14 +4752,14 @@
         <v>-15</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4">
         <v>7</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>234</v>
@@ -5060,13 +5168,13 @@
         <v>-6</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>277</v>
+        <v>423</v>
       </c>
       <c r="F100" s="1">
         <v>5</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>275</v>
@@ -5082,20 +5190,20 @@
       <c r="B101" s="2"/>
       <c r="C101" s="12"/>
       <c r="D101" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" s="2">
         <v>0</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H101" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I101" s="13" t="s">
         <v>279</v>
-      </c>
-      <c r="I101" s="13" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
@@ -5103,19 +5211,19 @@
         <v>2337</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="E102" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="F102" s="1">
         <v>3</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I102" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
@@ -5123,19 +5231,19 @@
         <v>2339</v>
       </c>
       <c r="D103" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E103" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E103" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="F103" s="1">
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I103" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
@@ -5146,22 +5254,22 @@
         <v>5</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>290</v>
       </c>
       <c r="F104" s="1">
         <v>5</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I104" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
@@ -5175,19 +5283,19 @@
         <v>19</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F105" s="1">
         <v>3</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I105" s="16" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
@@ -5195,22 +5303,22 @@
         <v>2378</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="F106" s="1">
         <v>3</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I106" s="16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
@@ -5218,19 +5326,19 @@
         <v>2390</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I107" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
@@ -5238,19 +5346,19 @@
         <v>2397</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I108" s="16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="57" x14ac:dyDescent="0.2">
@@ -5258,19 +5366,19 @@
         <v>2399</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F109" s="1">
         <v>3</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I109" s="16" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
@@ -5278,19 +5386,19 @@
         <v>2400</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I110" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="142.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -5311,13 +5419,13 @@
         <v>7</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I111" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
@@ -5328,16 +5436,16 @@
         <v>-10</v>
       </c>
       <c r="D112" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F112" s="1">
+        <v>0</v>
+      </c>
+      <c r="H112" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="F112" s="1">
-        <v>0</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="I112" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
@@ -5345,19 +5453,19 @@
         <v>2500</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I113" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
@@ -5365,19 +5473,19 @@
         <v>2687</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F114" s="1">
         <v>5</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I114" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
@@ -5388,19 +5496,19 @@
         <v>-2</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F115" s="1">
         <v>3</v>
       </c>
       <c r="G115" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I115" s="16" t="s">
         <v>327</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="I115" s="16" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -5411,11 +5519,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EFCE5F-2013-44CD-9DFE-6E90EE4F7B11}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.75" style="14" customWidth="1"/>
-    <col min="2" max="2" width="4.25" style="26" customWidth="1"/>
+    <col min="2" max="2" width="4.25" style="1" customWidth="1"/>
     <col min="3" max="3" width="3.625" style="15" customWidth="1"/>
     <col min="4" max="4" width="16" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
@@ -5425,7 +5533,7 @@
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="25" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -5458,331 +5566,536 @@
       <c r="A2" s="14">
         <v>1690</v>
       </c>
-      <c r="D2" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26" t="s">
+      <c r="D2" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="H2" s="26" t="s">
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="I2" s="26"/>
+      <c r="H2" s="1" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>1704</v>
       </c>
-      <c r="D3" s="26" t="s">
-        <v>387</v>
-      </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26" t="s">
+      <c r="D3" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="I3" s="26"/>
+      <c r="H3" s="1" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>1807</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F4" s="1">
+        <v>3</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26" t="s">
-        <v>388</v>
-      </c>
-      <c r="H4" s="26" t="s">
-        <v>381</v>
-      </c>
-      <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="14">
         <v>1819</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26" t="s">
-        <v>391</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>389</v>
-      </c>
-      <c r="I5" s="26"/>
+      <c r="H5" s="1" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="14">
         <v>1850</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="15">
         <v>6</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26" t="s">
-        <v>394</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="I6" s="26"/>
+      <c r="H6" s="1" t="s">
+        <v>391</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="14">
         <v>1861</v>
       </c>
-      <c r="D7" s="26" t="s">
-        <v>397</v>
-      </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26" t="s">
+      <c r="D7" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="F7" s="1">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="I7" s="26"/>
-    </row>
-    <row r="8" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="H7" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="14">
+        <v>1885</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="14">
         <v>1886</v>
       </c>
-      <c r="D8" s="26" t="s">
-        <v>360</v>
-      </c>
-      <c r="E8" s="26" t="s">
+      <c r="D9" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="26" t="s">
+      <c r="E9" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="H8" s="26" t="s">
-        <v>356</v>
-      </c>
-      <c r="I8" s="26"/>
-    </row>
-    <row r="9" spans="1:9" ht="114" x14ac:dyDescent="0.2">
-      <c r="A9" s="14">
+    </row>
+    <row r="10" spans="1:9" ht="114" x14ac:dyDescent="0.2">
+      <c r="A10" s="14">
         <v>1887</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="14">
+        <v>1895</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
-        <v>1895</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="14">
-        <v>1896</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="14">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="14">
+        <v>1897</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="14">
         <v>1899</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D14" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="114" x14ac:dyDescent="0.2">
-      <c r="A14" s="14">
-        <v>1900</v>
-      </c>
-      <c r="B14" s="26">
-        <v>4</v>
-      </c>
-      <c r="C14" s="15">
-        <v>27</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>358</v>
+      <c r="F14" s="1">
+        <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="171" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="114" x14ac:dyDescent="0.2">
       <c r="A15" s="14">
         <v>1900</v>
       </c>
-      <c r="B15" s="26">
-        <v>10</v>
+      <c r="B15" s="1">
+        <v>4</v>
       </c>
       <c r="C15" s="15">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>363</v>
+        <v>356</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>357</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="114" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="171" x14ac:dyDescent="0.2">
       <c r="A16" s="14">
         <v>1900</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="1">
+        <v>10</v>
+      </c>
+      <c r="C16" s="15">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="114" x14ac:dyDescent="0.2">
+      <c r="A17" s="14">
+        <v>1900</v>
+      </c>
+      <c r="B17" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C17" s="15">
         <v>14</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F17" s="1">
+        <v>7</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="14">
-        <v>1905</v>
-      </c>
-      <c r="B17" s="26">
-        <v>3</v>
-      </c>
-      <c r="C17" s="15">
-        <v>17</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:8" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A18" s="14">
         <v>1905</v>
       </c>
-      <c r="B18" s="26">
-        <v>6</v>
+      <c r="B18" s="1">
+        <v>3</v>
       </c>
       <c r="C18" s="15">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>371</v>
+        <v>369</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="14">
         <v>1905</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="1">
+        <v>6</v>
+      </c>
+      <c r="C19" s="15">
+        <v>30</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="F19" s="1">
+        <v>7</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="14">
+        <v>1905</v>
+      </c>
+      <c r="B20" s="1">
         <v>9</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C20" s="15">
         <v>27</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D20" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="57" x14ac:dyDescent="0.2">
-      <c r="A20" s="14">
+    </row>
+    <row r="21" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="14">
+        <v>1911</v>
+      </c>
+      <c r="B21" s="1">
+        <v>10</v>
+      </c>
+      <c r="C21" s="15">
+        <v>30</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F21" s="1">
+        <v>3</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="114" x14ac:dyDescent="0.2">
+      <c r="A22" s="14">
+        <v>1913</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A23" s="14">
+        <v>1922</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="57" x14ac:dyDescent="0.2">
+      <c r="A24" s="14">
         <v>1923</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D24" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>379</v>
+    </row>
+    <row r="25" spans="1:8" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="14">
+        <v>1923</v>
+      </c>
+      <c r="B25" s="1">
+        <v>-6</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A26" s="14">
+        <v>1925</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="14">
+        <v>1925</v>
+      </c>
+      <c r="B27" s="1">
+        <v>4</v>
+      </c>
+      <c r="C27" s="15">
+        <v>27</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A28" s="14">
+        <v>1925</v>
+      </c>
+      <c r="B28" s="1">
+        <v>-9</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="14">
+        <v>1927</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>413</v>
       </c>
     </row>
   </sheetData>

--- a/CSV/Timelines.xlsx
+++ b/CSV/Timelines.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1Data\1study\WebLearn\Timeline\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5B30100-3EF9-4C6F-844E-7C37D6E4866A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19670D99-869C-49C4-83EE-22675266AA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="21705" activeTab="1" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
+    <workbookView xWindow="5205" yWindow="2625" windowWidth="28800" windowHeight="15885" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
   </bookViews>
   <sheets>
     <sheet name="ThreeBody" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="431">
   <si>
     <t>Year</t>
   </si>
@@ -128,22 +128,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>四维空间翘曲点接触地球</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>君士坦丁堡战役中，四维空间翘曲点与地球接触</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>四维空间翘曲点完全离开地球</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>四维空间离开地球</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>21时，四维空间翘曲点完全离开地球。</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -151,500 +135,18 @@
     <t>君士坦丁堡陷落</t>
   </si>
   <si>
-    <t>傍晚，君士坦丁堡陷落。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶泰哲死亡</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶泰哲在批斗会上被打死，留下了崩溃的妻子绍琳和女儿叶文洁。
-这是叶文洁人生的转折点。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁读了《寂静的春天》，有了一个想法：人类真正的道德自觉是不可能的，就像他们不可能拔着自己的头发离开大地。
-她帮白沐霖抄写了发给中央的举报信，结果被诬陷是她写的，要被判反革命罪。
-同年，红岸基地以戴罪立功为由吸收叶文洁进入。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶得知红岸秘密</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁发送信号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁得知了红岸的秘密</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1970年初夏，杨卫宁将红岸工程的真实情况（寻找地外文明）告诉叶文洁。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁使用太阳向宇宙发射信号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1971年秋，叶文洁在杂志上发现，来自木星的电磁辐射与来自太阳的日凌干扰时间差16分42秒，刚好是从木星直接到地球和木星到太阳再到地球的时间差。所以她猜想太阳的“能量镜面”可以以数亿倍放大电磁辐射。但实验被雷志成政委以政治原因否决。
-叶文洁借试发射之机，使用12000兆赫向太阳发射信号。8分钟后，地球文明向太空发出的第一声能够被听到的啼鸣，以太阳为中心，以光速飞向整个宇宙。这时，在12000兆赫波段上，太阳是银河系中最亮的一颗星。
-但由于种种原因，红岸基地电台并未收到回波。所以叶文洁并不知道发射成功。同时，由于太阳在放大电波同时还叠加了一个正弦波，来自木星的电磁辐射波形与日凌干扰的波形看起来对不上，使叶文洁认为自己猜想有误。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁与杨卫宁组成家庭</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁成家</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1971-1978年是叶文洁一生中最平静的一段时间，但也引起了她对人类恶的一面的理性思考。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体文明1379号监听站收到地球消息</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶收到三体回复</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>凌晨0点，在向太阳发射信息不到9年后，在叶文洁值夜班时，收到了来自三体世界的警告回信。
-在4个多小时中，叶文洁知道了三体世界的存在和他们星际移民的企图。
-清晨，叶文洁通过太阳向三体文明发送回信，表示希望他们来解决人类文明的问题。
-下午，雷志成也发现了三体文明的消息，但他不知道叶文洁已经回信。他威胁叶文洁对此事保密，想要成为第一个发现地外文明的人。
-叶文洁故意制造了设备故障，想在雷志成吊下悬崖去检修的时候将其杀掉。但杨卫宁也一起下去了，由于机会难得，她只得将两人一起杀死。
-叶文洁怀孕。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁收到三体回复</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体第一舰队启航</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体文明收到来自叶文洁的回信，确定地球坐标。
-三体文明元首制定杀死人类文明科学的计划：染色、神迹、智子工程。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>红岸基地停用</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体加速器建成</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体文明用于制造智子的巨型加速器建成</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体质子实验</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体文明进三次质子二维展开实验</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体文明对质子的第一次二维展开实验，失败，质子被减成一维。
-两天后，三体文明对质子的第二次二维展开实验，失败，质子只被减到三维。并且被高维中的智慧存在攻击。
-一天后，三体文明对质子的第三次二维展开实验，成功。开始在二维展开后的质子上蚀刻电路。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>智子试运行成功</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>智子第一次试运行，成功</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2、3、4号智子建成，四个智子构成的量子阵列顺利建立。四个智子维度收缩至十一维。智子1号和2号被以光速发向地球。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>智子发向地球</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>叶文洁退休</t>
   </si>
   <si>
-    <t>2个智子被以光速发向地球</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体舰队进入第一片星际尘埃云</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体舰队进入尘埃云</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体舰队进尘埃云</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁与伊文斯</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>1990年代初，叶文洁回到北京，在父亲叶泰哲曾工作过的清华大学教授天体物理学。
-半年后，叶文洁认识麦克麦克·伊文斯。
-3年后，叶文洁将三体文明的事告诉麦克·伊文斯。
-3年后，叶文洁来到第二红岸基地——“审判日”号轮船，成为地球三体运动最高统帅。地球三体运动诞生。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁与麦克·伊文斯</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>危机纪元开始</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>多位科学家自杀，危机纪元开始</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>古筝行动</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>宇宙闪烁</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>面壁计划启动</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>面壁计划启动，选定四位面壁者</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>宇宙背景辐射闪烁</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2007年X月
-11日，汪淼照的胶卷上出现倒计时，1200小时开始。无论是数码相机还是胶片相机，别人拍的都很正常，汪淼拍的都会出现倒计时。
-12日，倒计时直接显示在汪淼视网膜上，他停下了纳米项目后，倒计时停止并消失。
-14日，凌晨1点到5点，宇宙背景辐射闪烁。
-15日，晚上，汪淼在《三体》游戏中成功揭示了宇宙的基本结构。
-16日，凌晨，申玉菲被潘寒枪杀。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>中国太空军正式成立</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>中国太空军成立</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2010年，中国太空军正式成立，成立时包括章北海。之后，章北海在与父亲的交谈中，确立了人类必败的思想（基础理论决定一切）。
-特别联大通过117号决议，宣布逃亡主义为非法。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>NASA实验得出，阶梯计划的载荷只能在半公斤以下，维德提出只送大脑。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>哈勃二号装配完成。一周后，在三体行星方向上四光年处，发现三体舰队的尾迹（刷子）。约1000根，速度约100倍第三宇宙速度（1670km/s）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>阶梯计划只送大脑</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>阶梯计划维德提出只送大脑</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体舰队的尾迹</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体舰队尾迹</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体舰队在星际尘埃云的尾迹（刷子）</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>由于人类文明即将开展面壁者计划，三体文明联系面壁者2号，告知其伊文斯命令的密码，让其继续执行杀死罗辑的任务。伪造交通事故进行刺杀，被罗辑幸运躲开。对罗辑的第二次狙击刺杀被防弹衣挡下。
-面壁计划启动。第一位是弗里德里克·泰勒，前美国国防部长；第二位是曼努尔·雷迪亚兹，委内瑞拉总统；第三位是比尔·希恩斯，科学和政治的综合素质极强；第四位是罗辑，人类在三体发来的信息中发现，他是被三体文明指名要消灭的唯一一个人类；
-ETO中，破壁人一号、二号和三号（希恩斯的妻子山杉惠子）也被选出，而罗辑，由于唯一一个知道其对三体文明威胁的人类——伊文斯已经死去，所以罗辑将直接与三体文明对决。
-罗辑找世外桃源享受，让史强找到庄颜后隐居；
-泰勒：研究宏原子核聚变，建立一支以球状闪电和宏原子核聚变为主要武器的，独立于地球主力的太空力量；在寻找赴死、牺牲精神；真实战略意图为用宏原子核聚变消灭地球太空军，使他们成为量子态，让量子幽灵去抵抗三体舰队。
-雷迪亚兹：要求研究2亿吨级以上的核弹，在某次看日出时患了恐日症；真实战略意图为用核弹减速水星，使其坠入太阳，毁灭太阳系，以此威慑三体文明。
-希恩斯：借助技术加快人脑的进化；真实战略意图为其是坚定的失败主义者和逃亡主义者，以思想刚印作为研究的最终目标，唯一目标是实现人类的逃亡。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>云天明接受阶梯计划</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>云接受阶梯计划</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>第三届人大常委会特别会议通过安乐死法。联合国启动群星计划。
-肺癌晚期的云天明决定安乐死，在这之前通过群星计划买下恒星DX3906送给了程心。
-程心得知云天明时无多日，将他推荐为阶梯计划候选人。
-在云天明安乐死前最后一刻，程心赶到叫停了安乐死。云天明接受了阶梯计划这个使命。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心使云天明接受阶梯计划的使命</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>阶梯计划实施</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空电梯始建，阶梯计划实施</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>泰勒自杀</t>
   </si>
   <si>
-    <t>泰勒的破壁人出现，泰勒自杀。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>阶梯计划提出</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心提出阶梯计划并被采用</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心结束学业参加工作。很快进入行星防御理事会战略情报局（PIA）工作。她提出的阶梯计划——向三体发射达到光速百分之一的方案被采用。根据对阶梯计划的数次可行性测试，要想达到光速百分之一，探测器的质量上限一降再降，从1t到200kg，程心提出只送一个被冰冻的人。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>在不到两个月时间里，许多理论物理学家先后自杀。自杀的学者大部分与“科学边界”有过联系。
-杨冬使用粒子加速器的实验被智子干扰，实验结果一片混乱。同时从母亲叶文洁电脑中得知了三体和ETO的事，随后也自杀。
-杨冬死后，叶文洁约见杨冬的高中同学罗辑，给予研究宇宙社会学的提示。三体世界得知此事后，让伊文斯杀死罗辑，同时，伊文斯教会了三体文明隐瞒杀死罗辑的原因。伊文斯将任务加密发给了面壁者2号，但暂未告知密码。
-伊文斯在与三体文明对话时，发现了三体人思维透明这一与人类的重大差异。这是伊文斯最后一次收到来自三体文明的信息。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>空天飞机出现</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>化学动力航天器的最后一代——空天飞机出现并投入大规模使用。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体舰队进入第二片尘埃云</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体舰队进入第二片星际尘埃</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑发出咒语</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>黑暗森林法则</t>
   </si>
   <si>
-    <t>罗辑看到了宇宙的真相，称其为黑暗森林法则</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>泰勒的破壁人出现。三体人不怕量子幽灵。泰勒自杀。
-于雷迪亚兹和希恩斯的下一步研究需要更高计算力的计算机，所以都选择进入冬眠。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>PDC从罗辑身边带走了庄颜和孩子，在末日等待罗辑。
-之后，罗辑看到了宇宙的真相，称其为“黑暗森林法则”，并躲入地堡中。同时，三体向ETO第二次发出了消灭罗辑的指令，并发射10个水滴探测器以更快的速度驶向地球。
-一周后，ETO散播针对罗辑的基因导弹病毒。
-一周后，在PDC会议上，罗辑公布了自己要用太阳向宇宙中发射的咒语——187J3X1恒星的位置信息。
-罗辑感染了基因导弹，无法医治，被紧急冬眠。
-两周后，罗辑的咒语通过太阳以光速飞向宇宙。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑感染了基因导弹，无法医治，被紧急冬眠。
-两周后，罗辑的咒语通过太阳以光速飞向宇宙。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑的咒语通过太阳以光速飞向宇宙</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>技术突破</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>天梯投入使用，可控核聚变重大突破</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体舰队的第二个尾迹</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体舰队在第2片星际尘埃上的航迹被发现，同时发现了三体舰队发射水滴探测器的事实。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>天梯一号、二号、三号投入正式使用。
-可控核聚变取得重大突破。
-中国开始计划经济，分发粮票等。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>章北海暗杀老航天人</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>章北海在太空中用陨石做成的子弹伪装成陨石雨，暗杀了反对研究无工质飞船引擎的三名老航天人。促使后期研究方向定为无工质引擎。
-章北海带着常伟思的信，与特遣队一起冬眠。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>章北海暗杀反对研究无工质引擎的老航天人</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>史晓明出狱</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2007年X月
-2-3天后，史强与汪淼参加制定夺取“审判日”号上的三体信息的会议。史强提出了用汪淼制造出的叫“飞刃”的纳米丝切割船体的方案，代号“古筝行动”。
-4天后，在巴拿马运河盖拉德水道，“古筝行动”成功实施，取得约28G被降临派截留的三体信息。
-3天后，三体世界与首次与地球叛军之外的人类进行了一次交流：在作战中心所有人的视网膜上出现了5个字“你们是虫子！”。此后中断了与地球的通讯。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2007年X月
-数天后，晚上，汪淼参加《三体》网友聚会，潘寒筛选出降临派的“同志”。
-数天后，ETO在化工场举行300多人，多为拯救派的聚会。叶文洁会上令杀手杀死潘寒。会议中途军队冲入，叶文洁被抓，过程中史强处理核弹时遭受到强烈辐射，患白血病。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>叶文洁被抓</t>
   </si>
   <si>
-    <t>叶文洁在ETO聚会杀死潘寒，被抓</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空电梯始建</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空电梯天梯开始建造</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太空电梯天梯一号、二号、三号同时开始建造。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑和庄颜的孩子出生。
-阶梯计划实施。但在第997枚核弹爆炸后，一根帆索断了，球形舱偏航，人类丢失了它的信号。云天明的大脑以光速百分之一飞向太空深处。
-程心冬眠，以阶梯计划联络员的身份前往未来。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>章北海暗杀老航天</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>常伟思退役</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷迪亚兹和希恩斯被唤醒</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷和希被唤醒</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷迪亚兹被砸死</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷迪亚兹被人民用石头砸死</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>水星实验在水星并不深的地层中进行，恒星型氢弹的巨大威力给主防御的领导者们留下了深刻的印象。
-10小时后，雷迪亚兹的破壁人出现。三体文明不怕，因为人类不可能造出足够多的核弹。
-PDC会议中，雷迪亚兹谎称自己身上有反触发系统成功脱身回国。6小时后，雷迪亚兹回到了自己的国家，被自己的人民用石头砸死。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>雷迪亚兹和希恩斯被唤醒。
-希恩斯在人脑中发现了思维做出判断的机制，通过对部分神经元的某一部分施加影响，可以使大脑不经思维就做出判断，相信某个信息为真或者伪。
-雷迪亚兹制造出了人类最大的氢弹，以建造日后的水星基地为由，要求在水星的地下进行试验。
-信念中心建成，太空军可以自愿接受人类必胜的思想钢印。但希恩斯隐蔽地修改了思想钢印机器程序中的一个正负号，使对命题判断为伪（人类必败）。
-希恩斯和山杉惠子进入冬眠。山杉惠子在冬眠前最后一刻思考出了希恩斯的计划，但已经无法呼叫冬眠停止。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大低谷开始</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大低谷结束</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>人民生活水平恢复到黄金时代的水平</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>人民生活水平恢复到黄金时代的水平。一切开始飞快进步，技术障碍一个个被突破。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>世界人口从83亿降低到35亿。
-太空武装力量到了崩溃的边缘，增援特遣队对稳定局势发挥了巨大作用。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大低谷开始，人口暴降</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>史强妻子去世</t>
   </si>
   <si>
@@ -654,810 +156,16 @@
     <t>章北海女儿去世</t>
   </si>
   <si>
-    <t>大低谷</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>人类社会再次宣布进入战争状态，开始建造太空舰队。太空舰队成为独立国家。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>开始建造太空舰队</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>开始建造太空舰队，成为独立国家</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>187J3X1恒星被光粒摧毁</t>
   </si>
   <si>
-    <t>187J3X1被摧毁</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>丁仪被唤醒</t>
   </si>
   <si>
-    <t>丁仪被唤醒，在北京大学物理系任教。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体舰队在第5片星际尘埃上的航迹被发现，队形变得稀稀拉拉，一大半早就停止了加速。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体舰队的第五个尾迹</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>人类观测到187J3X1恒星被摧毁，但没人注意。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>观测到187J3X1被摧毁</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑被唤醒</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑、希恩斯和山杉惠子被唤醒，面壁计划结束</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑、希恩斯和山杉惠子被唤醒，参加面壁计划的最后一次听证会，宣布面壁计划结束。会后，山杉惠子公开自己破壁人身份，解读了希恩斯的计划。
-罗辑与史强进入城市后，潜伏了一个多世纪的针对罗辑的KILLER杀人病毒被唤醒，罗辑多次遭到暗杀，被迫到地上生活。
-史强在地上见到了儿子史晓明，两人现仅相差5岁。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>章北海逃离</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>增援未来的章北海被唤醒，为了审查钢印族，代替东方延绪成为了“自然选择”号的代理舰长。
-随后，章北海驾驶“自然选择”号，使用前进四逃离。人类舰队派了4艘战舰追击，分别为“蓝色空间”号、“企业”号、“深空”号和“终极规律”号。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>章北海被唤醒，驾驶“自然选择”号逃离</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>人类发现了187J3X1恒星被摧毁，人类意识到罗辑的咒语生效，将其视为救世主。罗辑向史强解释了宇宙的黑暗森林法则。
-罗辑恢复了面壁者身份，但太阳已经被封锁，地球不能再发射恒星级电波。
-罗辑加入雪地工程，表面上是在太阳系内制作尘埃云对水滴进行预测，实际上他对每个核弹进行精确位置排布，使其爆炸后，从远方观察，太阳将在可见光等波段闪烁，发出三体世界坐标。当然，同时地球坐标也会暴露。罗辑要以此对三体世界进行威慑。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑被视为救世主</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现187J3X1被摧毁，罗辑的咒语生效，视其为救世主</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体水滴摧毁人类舰队，封锁太阳</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>处在太阳系遥远两侧的两个星舰地球几乎同时发生了黑暗战役，其中“青铜时代”号在全舰投票中，有94%（1670人）赞成攻击。“蓝色空间”号和“青铜时代”号活了下来，开始收集其它战舰的资源。
-在“青铜时代”号加速离开一年后，“蓝色空间”号也加速离开。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>水滴到达太阳系</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体舰队在第7片星际尘埃上的航迹被发现，绝大部分战舰都进入减速状态。有一艘战舰没有减速，人类文明认为是来谈判的。
-联合舰队从木星基地起航，共2015艘恒星级战舰组成联合舰队，统一出击，拦截三体水滴探测器，由丁仪首次接触水滴探测器。在丁仪的建议下，舰队同意在考察队出发后让“量子”号和“青铜时代”号进入深水状态。
-5个小时后，“螳螂”号捕获了水滴。
-考察队接触后发现，水滴表面绝对光滑。之后，水滴启动，使用最原始的撞击方式，在30多分钟后，几乎全歼了人类舰队。只有已经提前进入深水状态的“量子”号和“青铜时代”号成功地逃脱了水滴的攻击。
-至此，人类太空舰队仅剩7艘星际战舰：“自然选择”号和追击舰“蓝色空间”号、“企业”号、“深空”号、“终极规律”号，和从水滴攻击中成功逃脱的“量子”号和“青铜时代”号。两行人沿着几乎相反的方向飞离太阳系。
-十多个小时后，水滴到达地球，封死了太阳。
-人类集体精神崩溃，逃亡主义迅速复活。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>史强被唤醒</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体水滴探测器到达太阳系。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>史强被唤醒，白血病已被治好</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星舰地球黑暗战役</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>两个星舰地球发生黑暗战役，“蓝色空间”号和“青铜时代”号活了下来</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑被视为骗子</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>雪地工程陷入停顿。
-随着时间的推移，罗辑在公众眼中的形象渐渐衰落，成为了个大骗子。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>雪地工程陷入停顿，罗辑被视为骗子</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>建立威慑</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑建立黑暗森林威慑</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>人类得知宇宙的黑暗森林状态</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>人类得知黑暗森林</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>11月初，人类得知宇宙的黑暗森林状态，对电磁发射进行严格管制。
-人类政府令“青铜时代”号和“蓝色空间”号立刻返航。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑与三体文明再次进行对决，告知三体世界自己的计划。
-三体文明接受谈判，解除对太阳的封锁，让水滴和三体舰队改变航向。并将与三体世界的谈判权给了人类政府，但由于威慑度的问题，威慑控制权马上交还给了罗辑，并称其为“执剑人”。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>青铜时代号返航</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“青铜时代”号返航。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>引力发射器减少</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>引力发射器减少到四个</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>主张彻底消灭三体世界的极端组织“地球之子”企图夺取南极大陆的引力波发射器，差点成功。
-在三体世界的压力下，地球将引力发射器减少到四个，分别位于亚洲、北美、欧洲和“万有引力”号飞船。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“青铜时代”号在前来迎接的“万有引力”号的伴随下到达地球，随后全体人员都因谋杀罪和反人类罪被逮捕。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>青铜时代号到达</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>青铜时代号到达地球，全体人员被逮捕</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>对“青铜时代”号进行审判。随后，“青铜时代”号的军官拼死向“蓝色空间”号发出了警告信息。
-“蓝色空间”号加速逃离，“万有引力”号和2个水滴立刻起航追击。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>警告蓝色空间号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“青铜时代”号军官拼死向“蓝色空间”号发送警告</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体取得云天明大脑</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体取得云的大脑</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体第一舰队截获阶梯飞行器，取得云天明大脑。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“蓝色空间”号停止加速。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝色空间停止加速</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体可光速行驶</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体文明制造出能够光速行驶的第二舰队。
-猜测人类文明将对黑暗森林威慑心态转变，很可能会选择低威慑度的执剑人，所以冒险派出第二支舰队。
-为了防止曲率引擎产生的加速痕迹出现在三体星球附近，第二舰队将在穿过第一片星际尘埃云后再进入光速。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体文明制造出能够光速行驶的第二舰队</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体舰队进入光速</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体第二舰队穿过第一片星际尘埃云，穿过后立刻进入光速。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体第二舰队穿过星际尘埃云后立刻进入光速</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“蓝色空间”号投降</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝色空间号投降</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“蓝色空间”号投降，两舰同时开始减速</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“蓝色空间”号与“万有引力”号距离15个天文单位时，“蓝色空间”号投降，两舰同时开始减速。“万有引力”号全舰开始苏醒。
-两舰开始接触四维空泡，出现异常现象。在“万有引力”号上，被看作心理问题忽略。在“蓝色空间”号上则进行研究。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>由于发现DX3906有一个与地球十分相似的类地行星，所以程心被唤醒。
-维德伪造艾AA电话，刺杀程心，失败。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>程心被唤醒</t>
   </si>
   <si>
-    <t>程心被唤醒</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心被唤醒，维德刺杀程心失败</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270年下半年，“蓝色空间”号通过四维空间翘曲点分多批向“万有引力”号飞船投放60多名陆战队员和军官。并使用小型穿梭机杀死了水滴。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心以压倒性优势当选“执剑人”。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心当选执剑人</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“万有引力”号距“蓝色空间”号仅3个天文单位。
-三体文明给与“万有引力”号随行的两个水滴发出指令，在五个月后威慑控制权移交时立刻摧毁“万有引力”号。
-与“万有引力”和“蓝色空间”同行的两个水滴进入智子盲区，与地球的实时通信中断。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“魔戒”坠入三维空间，出现了长度1亿3000万千米的线。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>威慑后</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>威慑纪元</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“万有引力”号和“蓝色空间”号退出四维碎块。并发现四维碎块本身在缩小。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现四维碎块缩小</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现四维碎块本身在缩小</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“魔戒”坠入三维空间</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>魔戒坠入三维空间</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>11月28日
-16点10分，罗辑将威慑控制权移交给程心。
-16:17:34，水滴来袭地球。同时水滴攻击“万有引力”号和“蓝色空间”号。
-半分钟后，水滴没有击中“万有引力”号和“蓝色空间”号。“万有引力”号的指挥官们发现水滴死了，“蓝色空间”号通过四维空间翘曲点推偏水滴，救了两舰。
-16:27:58，地球上所有引力波发射器被摧毁，太阳被封锁，地球的黑暗森林威慑终止。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“万有引力”号被“蓝色空间”号占领。
-21点，两舰发现三体第二舰队正在以光速驶向地球。两舰猜测地球方已发生事变，且引力波广播没有启动。
-两舰进行全民公决后，启动了引力波发射器。
-11月29日
-“蓝色空间”号将四维空间翘曲点的存在告诉“万有引力”号船员。
-派出探险队进入四维空间对四维物体“魔戒”进行探测。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>引力波发射器启动</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“万有引力”号启动了引力波发射器</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>地球观测到三体世界派出的第二支舰队，穿过第1片尘埃云。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体第二舰队</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体第二舰队穿过第1片尘埃云</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>地球观测到三体第二舰队，穿过第2片尘埃云，发现三体舰队达到了光速。
-三体舰队到达距太阳6000个天文单位处，脱离光速至光速的15%，使用常规推进器减速。
-智子命令人类一年内移民到保留地——澳大利亚和火星，全人类移民开始。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体第二舰队达到光速</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体达到光速</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>世界人口的一半，21亿人已经迁移到澳大利亚。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>21亿人迁至澳大利亚</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>21亿人至澳大利亚</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>发现三体第二舰队以光速穿过第2片尘埃云，全人类移民开始。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>堪培拉惨案发生。饥饿的移民大军与堪培拉军队发生冲突，十多天的混乱后，死亡50多万人，几千万人完全断绝了食物和饮水供应。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>堪培拉惨案</t>
-  </si>
-  <si>
-    <t>饥饿的移民大军与堪培拉军队发生冲突</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>澳大利亚人数达到34亿</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>34亿人于澳大利亚</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大移民完成。此时澳大利亚41亿6000有万人，火星基地100万人，地球治安军500万人，200万地球抵抗运动成员等。
-治安军开始打击电力系统、港口和大型运输设备。
-智子宣布，澳大利亚必须处于低技术的农业社会，禁止使用包括电力在内的任何现代技术。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大移民完成</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>去澳大利亚的大移民完成</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体文明得知了“万有引力”号启动了引力波广播，决定放弃地球。
-三体第二舰队转向，所有水滴撤离。
-人类开始从澳大利亚疏散。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体得知引力波广播启动</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>得知引力波启动</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体得知引力波广播启动，放弃地球，人类从澳大利亚疏散</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>太阳系毁灭</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>大疏散完成</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心视网膜剥离坏死，克隆培育需要5年左右，所以程心短期冬眠。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心短期冬眠</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心视网膜剥离坏死，短期冬眠</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>各大城市的伤痕完全消失</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>城市伤痕完全消失</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>10月，三体世界被光粒摧毁，发射光粒的是某个宇宙飞行器。。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体星系毁灭</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>罗辑从智子口中问出，有可能向宇宙发布避免黑暗森林打击的安全声明。
-之后，智子告诉程心，云天明要见她。
-三天后，在地日拉格朗日点，程心通过智子会见了云天明。会见中，云天明讲了三个他编的藏有海量信息的童话故事：《国王的新画师》、《饕餮海》和《深水王子》。
-联合国成立情报解读委员会（IDC），开始解读云天明的三个童话故事。
-掩体计划得到空前关注。
-云天明情报中，曲率驱动和降低光速（黑域）以达到安全声明的隐喻被解读，但针眼画师的画这个隐喻最终都未被成功解读。此隐喻的是对于太阳系这种多行星星系，将会使用二向箔进行降维黑暗森林打击。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心被唤醒，视力恢复。
-人类观测到三体世界被摧毁。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>云天明的三个童话</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>云天明对程心讲了三个藏有海量信息的童话故事</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>曲率飞船研究被禁</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>得知曲率飞船进入光速会留下航迹，曲率研究被禁</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心将自己星环公司的移交给维德，进行曲率驱动研究。条件是若在研制光速飞船过程中有可能危害人类生命，必须唤醒程心。
-程心与艾AA进入冬眠。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>林格-斐兹罗观测站在三体恒星残骸处和三体第二舰队进入光速的位置，发现了“肥皂泡”，得知曲率驱动飞船在进入光速的加速阶段会留下航迹。曲率驱动的研究被完全禁止。
-两天后，关于曲率驱动航迹的警告被误传，人们以为是打击警告，产生动乱，死亡1万多人。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心将星环公司交给维德，与艾AA进入冬眠</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑洞项目开始。使用环日加速器和木卫十三制作了一个微型黑洞。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>掩体纪元</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑洞项目开始</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用环日加速器制作了一个微型黑洞</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环集团公开宣布研制曲率飞船的计划，与联邦政府摩擦不断。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环集团公开研制曲率飞船计划</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环公开曲率计划</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑洞项目研究者高Way主动进入微型黑洞</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>高Way主动进入微型黑洞</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>高Way进入黑洞</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心命令星环集团投降</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心命令星环投降</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环集团宣布脱离太阳系联邦独立，与太阳系政府间的冲突升级。星环集团决定使用反物质子弹进行威慑。
-9日，程心在木星背面的亚洲一号太空城被唤醒。
-程心命令星环集团投降。星环集团向联邦政府投降。
-一周后，星环集团被宣布为非法，维德等人被逮捕。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>维德被执行死刑。
-程心进入冬眠，预定在打击之后唤醒。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>维德被执行死刑，程心进入冬眠</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心被唤醒，命令星环集团投降</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>维德死刑 程心冬眠</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环集团的残余力量在水星秘密基地恢复了空间曲率驱动的研究。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环集团在水星秘密基地恢复曲率引擎研究</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环集团恢复曲率引擎研究</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环恢复曲率研究</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环集团发现了曲率驱动尾迹可以降低光速，可以制作黑域，所以与联邦政府达成了合作。
-这里原文时间出入很大：程心逃亡时罗辑告诉他，韦德死后35年水星基地恢复，韦德死于掩体纪元11年，那么掩体纪元46年才开始进行研究。而后又说进行了半个世纪的研究，但是后面我们知道太阳系在掩体纪元67年就毁灭了，时间出入很大，这里只能压缩研究时间以对齐主要时间轴。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环集团发现曲率尾迹可降低光速制作黑域，与政府达成合作</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星环发现黑域制法</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>掩体纪元11年</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>掩体纪元46年</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>掩体纪元67年</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>一艘智慧飞船以接近光速的速度从奥尔特星云外侧掠过，对太阳系发射了二向箔。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>一艘智慧飞船对太阳系发射了二向箔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞船发射二向箔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三套曲率引擎制造完成。其中第一套引擎已经经过3年测试完，第二和三套进行测试。
-第一套曲率引擎被安装在星环号上。
-太阳系预警系统发现了此不明智慧飞船，并发现其向太阳系发射的东西。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>曲率引擎完成测试</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>3套曲率引擎制造完成。第1套测试完被安装在星环号上</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>位于银河系猎户旋臂的歌者发现了与三体世界交流的太阳系，也打出了二向箔。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>距太阳150个天文单位的二向箔减速至光速千分之一，人类出动飞船进行拦截。
-二向箔的封装力场完全蒸发，三维空间开始向二维跌落，逃逸速度为光速，人类文明无生还希望。
-5月19日，程心被唤醒。
-太阳系联邦政府正式向国际社会发布黑暗森林打击警报。
-程心与艾AA乘坐星环号到冥王星，运出部分文物。
-太阳系星球开始坠入二维。
-程心与艾AA被告知星环号可进行光速航行。罗辑令飞船AI进入光速飞行，程心和艾AA以光速逃离了太阳系，目标为程心的星星——287光年外的DX3906。
-太阳系毁灭。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>歌者打出了二向箔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>歌者文明发现与三体交流的太阳系，也打出了二向箔</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>二向箔打击，太阳系二维化，程心与艾AA逃跑</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>银河纪元</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>星舰文明到新世界</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2400年代，“万有引力”号和“蓝色空间”号到达新世界</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2500年代，人类新世界制造出曲率光速飞船。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>人类新文明制造出曲率光速飞船</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心和艾AA到达（程心参考系约10天）。见到等待她们的关一帆。
-发现有5艘不明宇宙飞船在DX3906的第一颗行星——“灰星”表面降落，关一帆与程心一起去探察。
-4天后，到达“灰星”，在其表面上发现了那5艘飞船留下的光速为0的航迹——死线。两人马上回返。
-4天后，云天明来到DX3906。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心到达DX3906</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心和艾AA到达DX3906，见到关一帆</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>新文明达到光速</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心坠入黑域</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心和关一帆坠入黑域</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑域纪元</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>在程心和关一帆乘坐穿梭机着陆过程中，死线扩散了（有可能因为云天明飞船的扰动），穿梭机被困，以光速绕行星运动。
-DX3906被黑域包裹。
-关一帆开始初始化神经元计算机，以控制飞船脱离光速。
-18903729地球年后，飞船脱离光速。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>掩体纪元66年</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶文洁收到三体世界的警告信息，并回复</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“蓝色空间”号杀死水滴</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>蓝色空间杀死水滴</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>“蓝色空间”号通过四维空间翘曲点杀死了水滴</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体令水滴在威慑控制权移交时摧毁“万有引力”号。</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体计划摧毁“万有引力”号</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>三体预定水滴攻击</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心接手 水滴进攻</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>程心接手执剑人，水滴进攻，威慑终结</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>赫兹实验证实了电磁波的存在</t>
@@ -1811,19 +519,1035 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>四维空间翘曲点接触地球</t>
+  </si>
+  <si>
+    <t>君士坦丁堡战役中，四维空间翘曲点与地球接触</t>
+  </si>
+  <si>
+    <t>四维空间翘曲点完全离开地球</t>
+  </si>
+  <si>
+    <t>四维空间离开地球</t>
+  </si>
+  <si>
+    <t>傍晚，君士坦丁堡陷落。</t>
+  </si>
+  <si>
+    <t>叶泰哲死亡</t>
+  </si>
+  <si>
+    <t>叶泰哲在批斗会上被打死，留下了崩溃的妻子绍琳和女儿叶文洁。_x000D_
+这是叶文洁人生的转折点。</t>
+  </si>
+  <si>
+    <t>叶文洁读了《寂静的春天》，有了一个想法：人类真正的道德自觉是不可能的，就像他们不可能拔着自己的头发离开大地。_x000D_
+她帮白沐霖抄写了发给中央的举报信，结果被诬陷是她写的，要被判反革命罪。_x000D_
+同年，红岸基地以戴罪立功为由吸收叶文洁进入。</t>
+  </si>
+  <si>
+    <t>叶文洁得知了红岸的秘密</t>
+  </si>
+  <si>
+    <t>叶得知红岸秘密</t>
+  </si>
+  <si>
+    <t>1970年初夏，杨卫宁将红岸工程的真实情况（寻找地外文明）告诉叶文洁。</t>
+  </si>
+  <si>
+    <t>叶文洁发送信号</t>
+  </si>
+  <si>
+    <t>叶文洁使用太阳向宇宙发射信号</t>
+  </si>
+  <si>
+    <t>1971年秋，叶文洁在杂志上发现，来自木星的电磁辐射与来自太阳的日凌干扰时间差16分42秒，刚好是从木星直接到地球和木星到太阳再到地球的时间差。所以她猜想太阳的“能量镜面”可以以数亿倍放大电磁辐射。但实验被雷志成政委以政治原因否决。_x000D_
+叶文洁借试发射之机，使用12000兆赫向太阳发射信号。8分钟后，地球文明向太空发出的第一声能够被听到的啼鸣，以太阳为中心，以光速飞向整个宇宙。这时，在12000兆赫波段上，太阳是银河系中最亮的一颗星。_x000D_
+但由于种种原因，红岸基地电台并未收到回波。所以叶文洁并不知道发射成功。同时，由于太阳在放大电波同时还叠加了一个正弦波，来自木星的电磁辐射波形与日凌干扰的波形看起来对不上，使叶文洁认为自己猜想有误。</t>
+  </si>
+  <si>
+    <t>叶文洁与杨卫宁组成家庭</t>
+  </si>
+  <si>
+    <t>叶文洁成家</t>
+  </si>
+  <si>
+    <t>1971-1978年是叶文洁一生中最平静的一段时间，但也引起了她对人类恶的一面的理性思考。</t>
+  </si>
+  <si>
+    <t>三体文明1379号监听站收到地球消息</t>
+  </si>
+  <si>
+    <t>叶文洁收到三体回复</t>
+  </si>
+  <si>
+    <t>叶收到三体回复</t>
+  </si>
+  <si>
+    <t>叶文洁收到三体世界的警告信息，并回复</t>
+  </si>
+  <si>
+    <t>凌晨0点，在向太阳发射信息不到9年后，在叶文洁值夜班时，收到了来自三体世界的警告回信。_x000D_
+在4个多小时中，叶文洁知道了三体世界的存在和他们星际移民的企图。_x000D_
+清晨，叶文洁通过太阳向三体文明发送回信，表示希望他们来解决人类文明的问题。_x000D_
+下午，雷志成也发现了三体文明的消息，但他不知道叶文洁已经回信。他威胁叶文洁对此事保密，想要成为第一个发现地外文明的人。_x000D_
+叶文洁故意制造了设备故障，想在雷志成吊下悬崖去检修的时候将其杀掉。但杨卫宁也一起下去了，由于机会难得，她只得将两人一起杀死。_x000D_
+叶文洁怀孕。</t>
+  </si>
+  <si>
+    <t>三体第一舰队启航</t>
+  </si>
+  <si>
+    <t>三体文明收到来自叶文洁的回信，确定地球坐标。_x000D_
+三体文明元首制定杀死人类文明科学的计划：染色、神迹、智子工程。</t>
+  </si>
+  <si>
+    <t>红岸基地停用</t>
+  </si>
+  <si>
+    <t>三体加速器建成</t>
+  </si>
+  <si>
+    <t>三体文明用于制造智子的巨型加速器建成</t>
+  </si>
+  <si>
+    <t>三体质子实验</t>
+  </si>
+  <si>
+    <t>三体文明进三次质子二维展开实验</t>
+  </si>
+  <si>
+    <t>三体文明对质子的第一次二维展开实验，失败，质子被减成一维。_x000D_
+两天后，三体文明对质子的第二次二维展开实验，失败，质子只被减到三维。并且被高维中的智慧存在攻击。_x000D_
+一天后，三体文明对质子的第三次二维展开实验，成功。开始在二维展开后的质子上蚀刻电路。</t>
+  </si>
+  <si>
+    <t>智子试运行成功</t>
+  </si>
+  <si>
+    <t>智子第一次试运行，成功</t>
+  </si>
+  <si>
+    <t>智子发向地球</t>
+  </si>
+  <si>
+    <t>2个智子被以光速发向地球</t>
+  </si>
+  <si>
+    <t>2、3、4号智子建成，四个智子构成的量子阵列顺利建立。四个智子维度收缩至十一维。智子1号和2号被以光速发向地球。</t>
+  </si>
+  <si>
+    <t>叶文洁与伊文斯</t>
+  </si>
+  <si>
+    <t>叶文洁与麦克·伊文斯</t>
+  </si>
+  <si>
+    <t>1990年代初，叶文洁回到北京，在父亲叶泰哲曾工作过的清华大学教授天体物理学。_x000D_
+半年后，叶文洁认识麦克麦克·伊文斯。_x000D_
+3年后，叶文洁将三体文明的事告诉麦克·伊文斯。_x000D_
+3年后，叶文洁来到第二红岸基地——“审判日”号轮船，成为地球三体运动最高统帅。地球三体运动诞生。</t>
+  </si>
+  <si>
+    <t>三体舰队进入尘埃云</t>
+  </si>
+  <si>
+    <t>三体舰队进尘埃云</t>
+  </si>
+  <si>
+    <t>三体舰队进入第一片星际尘埃云</t>
+  </si>
+  <si>
+    <t>危机纪元开始</t>
+  </si>
+  <si>
+    <t>多位科学家自杀，危机纪元开始</t>
+  </si>
+  <si>
+    <t>在不到两个月时间里，许多理论物理学家先后自杀。自杀的学者大部分与“科学边界”有过联系。_x000D_
+杨冬使用粒子加速器的实验被智子干扰，实验结果一片混乱。同时从母亲叶文洁电脑中得知了三体和ETO的事，随后也自杀。_x000D_
+杨冬死后，叶文洁约见杨冬的高中同学罗辑，给予研究宇宙社会学的提示。三体世界得知此事后，让伊文斯杀死罗辑，同时，伊文斯教会了三体文明隐瞒杀死罗辑的原因。伊文斯将任务加密发给了面壁者2号，但暂未告知密码。_x000D_
+伊文斯在与三体文明对话时，发现了三体人思维透明这一与人类的重大差异。这是伊文斯最后一次收到来自三体文明的信息。</t>
+  </si>
+  <si>
+    <t>阶梯计划提出</t>
+  </si>
+  <si>
+    <t>程心提出阶梯计划并被采用</t>
+  </si>
+  <si>
+    <t>程心结束学业参加工作。很快进入行星防御理事会战略情报局（PIA）工作。她提出的阶梯计划——向三体发射达到光速百分之一的方案被采用。根据对阶梯计划的数次可行性测试，要想达到光速百分之一，探测器的质量上限一降再降，从1t到200kg，程心提出只送一个被冰冻的人。</t>
+  </si>
+  <si>
+    <t>宇宙闪烁</t>
+  </si>
+  <si>
+    <t>宇宙背景辐射闪烁，汪淼视网膜出现倒计时</t>
+  </si>
+  <si>
+    <t>2007年X月_x000D_
+11日，汪淼照的胶卷上出现倒计时，1200小时开始。无论是数码相机还是胶片相机，别人拍的都很正常，汪淼拍的都会出现倒计时。_x000D_
+12日，倒计时直接显示在汪淼视网膜上，他停下了纳米项目后，倒计时停止并消失。_x000D_
+14日，凌晨1点到5点，宇宙背景辐射闪烁。_x000D_
+15日，晚上，汪淼在《三体》游戏中成功揭示了宇宙的基本结构。_x000D_
+16日，凌晨，申玉菲被潘寒枪杀。</t>
+  </si>
+  <si>
+    <t>叶文洁在ETO聚会杀死潘寒，被抓</t>
+  </si>
+  <si>
+    <t>2007年X月_x000D_
+数天后，晚上，汪淼参加《三体》网友聚会，潘寒筛选出降临派的“同志”。_x000D_
+数天后，ETO在化工场举行300多人，多为拯救派的聚会。叶文洁会上令杀手杀死潘寒。会议中途军队冲入，叶文洁被抓，过程中史强处理核弹时遭受到强烈辐射，患白血病。</t>
+  </si>
+  <si>
+    <t>古筝行动</t>
+  </si>
+  <si>
+    <t>2007年X月_x000D_
+2-3天后，史强与汪淼参加制定夺取“审判日”号上的三体信息的会议。史强提出了用汪淼制造出的叫“飞刃”的纳米丝切割船体的方案，代号“古筝行动”。_x000D_
+4天后，在巴拿马运河盖拉德水道，“古筝行动”成功实施，取得约28G被降临派截留的三体信息。_x000D_
+3天后，三体世界与首次与地球叛军之外的人类进行了一次交流：在作战中心所有人的视网膜上出现了5个字“你们是虫子！”。此后中断了与地球的通讯。</t>
+  </si>
+  <si>
+    <t>中国太空军正式成立</t>
+  </si>
+  <si>
+    <t>中国太空军成立</t>
+  </si>
+  <si>
+    <t>中国太空军成立，逃亡主义被宣布为非法</t>
+  </si>
+  <si>
+    <t>2010年，中国太空军正式成立，成立时包括章北海。之后，章北海在与父亲的交谈中，确立了人类必败的思想（基础理论决定一切）。_x000D_
+特别联大通过117号决议，宣布逃亡主义为非法。</t>
+  </si>
+  <si>
+    <t>阶梯计划只送大脑</t>
+  </si>
+  <si>
+    <t>阶梯计划维德提出只送大脑</t>
+  </si>
+  <si>
+    <t>NASA实验得出，阶梯计划的载荷只能在半公斤以下，维德提出只送大脑。</t>
+  </si>
+  <si>
+    <t>面壁计划启动</t>
+  </si>
+  <si>
+    <t>联合国启动面壁计划，选定四位面壁者对抗三体</t>
+  </si>
+  <si>
+    <t>由于人类文明即将开展面壁者计划，三体文明联系面壁者2号，告知其伊文斯命令的密码，让其继续执行杀死罗辑的任务。伪造交通事故进行刺杀，被罗辑幸运躲开。对罗辑的第二次狙击刺杀被防弹衣挡下。_x000D_
+面壁计划启动。第一位是弗里德里克·泰勒，前美国国防部长；第二位是曼努尔·雷迪亚兹，委内瑞拉总统；第三位是比尔·希恩斯，科学和政治的综合素质极强；第四位是罗辑，人类在三体发来的信息中发现，他是被三体文明指名要消灭的唯一一个人类；_x000D_
+ETO中，破壁人一号、二号和三号（希恩斯的妻子山杉惠子）也被选出，而罗辑，由于唯一一个知道其对三体文明威胁的人类——伊文斯已经死去，所以罗辑将直接与三体文明对决。_x000D_
+罗辑找世外桃源享受，让史强找到庄颜后隐居；_x000D_
+泰勒：研究宏原子核聚变，建立一支以球状闪电和宏原子核聚变为主要武器的，独立于地球主力的太空力量；在寻找赴死、牺牲精神；真实战略意图为用宏原子核聚变消灭地球太空军，使他们成为量子态，让量子幽灵去抵抗三体舰队。_x000D_
+雷迪亚兹：要求研究2亿吨级以上的核弹，在某次看日出时患了恐日症；真实战略意图为用核弹减速水星，使其坠入太阳，毁灭太阳系，以此威慑三体文明。_x000D_
+希恩斯：借助技术加快人脑的进化；真实战略意图为其是坚定的失败主义者和逃亡主义者，以思想刚印作为研究的最终目标，唯一目标是实现人类的逃亡。</t>
+  </si>
+  <si>
+    <t>发现三体舰队的尾迹</t>
+  </si>
+  <si>
+    <t>发现三体舰队尾迹</t>
+  </si>
+  <si>
+    <t>发现三体舰队在星际尘埃云的尾迹（刷子）</t>
+  </si>
+  <si>
+    <t>哈勃二号装配完成。一周后，在三体行星方向上四光年处，发现三体舰队的尾迹（刷子）。约1000根，速度约100倍第三宇宙速度（1670km/s）</t>
+  </si>
+  <si>
+    <t>云天明接受阶梯计划</t>
+  </si>
+  <si>
+    <t>云接受阶梯计划</t>
+  </si>
+  <si>
+    <t>程心使云天明接受阶梯计划的使命</t>
+  </si>
+  <si>
+    <t>第三届人大常委会特别会议通过安乐死法。联合国启动群星计划。_x000D_
+肺癌晚期的云天明决定安乐死，在这之前通过群星计划买下恒星DX3906送给了程心。_x000D_
+程心得知云天明时无多日，将他推荐为阶梯计划候选人。_x000D_
+在云天明安乐死前最后一刻，程心赶到叫停了安乐死。云天明接受了阶梯计划这个使命。</t>
+  </si>
+  <si>
+    <t>太空电梯始建</t>
+  </si>
+  <si>
+    <t>太空电梯天梯开始建造</t>
+  </si>
+  <si>
+    <t>太空电梯天梯一号、二号、三号同时开始建造。</t>
+  </si>
+  <si>
+    <t>阶梯计划实施</t>
+  </si>
+  <si>
+    <t>太空电梯始建，阶梯计划实施</t>
+  </si>
+  <si>
+    <t>罗辑和庄颜的孩子出生。_x000D_
+阶梯计划实施。但在第997枚核弹爆炸后，一根帆索断了，球形舱偏航，人类丢失了它的信号。云天明的大脑以光速百分之一飞向太空深处。_x000D_
+程心冬眠，以阶梯计划联络员的身份前往未来。</t>
+  </si>
+  <si>
+    <t>空天飞机出现</t>
+  </si>
+  <si>
+    <t>化学动力航天器的最后一代——空天飞机出现并投入大规模使用。</t>
+  </si>
+  <si>
+    <t>三体舰队进入第二片尘埃云</t>
+  </si>
+  <si>
+    <t>三体舰队进入第二片星际尘埃</t>
+  </si>
+  <si>
+    <t>泰勒的破壁人出现，泰勒自杀。</t>
+  </si>
+  <si>
+    <t>泰勒的破壁人出现。三体人不怕量子幽灵。泰勒自杀。_x000D_
+于雷迪亚兹和希恩斯的下一步研究需要更高计算力的计算机，所以都选择进入冬眠。</t>
+  </si>
+  <si>
+    <t>罗辑看到了宇宙的真相，称其为黑暗森林法则</t>
+  </si>
+  <si>
+    <t>PDC从罗辑身边带走了庄颜和孩子，在末日等待罗辑。_x000D_
+之后，罗辑看到了宇宙的真相，称其为“黑暗森林法则”，并躲入地堡中。同时，三体向ETO第二次发出了消灭罗辑的指令，并发射10个水滴探测器以更快的速度驶向地球。_x000D_
+一周后，ETO散播针对罗辑的基因导弹病毒。_x000D_
+一周后，在PDC会议上，罗辑公布了自己要用太阳向宇宙中发射的咒语——187J3X1恒星的位置信息。_x000D_
+罗辑感染了基因导弹，无法医治，被紧急冬眠。_x000D_
+两周后，罗辑的咒语通过太阳以光速飞向宇宙。</t>
+  </si>
+  <si>
+    <t>罗辑发出咒语</t>
+  </si>
+  <si>
+    <t>罗辑向宇宙广播187J3X1恒星坐标</t>
+  </si>
+  <si>
+    <t>罗辑感染了基因导弹，无法医治，被紧急冬眠。_x000D_
+两周后，罗辑的咒语通过太阳以光速飞向宇宙。</t>
+  </si>
+  <si>
+    <t>技术突破</t>
+  </si>
+  <si>
+    <t>天梯投入使用，可控核聚变重大突破</t>
+  </si>
+  <si>
+    <t>天梯一号、二号、三号投入正式使用。_x000D_
+可控核聚变取得重大突破。_x000D_
+中国开始计划经济，分发粮票等。</t>
+  </si>
+  <si>
+    <t>发现三体舰队的第二个尾迹</t>
+  </si>
+  <si>
+    <t>三体舰队在第2片星际尘埃上的航迹被发现，同时发现了三体舰队发射水滴探测器的事实。</t>
+  </si>
+  <si>
+    <t>章北海暗杀老航天人</t>
+  </si>
+  <si>
+    <t>章北海暗杀老航天</t>
+  </si>
+  <si>
+    <t>章北海暗杀反对研究无工质引擎的老航天人</t>
+  </si>
+  <si>
+    <t>章北海在太空中用陨石做成的子弹伪装成陨石雨，暗杀了反对研究无工质飞船引擎的三名老航天人。促使后期研究方向定为无工质引擎。_x000D_
+章北海带着常伟思的信，与特遣队一起冬眠。</t>
+  </si>
+  <si>
+    <t>史晓明出狱</t>
+  </si>
+  <si>
+    <t>雷迪亚兹和希恩斯被唤醒</t>
+  </si>
+  <si>
+    <t>雷和希被唤醒</t>
+  </si>
+  <si>
+    <t>两位面壁者被唤醒，思想钢印与水星核弹试验</t>
+  </si>
+  <si>
+    <t>雷迪亚兹和希恩斯被唤醒。_x000D_
+希恩斯在人脑中发现了思维做出判断的机制，通过对部分神经元的某一部分施加影响，可以使大脑不经思维就做出判断，相信某个信息为真或者伪。_x000D_
+雷迪亚兹制造出了人类最大的氢弹，以建造日后的水星基地为由，要求在水星的地下进行试验。_x000D_
+信念中心建成，太空军可以自愿接受人类必胜的思想钢印。但希恩斯隐蔽地修改了思想钢印机器程序中的一个正负号，使对命题判断为伪（人类必败）。_x000D_
+希恩斯和山杉惠子进入冬眠。山杉惠子在冬眠前最后一刻思考出了希恩斯的计划，但已经无法呼叫冬眠停止。</t>
+  </si>
+  <si>
+    <t>雷迪亚兹被人民用石头砸死</t>
+  </si>
+  <si>
+    <t>雷迪亚兹被砸死</t>
+  </si>
+  <si>
+    <t>破壁人揭穿雷迪亚兹真实意图，其回国后被民众砸死</t>
+  </si>
+  <si>
+    <t>水星实验在水星并不深的地层中进行，恒星型氢弹的巨大威力给主防御的领导者们留下了深刻的印象。_x000D_
+10小时后，雷迪亚兹的破壁人出现。三体文明不怕，因为人类不可能造出足够多的核弹。_x000D_
+PDC会议中，雷迪亚兹谎称自己身上有反触发系统成功脱身回国。6小时后，雷迪亚兹回到了自己的国家，被自己的人民用石头砸死。</t>
+  </si>
+  <si>
+    <t>常伟思退役</t>
+  </si>
+  <si>
+    <t>大低谷开始</t>
+  </si>
+  <si>
+    <t>大低谷开始，人口暴降</t>
+  </si>
+  <si>
+    <t>世界人口从83亿降低到35亿。_x000D_
+太空武装力量到了崩溃的边缘，增援特遣队对稳定局势发挥了巨大作用。</t>
+  </si>
+  <si>
+    <t>大低谷</t>
+  </si>
+  <si>
+    <t>大低谷结束</t>
+  </si>
+  <si>
+    <t>人民生活水平恢复，技术飞速进步</t>
+  </si>
+  <si>
+    <t>人民生活水平恢复到黄金时代的水平。一切开始飞快进步，技术障碍一个个被突破。</t>
+  </si>
+  <si>
+    <t>开始建造太空舰队</t>
+  </si>
+  <si>
+    <t>开始建造太空舰队，成为独立国家</t>
+  </si>
+  <si>
+    <t>人类社会再次宣布进入战争状态，开始建造太空舰队。太空舰队成为独立国家。</t>
+  </si>
+  <si>
+    <t>187J3X1被摧毁</t>
+  </si>
+  <si>
+    <t>罗辑咒语目标恒星被光粒摧毁</t>
+  </si>
+  <si>
+    <t>丁仪被唤醒，在北京大学物理系任教。</t>
+  </si>
+  <si>
+    <t>发现三体舰队的第五个尾迹</t>
+  </si>
+  <si>
+    <t>三体舰队在第5片星际尘埃上的航迹被发现，队形变得稀稀拉拉，一大半早就停止了加速。</t>
+  </si>
+  <si>
+    <t>观测到187J3X1被摧毁</t>
+  </si>
+  <si>
+    <t>观测到187J3X1摧毁</t>
+  </si>
+  <si>
+    <t>人类观测到187J3X1恒星被摧毁，但没人注意。</t>
+  </si>
+  <si>
+    <t>水滴到达太阳系</t>
+  </si>
+  <si>
+    <t>三体水滴探测器到达太阳系。</t>
+  </si>
+  <si>
+    <t>史强被唤醒</t>
+  </si>
+  <si>
+    <t>史强被唤醒，白血病已被治愈</t>
+  </si>
+  <si>
+    <t>罗辑被唤醒</t>
+  </si>
+  <si>
+    <t>罗辑被唤醒参加面壁计划最终听证会</t>
+  </si>
+  <si>
+    <t>罗辑、希恩斯和山杉惠子被唤醒，参加面壁计划的最后一次听证会，宣布面壁计划结束。会后，山杉惠子公开自己破壁人身份，解读了希恩斯的计划。_x000D_
+罗辑与史强进入城市后，潜伏了一个多世纪的针对罗辑的KILLER杀人病毒被唤醒，罗辑多次遭到暗杀，被迫到地上生活。_x000D_
+史强在地上见到了儿子史晓明，两人现仅相差5岁。</t>
+  </si>
+  <si>
+    <t>章北海逃离</t>
+  </si>
+  <si>
+    <t>章北海被唤醒，驾驶“自然选择”号逃离</t>
+  </si>
+  <si>
+    <t>增援未来的章北海被唤醒，为了审查钢印族，代替东方延绪成为了“自然选择”号的代理舰长。_x000D_
+随后，章北海驾驶“自然选择”号，使用前进四逃离。人类舰队派了4艘战舰追击，分别为“蓝色空间”号、“企业”号、“深空”号和“终极规律”号。</t>
+  </si>
+  <si>
+    <t>三体水滴摧毁人类舰队，封锁太阳</t>
+  </si>
+  <si>
+    <t>三体舰队在第7片星际尘埃上的航迹被发现，绝大部分战舰都进入减速状态。有一艘战舰没有减速，人类文明认为是来谈判的。_x000D_
+联合舰队从木星基地起航，共2015艘恒星级战舰组成联合舰队，统一出击，拦截三体水滴探测器，由丁仪首次接触水滴探测器。在丁仪的建议下，舰队同意在考察队出发后让“量子”号和“青铜时代”号进入深水状态。_x000D_
+5个小时后，“螳螂”号捕获了水滴。_x000D_
+考察队接触后发现，水滴表面绝对光滑。之后，水滴启动，使用最原始的撞击方式，在30多分钟后，几乎全歼了人类舰队。只有已经提前进入深水状态的“量子”号和“青铜时代”号成功地逃脱了水滴的攻击。_x000D_
+至此，人类太空舰队仅剩7艘星际战舰：“自然选择”号和追击舰“蓝色空间”号、“企业”号、“深空”号、“终极规律”号，和从水滴攻击中成功逃脱的“量子”号和“青铜时代”号。两行人沿着几乎相反的方向飞离太阳系。_x000D_
+十多个小时后，水滴到达地球，封死了太阳。_x000D_
+人类集体精神崩溃，逃亡主义迅速复活。</t>
+  </si>
+  <si>
+    <t>罗辑被视为救世主</t>
+  </si>
+  <si>
+    <t>187J3X1被摧毁证实咒语生效，罗辑成为救世主</t>
+  </si>
+  <si>
+    <t>人类发现了187J3X1恒星被摧毁，人类意识到罗辑的咒语生效，将其视为救世主。罗辑向史强解释了宇宙的黑暗森林法则。_x000D_
+罗辑恢复了面壁者身份，但太阳已经被封锁，地球不能再发射恒星级电波。_x000D_
+罗辑加入雪地工程，表面上是在太阳系内制作尘埃云对水滴进行预测，实际上他对每个核弹进行精确位置排布，使其爆炸后，从远方观察，太阳将在可见光等波段闪烁，发出三体世界坐标。当然，同时地球坐标也会暴露。罗辑要以此对三体世界进行威慑。</t>
+  </si>
+  <si>
+    <t>星舰地球黑暗战役</t>
+  </si>
+  <si>
+    <t>两个星舰地球发生黑暗战役，“蓝色空间”号和“青铜时代”号活了下来</t>
+  </si>
+  <si>
+    <t>处在太阳系遥远两侧的两个星舰地球几乎同时发生了黑暗战役，其中“青铜时代”号在全舰投票中，有94%（1670人）赞成攻击。“蓝色空间”号和“青铜时代”号活了下来，开始收集其它战舰的资源。_x000D_
+在“青铜时代”号加速离开一年后，“蓝色空间”号也加速离开。</t>
+  </si>
+  <si>
+    <t>罗辑被视为骗子</t>
+  </si>
+  <si>
+    <t>雪地工程陷入停顿，罗辑被视为骗子</t>
+  </si>
+  <si>
+    <t>雪地工程陷入停顿。_x000D_
+随着时间的推移，罗辑在公众眼中的形象渐渐衰落，成为了个大骗子。</t>
+  </si>
+  <si>
+    <t>建立威慑</t>
+  </si>
+  <si>
+    <t>罗辑建立黑暗森林威慑</t>
+  </si>
+  <si>
+    <t>罗辑与三体文明再次进行对决，告知三体世界自己的计划。_x000D_
+三体文明接受谈判，解除对太阳的封锁，让水滴和三体舰队改变航向。并将与三体世界的谈判权给了人类政府，但由于威慑度的问题，威慑控制权马上交还给了罗辑，并称其为“执剑人”。</t>
+  </si>
+  <si>
+    <t>人类得知宇宙的黑暗森林状态</t>
+  </si>
+  <si>
+    <t>人类得知黑暗森林</t>
+  </si>
+  <si>
+    <t>11月初，人类得知宇宙的黑暗森林状态，对电磁发射进行严格管制。_x000D_
+人类政府令“青铜时代”号和“蓝色空间”号立刻返航。</t>
+  </si>
+  <si>
+    <t>青铜时代号返航</t>
+  </si>
+  <si>
+    <t>“青铜时代”号返航。</t>
+  </si>
+  <si>
+    <t>引力发射器减少</t>
+  </si>
+  <si>
+    <t>引力发射器减少到四个</t>
+  </si>
+  <si>
+    <t>主张彻底消灭三体世界的极端组织“地球之子”企图夺取南极大陆的引力波发射器，差点成功。_x000D_
+在三体世界的压力下，地球将引力发射器减少到四个，分别位于亚洲、北美、欧洲和“万有引力”号飞船。</t>
+  </si>
+  <si>
+    <t>青铜时代号到达</t>
+  </si>
+  <si>
+    <t>青铜时代号到达地球，全体人员被逮捕</t>
+  </si>
+  <si>
+    <t>“青铜时代”号在前来迎接的“万有引力”号的伴随下到达地球，随后全体人员都因谋杀罪和反人类罪被逮捕。</t>
+  </si>
+  <si>
+    <t>警告蓝色空间号</t>
+  </si>
+  <si>
+    <t>“青铜时代”号军官拼死向“蓝色空间”号发送警告</t>
+  </si>
+  <si>
+    <t>对“青铜时代”号进行审判。随后，“青铜时代”号的军官拼死向“蓝色空间”号发出了警告信息。_x000D_
+“蓝色空间”号加速逃离，“万有引力”号和2个水滴立刻起航追击。</t>
+  </si>
+  <si>
+    <t>三体取得云天明大脑</t>
+  </si>
+  <si>
+    <t>三体取得云的大脑</t>
+  </si>
+  <si>
+    <t>三体第一舰队截获阶梯飞行器，取得云天明大脑。</t>
+  </si>
+  <si>
+    <t>“蓝色空间”号停止加速。</t>
+  </si>
+  <si>
+    <t>蓝色空间停止加速</t>
+  </si>
+  <si>
+    <t>三体可光速行驶</t>
+  </si>
+  <si>
+    <t>三体第二舰队制造完成，具备光速行驶能力</t>
+  </si>
+  <si>
+    <t>三体文明制造出能够光速行驶的第二舰队。_x000D_
+猜测人类文明将对黑暗森林威慑心态转变，很可能会选择低威慑度的执剑人，所以冒险派出第二支舰队。_x000D_
+为了防止曲率引擎产生的加速痕迹出现在三体星球附近，第二舰队将在穿过第一片星际尘埃云后再进入光速。</t>
+  </si>
+  <si>
+    <t>三体舰队进入光速</t>
+  </si>
+  <si>
+    <t>三体第二舰队穿过星际尘埃云后立刻进入光速</t>
+  </si>
+  <si>
+    <t>三体第二舰队穿过第一片星际尘埃云，穿过后立刻进入光速。</t>
+  </si>
+  <si>
+    <t>“蓝色空间”号投降</t>
+  </si>
+  <si>
+    <t>蓝色空间号投降</t>
+  </si>
+  <si>
+    <t>“蓝色空间”号投降，两舰同时开始减速</t>
+  </si>
+  <si>
+    <t>“蓝色空间”号与“万有引力”号距离15个天文单位时，“蓝色空间”号投降，两舰同时开始减速。“万有引力”号全舰开始苏醒。_x000D_
+两舰开始接触四维空泡，出现异常现象。在“万有引力”号上，被看作心理问题忽略。在“蓝色空间”号上则进行研究。</t>
+  </si>
+  <si>
+    <t>程心因DX3906被唤醒，遭遇维德刺杀</t>
+  </si>
+  <si>
+    <t>由于发现DX3906有一个与地球十分相似的类地行星，所以程心被唤醒。_x000D_
+维德伪造艾AA电话，刺杀程心，失败。</t>
+  </si>
+  <si>
+    <t>三体计划摧毁“万有引力”号</t>
+  </si>
+  <si>
+    <t>三体预定水滴攻击</t>
+  </si>
+  <si>
+    <t>三体令水滴在威慑控制权移交时摧毁“万有引力”号。</t>
+  </si>
+  <si>
+    <t>“万有引力”号距“蓝色空间”号仅3个天文单位。_x000D_
+三体文明给与“万有引力”号随行的两个水滴发出指令，在五个月后威慑控制权移交时立刻摧毁“万有引力”号。_x000D_
+与“万有引力”和“蓝色空间”同行的两个水滴进入智子盲区，与地球的实时通信中断。</t>
+  </si>
+  <si>
+    <t>“蓝色空间”号杀死水滴</t>
+  </si>
+  <si>
+    <t>蓝色空间杀死水滴</t>
+  </si>
+  <si>
+    <t>“蓝色空间”号通过四维空间翘曲点杀死了水滴</t>
+  </si>
+  <si>
+    <t>2270年下半年，“蓝色空间”号通过四维空间翘曲点分多批向“万有引力”号飞船投放60多名陆战队员和军官。并使用小型穿梭机杀死了水滴。</t>
+  </si>
+  <si>
+    <t>程心当选执剑人</t>
+  </si>
+  <si>
+    <t>程心以压倒性优势当选“执剑人”。</t>
+  </si>
+  <si>
+    <t>程心接手 水滴进攻</t>
+  </si>
+  <si>
+    <t>程心接手执剑人，水滴进攻，威慑终结</t>
+  </si>
+  <si>
+    <t>11月28日_x000D_
+16点10分，罗辑将威慑控制权移交给程心。_x000D_
+16:17:34，水滴来袭地球。同时水滴攻击“万有引力”号和“蓝色空间”号。_x000D_
+半分钟后，水滴没有击中“万有引力”号和“蓝色空间”号。“万有引力”号的指挥官们发现水滴死了，“蓝色空间”号通过四维空间翘曲点推偏水滴，救了两舰。_x000D_
+16:27:58，地球上所有引力波发射器被摧毁，太阳被封锁，地球的黑暗森林威慑终止。</t>
+  </si>
+  <si>
+    <t>引力波发射器启动</t>
+  </si>
+  <si>
+    <t>“万有引力”号启动了引力波发射器</t>
+  </si>
+  <si>
+    <t>“万有引力”号被“蓝色空间”号占领。_x000D_
+21点，两舰发现三体第二舰队正在以光速驶向地球。两舰猜测地球方已发生事变，且引力波广播没有启动。_x000D_
+两舰进行全民公决后，启动了引力波发射器。_x000D_
+11月29日_x000D_
+“蓝色空间”号将四维空间翘曲点的存在告诉“万有引力”号船员。_x000D_
+派出探险队进入四维空间对四维物体“魔戒”进行探测。</t>
+  </si>
+  <si>
+    <t>威慑后</t>
+  </si>
+  <si>
+    <t>发现四维碎块本身在缩小</t>
+  </si>
+  <si>
+    <t>发现四维碎块缩小</t>
+  </si>
+  <si>
+    <t>“万有引力”号和“蓝色空间”号退出四维碎块。并发现四维碎块本身在缩小。</t>
+  </si>
+  <si>
+    <t>“魔戒”坠入三维空间</t>
+  </si>
+  <si>
+    <t>魔戒坠入三维空间</t>
+  </si>
+  <si>
+    <t>“魔戒”坠入三维空间，出现了长度1亿3000万千米的线。</t>
+  </si>
+  <si>
+    <t>发现三体第二舰队</t>
+  </si>
+  <si>
+    <t>发现三体第二舰队穿过第1片尘埃云</t>
+  </si>
+  <si>
+    <t>地球观测到三体世界派出的第二支舰队，穿过第1片尘埃云。</t>
+  </si>
+  <si>
+    <t>发现三体第二舰队达到光速</t>
+  </si>
+  <si>
+    <t>发现三体达到光速</t>
+  </si>
+  <si>
+    <t>发现三体第二舰队以光速穿过第2片尘埃云，全人类移民开始。</t>
+  </si>
+  <si>
+    <t>地球观测到三体第二舰队，穿过第2片尘埃云，发现三体舰队达到了光速。_x000D_
+三体舰队到达距太阳6000个天文单位处，脱离光速至光速的15%，使用常规推进器减速。_x000D_
+智子命令人类一年内移民到保留地——澳大利亚和火星，全人类移民开始。</t>
+  </si>
+  <si>
+    <t>21亿人迁至澳大利亚</t>
+  </si>
+  <si>
+    <t>21亿人至澳大利亚</t>
+  </si>
+  <si>
+    <t>世界一半人口迁移至澳大利亚保留地</t>
+  </si>
+  <si>
+    <t>世界人口的一半，21亿人已经迁移到澳大利亚。</t>
+  </si>
+  <si>
+    <t>移民大军与军队冲突，数十万人死亡</t>
+  </si>
+  <si>
+    <t>堪培拉惨案发生。饥饿的移民大军与堪培拉军队发生冲突，十多天的混乱后，死亡50多万人，几千万人完全断绝了食物和饮水供应。</t>
+  </si>
+  <si>
+    <t>34亿人于澳大利亚</t>
+  </si>
+  <si>
+    <t>澳大利亚人口达到34亿</t>
+  </si>
+  <si>
+    <t>大移民完成</t>
+  </si>
+  <si>
+    <t>去澳大利亚的大移民完成</t>
+  </si>
+  <si>
+    <t>大移民完成。此时澳大利亚41亿6000有万人，火星基地100万人，地球治安军500万人，200万地球抵抗运动成员等。_x000D_
+治安军开始打击电力系统、港口和大型运输设备。_x000D_
+智子宣布，澳大利亚必须处于低技术的农业社会，禁止使用包括电力在内的任何现代技术。</t>
+  </si>
+  <si>
+    <t>三体得知引力波广播启动</t>
+  </si>
+  <si>
+    <t>得知引力波启动</t>
+  </si>
+  <si>
+    <t>三体得知引力波广播启动，放弃地球，人类从澳大利亚疏散</t>
+  </si>
+  <si>
+    <t>三体文明得知了“万有引力”号启动了引力波广播，决定放弃地球。_x000D_
+三体第二舰队转向，所有水滴撤离。_x000D_
+人类开始从澳大利亚疏散。</t>
+  </si>
+  <si>
+    <t>大疏散完成</t>
+  </si>
+  <si>
+    <t>人类从澳大利亚疏散完成，返回各地</t>
+  </si>
+  <si>
+    <t>程心短期冬眠</t>
+  </si>
+  <si>
+    <t>程心视网膜剥离坏死，短期冬眠</t>
+  </si>
+  <si>
+    <t>程心视网膜剥离坏死，克隆培育需要5年左右，所以程心短期冬眠。</t>
+  </si>
+  <si>
+    <t>城市伤痕完全消失</t>
+  </si>
+  <si>
+    <t>各大城市的伤痕完全消失</t>
+  </si>
+  <si>
+    <t>三体星系毁灭</t>
+  </si>
+  <si>
+    <t>10月，三体世界被光粒摧毁，发射光粒的是某个宇宙飞行器。。</t>
+  </si>
+  <si>
+    <t>程心被唤醒，视力恢复。_x000D_
+人类观测到三体世界被摧毁。</t>
+  </si>
+  <si>
+    <t>云天明的三个童话</t>
+  </si>
+  <si>
+    <t>云天明对程心讲了三个藏有海量信息的童话故事</t>
+  </si>
+  <si>
+    <t>罗辑从智子口中问出，有可能向宇宙发布避免黑暗森林打击的安全声明。_x000D_
+之后，智子告诉程心，云天明要见她。_x000D_
+三天后，在地日拉格朗日点，程心通过智子会见了云天明。会见中，云天明讲了三个他编的藏有海量信息的童话故事：《国王的新画师》、《饕餮海》和《深水王子》。_x000D_
+联合国成立情报解读委员会（IDC），开始解读云天明的三个童话故事。_x000D_
+掩体计划得到空前关注。_x000D_
+云天明情报中，曲率驱动和降低光速（黑域）以达到安全声明的隐喻被解读，但针眼画师的画这个隐喻最终都未被成功解读。此隐喻的是对于太阳系这种多行星星系，将会使用二向箔进行降维黑暗森林打击。</t>
+  </si>
+  <si>
+    <t>曲率飞船研究被禁</t>
+  </si>
+  <si>
+    <t>得知曲率飞船进入光速会留下航迹，曲率研究被禁</t>
+  </si>
+  <si>
+    <t>林格-斐兹罗观测站在三体恒星残骸处和三体第二舰队进入光速的位置，发现了“肥皂泡”，得知曲率驱动飞船在进入光速的加速阶段会留下航迹。曲率驱动的研究被完全禁止。_x000D_
+两天后，关于曲率驱动航迹的警告被误传，人们以为是打击警告，产生动乱，死亡1万多人。</t>
+  </si>
+  <si>
     <t>程心交出星环 冬眠</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>观测到187J3X1摧毁</t>
-    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>程心将星环公司交给维德，与艾AA进入冬眠</t>
+  </si>
+  <si>
+    <t>程心将自己星环公司的移交给维德，进行曲率驱动研究。条件是若在研制光速飞船过程中有可能危害人类生命，必须唤醒程心。_x000D_
+程心与艾AA进入冬眠。</t>
+  </si>
+  <si>
+    <t>黑洞项目开始</t>
+  </si>
+  <si>
+    <t>环日加速器与木卫十三制作微型黑洞</t>
+  </si>
+  <si>
+    <t>黑洞项目开始。使用环日加速器和木卫十三制作了一个微型黑洞。</t>
+  </si>
+  <si>
+    <t>掩体纪元</t>
+  </si>
+  <si>
+    <t>星环集团公开研制曲率飞船计划</t>
+  </si>
+  <si>
+    <t>星环公开曲率计划</t>
+  </si>
+  <si>
+    <t>星环集团公开宣布研制曲率飞船的计划，与联邦政府摩擦不断。</t>
+  </si>
+  <si>
+    <t>高Way主动进入微型黑洞</t>
+  </si>
+  <si>
+    <t>高Way进入黑洞</t>
+  </si>
+  <si>
+    <t>黑洞项目研究者高Way主动进入微型黑洞</t>
+  </si>
+  <si>
+    <t>程心命令星环集团投降</t>
+  </si>
+  <si>
+    <t>程心命令星环投降</t>
+  </si>
+  <si>
+    <t>程心被唤醒，命令星环集团投降</t>
+  </si>
+  <si>
+    <t>星环集团宣布脱离太阳系联邦独立，与太阳系政府间的冲突升级。星环集团决定使用反物质子弹进行威慑。_x000D_
+9日，程心在木星背面的亚洲一号太空城被唤醒。_x000D_
+程心命令星环集团投降。星环集团向联邦政府投降。_x000D_
+一周后，星环集团被宣布为非法，维德等人被逮捕。</t>
+  </si>
+  <si>
+    <t>掩体纪元11年</t>
+  </si>
+  <si>
+    <t>维德死刑 程心冬眠</t>
+  </si>
+  <si>
+    <t>维德被执行死刑，程心进入冬眠</t>
+  </si>
+  <si>
+    <t>维德被执行死刑。_x000D_
+程心进入冬眠，预定在打击之后唤醒。</t>
+  </si>
+  <si>
+    <t>星环集团恢复曲率引擎研究</t>
+  </si>
+  <si>
+    <t>星环恢复曲率研究</t>
+  </si>
+  <si>
+    <t>水星秘密基地恢复空间曲率驱动研究</t>
+  </si>
+  <si>
+    <t>星环集团的残余力量在水星秘密基地恢复了空间曲率驱动的研究。</t>
+  </si>
+  <si>
+    <t>掩体纪元46年</t>
+  </si>
+  <si>
+    <t>星环发现黑域制法</t>
+  </si>
+  <si>
+    <t>发现曲率尾迹可降低光速，与联邦政府合作</t>
+  </si>
+  <si>
+    <t>星环集团发现了曲率驱动尾迹可以降低光速，可以制作黑域，所以与联邦政府达成了合作。_x000D_
+这里原文时间出入很大：程心逃亡时罗辑告诉他，韦德死后35年水星基地恢复，韦德死于掩体纪元11年，那么掩体纪元46年才开始进行研究。而后又说进行了半个世纪的研究，但是后面我们知道太阳系在掩体纪元67年就毁灭了，时间出入很大，这里只能压缩研究时间以对齐主要时间轴。</t>
+  </si>
+  <si>
+    <t>飞船发射二向箔</t>
+  </si>
+  <si>
+    <t>一艘智慧飞船对太阳系发射了二向箔</t>
+  </si>
+  <si>
+    <t>一艘智慧飞船以接近光速的速度从奥尔特星云外侧掠过，对太阳系发射了二向箔。</t>
+  </si>
+  <si>
+    <t>曲率引擎完成测试</t>
+  </si>
+  <si>
+    <t>3套曲率引擎制造完成。第1套测试完被安装在星环号上</t>
+  </si>
+  <si>
+    <t>三套曲率引擎制造完成。其中第一套引擎已经经过3年测试完，第二和三套进行测试。_x000D_
+第一套曲率引擎被安装在星环号上。_x000D_
+太阳系预警系统发现了此不明智慧飞船，并发现其向太阳系发射的东西。</t>
+  </si>
+  <si>
+    <t>掩体纪元66年</t>
+  </si>
+  <si>
+    <t>歌者打出了二向箔</t>
+  </si>
+  <si>
+    <t>歌者文明发现太阳系，发射二向箔打击</t>
+  </si>
+  <si>
+    <t>位于银河系猎户旋臂的歌者发现了与三体世界交流的太阳系，也打出了二向箔。</t>
+  </si>
+  <si>
+    <t>掩体纪元67年</t>
+  </si>
+  <si>
+    <t>太阳系毁灭</t>
+  </si>
+  <si>
+    <t>二向箔打击，太阳系二维化，程心与艾AA逃跑</t>
+  </si>
+  <si>
+    <t>距太阳150个天文单位的二向箔减速至光速千分之一，人类出动飞船进行拦截。_x000D_
+二向箔的封装力场完全蒸发，三维空间开始向二维跌落，逃逸速度为光速，人类文明无生还希望。_x000D_
+5月19日，程心被唤醒。_x000D_
+太阳系联邦政府正式向国际社会发布黑暗森林打击警报。_x000D_
+程心与艾AA乘坐星环号到冥王星，运出部分文物。_x000D_
+太阳系星球开始坠入二维。_x000D_
+程心与艾AA被告知星环号可进行光速航行。罗辑令飞船AI进入光速飞行，程心和艾AA以光速逃离了太阳系，目标为程心的星星——287光年外的DX3906。_x000D_
+太阳系毁灭。</t>
+  </si>
+  <si>
+    <t>星舰文明到新世界</t>
+  </si>
+  <si>
+    <t>2400年代，“万有引力”号和“蓝色空间”号到达新世界</t>
+  </si>
+  <si>
+    <t>银河纪元</t>
+  </si>
+  <si>
+    <t>新文明达到光速</t>
+  </si>
+  <si>
+    <t>人类新文明制造出曲率光速飞船</t>
+  </si>
+  <si>
+    <t>2500年代，人类新世界制造出曲率光速飞船。</t>
+  </si>
+  <si>
+    <t>程心到达DX3906</t>
+  </si>
+  <si>
+    <t>程心和艾AA到达DX3906，见到关一帆</t>
+  </si>
+  <si>
+    <t>程心和艾AA到达（程心参考系约10天）。见到等待她们的关一帆。_x000D_
+发现有5艘不明宇宙飞船在DX3906的第一颗行星——“灰星”表面降落，关一帆与程心一起去探察。_x000D_
+4天后，到达“灰星”，在其表面上发现了那5艘飞船留下的光速为0的航迹——死线。两人马上回返。_x000D_
+4天后，云天明来到DX3906。</t>
+  </si>
+  <si>
+    <t>程心坠入黑域</t>
+  </si>
+  <si>
+    <t>程心与关一帆被困死线，DX3906被黑域包裹</t>
+  </si>
+  <si>
+    <t>在程心和关一帆乘坐穿梭机着陆过程中，死线扩散了（有可能因为云天明飞船的扰动），穿梭机被困，以光速绕行星运动。_x000D_
+DX3906被黑域包裹。_x000D_
+关一帆开始初始化神经元计算机，以控制飞船脱离光速。_x000D_
+18903729地球年后，飞船脱离光速。</t>
+  </si>
+  <si>
+    <t>黑域纪元</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1980,14 +1704,6 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2173,7 +1889,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -2308,37 +2024,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -2350,37 +2035,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2415,43 +2069,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -2586,77 +2203,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
@@ -3020,150 +2586,145 @@
   <dimension ref="A1:I115"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.75" style="14" customWidth="1"/>
-    <col min="2" max="2" width="4.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4" style="15" customWidth="1"/>
-    <col min="4" max="4" width="17.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="33.125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="64.75" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="24.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="62.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="5" t="s">
+    <row r="1" spans="1:9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
+      <c r="A2" s="1">
         <v>1453</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>5</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="1">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="G2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="14">
+      <c r="A3" s="1">
         <v>1453</v>
       </c>
       <c r="B3" s="1">
         <v>5</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="1">
         <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>37</v>
+        <v>136</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>1453</v>
       </c>
       <c r="B4" s="1">
         <v>5</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="1">
         <v>29</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>39</v>
+      <c r="D4" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <v>1947</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="1">
         <v>6</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="10"/>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+      <c r="A6" s="1">
         <v>1967</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>41</v>
+        <v>138</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -3172,14 +2733,14 @@
         <v>10</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I6" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="14">
+      <c r="A7" s="1">
         <v>1968</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -3194,12 +2755,12 @@
       <c r="H7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="14">
+      <c r="A8" s="1">
         <v>1969</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -3212,126 +2773,123 @@
         <v>16</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="14">
+      <c r="A9" s="1">
         <v>1970</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>46</v>
+        <v>141</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
+    <row r="10" spans="1:9" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <v>1971</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="F10" s="1">
         <v>2</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>48</v>
+        <v>145</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="14">
+      <c r="A11" s="1">
         <v>1973</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>50</v>
+      <c r="D11" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17">
+    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
         <v>1975</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="4" t="s">
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="19" t="s">
+      <c r="I12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="11">
+      <c r="A13" s="1">
         <v>1979</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="1">
         <v>10</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="1">
         <v>21</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="D13" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F13" s="1">
         <v>7</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13" s="13" t="s">
+      <c r="G13" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="14">
+      <c r="A14" s="1">
         <v>1980</v>
       </c>
       <c r="B14" s="1">
@@ -3346,16 +2904,16 @@
       <c r="G14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="14">
+      <c r="A15" s="1">
         <v>1982</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>22</v>
@@ -3366,12 +2924,12 @@
       <c r="H15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="I15" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="14">
+      <c r="A16" s="1">
         <v>1984</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -3384,954 +2942,952 @@
         <v>25</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="14">
+      <c r="A17" s="1">
         <v>1987</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>59</v>
+      <c r="D17" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="I17" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="14">
+      <c r="A18" s="1">
         <v>1988</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>60</v>
+      <c r="D18" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I18" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A19" s="14">
+      <c r="A19" s="1">
         <v>1990</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>62</v>
+      <c r="D19" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>63</v>
+        <v>161</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="14">
+      <c r="A20" s="1">
         <v>1992</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>65</v>
+      <c r="D20" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="14">
+      <c r="A21" s="1">
         <v>1995</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>68</v>
+      <c r="D21" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="F21" s="1">
         <v>3</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A22" s="14">
+      <c r="A22" s="1">
         <v>1999</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>74</v>
+      <c r="D22" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F22" s="1">
         <v>5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>76</v>
+        <v>169</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I22" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="14">
+      <c r="A23" s="1">
         <v>2004</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>69</v>
+      <c r="D23" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="27.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="17">
+    <row r="24" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
         <v>2006</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" s="4">
+      <c r="D24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="1">
         <v>1</v>
       </c>
-      <c r="G24" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="4"/>
-      <c r="I24" s="19" t="s">
+      <c r="G24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I24" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="14">
+    <row r="25" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
         <v>2007</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="F25" s="1">
         <v>7</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>78</v>
+        <v>175</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="I25" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="57" x14ac:dyDescent="0.2">
-      <c r="A26" s="14">
+      <c r="A26" s="1">
         <v>2007</v>
       </c>
       <c r="B26" s="1">
         <v>-2</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="F26" s="1">
         <v>3</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I26" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="114" x14ac:dyDescent="0.2">
-      <c r="A27" s="14">
+      <c r="A27" s="1">
         <v>2007</v>
       </c>
       <c r="B27" s="1">
         <v>-6</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="F27" s="1">
         <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="I27" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A28" s="14">
+      <c r="A28" s="1">
         <v>2007</v>
       </c>
       <c r="B28" s="1">
         <v>-6</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="1">
         <v>-15</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>131</v>
+        <v>183</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I28" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A29" s="14">
+    <row r="29" spans="1:9" ht="128.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
         <v>2007</v>
       </c>
       <c r="B29" s="1">
         <v>-7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="F29" s="1">
         <v>5</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I29" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A30" s="14">
+      <c r="A30" s="1">
         <v>2010</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
       <c r="F30" s="1">
         <v>1</v>
       </c>
+      <c r="G30" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="H30" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I30" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="I30" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="14">
+      <c r="A31" s="1">
         <v>2010</v>
       </c>
       <c r="B31" s="1">
         <v>-5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>90</v>
+        <v>191</v>
       </c>
       <c r="F31" s="1">
         <v>3</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="267" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="14">
+    <row r="32" spans="1:9" ht="299.25" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
         <v>2010</v>
       </c>
       <c r="B32" s="1">
         <v>-6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>81</v>
+        <v>194</v>
       </c>
       <c r="F32" s="1">
         <v>7</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>82</v>
+        <v>195</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I32" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="14">
+    <row r="33" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
         <v>2010</v>
       </c>
       <c r="B33" s="1">
         <v>-7</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>92</v>
+        <v>197</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>94</v>
+        <v>199</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I33" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="88.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14">
+    <row r="34" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
         <v>2011</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>97</v>
+      <c r="D34" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F34" s="1">
         <v>3</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>99</v>
+        <v>203</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I34" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="14">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
         <v>2014</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E35" s="3"/>
+      <c r="D35" s="1" t="s">
+        <v>205</v>
+      </c>
       <c r="F35" s="1">
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I35" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="14">
+    <row r="36" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>2014</v>
       </c>
       <c r="B36" s="1">
         <v>-3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>100</v>
+        <v>208</v>
       </c>
       <c r="F36" s="1">
         <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I36" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="14">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
         <v>2015</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="I37" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="14">
+    <row r="38" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
         <v>2015</v>
       </c>
       <c r="B38" s="1">
         <v>-2</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>73</v>
+      <c r="D38" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I38" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="14">
+    <row r="39" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
         <v>2015</v>
       </c>
       <c r="B39" s="1">
         <v>-3</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>102</v>
+      <c r="D39" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F39" s="1">
         <v>5</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>103</v>
+        <v>215</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="I39" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="A40" s="14">
+      <c r="A40" s="1">
         <v>2015</v>
       </c>
       <c r="B40" s="1">
         <v>-4</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="F40" s="1">
         <v>5</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I40" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A41" s="14">
+      <c r="A41" s="1">
         <v>2015</v>
       </c>
       <c r="B41" s="1">
         <v>-5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="F41" s="1">
         <v>7</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>118</v>
+        <v>220</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I41" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A42" s="14">
+      <c r="A42" s="1">
         <v>2019</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>119</v>
+        <v>222</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>120</v>
+        <v>223</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I42" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A43" s="14">
+      <c r="A43" s="1">
         <v>2019</v>
       </c>
       <c r="B43" s="1">
         <v>-2</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>121</v>
+        <v>225</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I43" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A44" s="14">
+      <c r="A44" s="1">
         <v>2019</v>
       </c>
       <c r="B44" s="1">
         <v>-3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>124</v>
+        <v>227</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="F44" s="1">
         <v>5</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>126</v>
+        <v>229</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I44" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A45" s="14">
+      <c r="A45" s="1">
         <v>2026</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>127</v>
+      <c r="D45" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
       </c>
-      <c r="I45" s="16" t="s">
+      <c r="I45" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="128.25" x14ac:dyDescent="0.2">
-      <c r="A46" s="14">
+    <row r="46" spans="1:9" ht="156.75" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
         <v>2027</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>138</v>
+      <c r="D46" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>139</v>
+        <v>233</v>
       </c>
       <c r="F46" s="1">
         <v>3</v>
       </c>
+      <c r="G46" s="1" t="s">
+        <v>234</v>
+      </c>
       <c r="H46" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I46" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A47" s="14">
+      <c r="A47" s="1">
         <v>2027</v>
       </c>
       <c r="B47" s="1">
         <v>-4</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>141</v>
+      <c r="D47" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>140</v>
+        <v>237</v>
       </c>
       <c r="F47" s="1">
         <v>4</v>
       </c>
+      <c r="G47" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="H47" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I47" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="14">
+      <c r="A48" s="1">
         <v>2027</v>
       </c>
       <c r="B48" s="1">
         <v>-6</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>137</v>
+      <c r="D48" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
       </c>
-      <c r="I48" s="16" t="s">
+      <c r="I48" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A49" s="14">
+      <c r="A49" s="1">
         <v>2040</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>144</v>
+      <c r="D49" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="F49" s="1">
         <v>5</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>149</v>
+      <c r="G49" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="I49" s="16" t="s">
-        <v>153</v>
+        <v>243</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A50" s="14">
+      <c r="A50" s="1">
         <v>2041</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>150</v>
+      <c r="D50" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
       </c>
-      <c r="G50" s="3"/>
-      <c r="I50" s="16" t="s">
-        <v>153</v>
+      <c r="I50" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A51" s="14">
+      <c r="A51" s="1">
         <v>2047</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>151</v>
+      <c r="D51" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
       </c>
-      <c r="G51" s="3"/>
-      <c r="I51" s="16" t="s">
-        <v>153</v>
+      <c r="I51" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A52" s="14">
+      <c r="A52" s="1">
         <v>2081</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>152</v>
+      <c r="D52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
       </c>
-      <c r="G52" s="3"/>
-      <c r="I52" s="16" t="s">
-        <v>153</v>
+      <c r="I52" s="1" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A53" s="14">
+      <c r="A53" s="1">
         <v>2100</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>145</v>
+      <c r="D53" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="F53" s="1">
         <v>3</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="I53" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A54" s="14">
+    <row r="54" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
         <v>2140</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>155</v>
+      <c r="D54" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="F54" s="1">
         <v>1</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I54" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="I54" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A55" s="14">
+    <row r="55" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
         <v>2154</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>158</v>
+      <c r="D55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="F55" s="1">
         <v>3</v>
       </c>
-      <c r="H55" s="3"/>
-      <c r="I55" s="16" t="s">
+      <c r="G55" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A56" s="14">
+      <c r="A56" s="1">
         <v>2198</v>
       </c>
-      <c r="D56" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E56" s="7"/>
+      <c r="D56" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="F56" s="1">
         <v>0</v>
       </c>
-      <c r="H56" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I56" s="16" t="s">
+      <c r="H56" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I56" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="27" x14ac:dyDescent="0.2">
-      <c r="A57" s="14">
+    <row r="57" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
         <v>2201</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>93</v>
+      <c r="D57" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F57" s="1">
         <v>1</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="I57" s="16" t="s">
+      <c r="H57" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I57" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A58" s="14">
+    <row r="58" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
         <v>2204</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>424</v>
+      <c r="D58" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="F58" s="1">
         <v>1</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="I58" s="16" t="s">
+      <c r="H58" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A59" s="14">
+      <c r="A59" s="1">
         <v>2205</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E59" s="7"/>
+      <c r="D59" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="F59" s="1">
         <v>3</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="I59" s="16" t="s">
+      <c r="H59" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" s="14">
+    <row r="60" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
         <v>2205</v>
       </c>
       <c r="B60" s="1">
         <v>-1</v>
       </c>
-      <c r="C60" s="15">
+      <c r="C60" s="1">
         <v>-15</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E60" s="7"/>
+      <c r="D60" s="1" t="s">
+        <v>261</v>
+      </c>
       <c r="F60" s="1">
         <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="H60" s="3"/>
-      <c r="I60" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="I60" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="67.5" x14ac:dyDescent="0.2">
-      <c r="A61" s="14">
+    <row r="61" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
         <v>2205</v>
       </c>
       <c r="B61" s="1">
         <v>-2</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E61" s="7"/>
+      <c r="D61" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="F61" s="1">
         <v>3</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="I61" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="I61" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="54" x14ac:dyDescent="0.2">
-      <c r="A62" s="14">
+    <row r="62" spans="1:9" ht="57" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
         <v>2205</v>
       </c>
       <c r="B62" s="1">
         <v>-5</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E62" s="7"/>
+      <c r="D62" s="1" t="s">
+        <v>266</v>
+      </c>
       <c r="F62" s="1">
         <v>5</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="I62" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="199.5" x14ac:dyDescent="0.2">
-      <c r="A63" s="14">
+      <c r="A63" s="1">
         <v>2205</v>
       </c>
       <c r="B63" s="1">
@@ -4344,748 +3900,745 @@
         <v>7</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I63" s="16" t="s">
+        <v>270</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A64" s="14">
+    <row r="64" spans="1:9" ht="114" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
         <v>2205</v>
       </c>
       <c r="B64" s="1">
         <v>-7</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>172</v>
+        <v>271</v>
       </c>
       <c r="F64" s="1">
         <v>3</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>173</v>
+        <v>272</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="I64" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="I64" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="57" x14ac:dyDescent="0.2">
-      <c r="A65" s="14">
+      <c r="A65" s="1">
         <v>2205</v>
       </c>
       <c r="B65" s="1">
         <v>-8</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="F65" s="1">
         <v>5</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>182</v>
+        <v>275</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="I65" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="29.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="14">
+    <row r="66" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
         <v>2206</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>183</v>
+        <v>277</v>
       </c>
       <c r="F66" s="1">
         <v>1</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="I66" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="57" x14ac:dyDescent="0.2">
-      <c r="A67" s="11">
+      <c r="A67" s="1">
         <v>2208</v>
       </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2">
+      <c r="D67" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="F67" s="1">
         <v>7</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="I67" s="13" t="s">
+      <c r="G67" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A68" s="14">
+      <c r="A68" s="1">
         <v>2208</v>
       </c>
       <c r="B68" s="1">
         <v>11</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>188</v>
+        <v>283</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>189</v>
+        <v>284</v>
       </c>
       <c r="F68" s="1">
         <v>5</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="I68" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A69" s="14">
+      <c r="A69" s="1">
         <v>2209</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>192</v>
+        <v>286</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="I69" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="57" x14ac:dyDescent="0.2">
-      <c r="A70" s="14">
+      <c r="A70" s="1">
         <v>2214</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>194</v>
+        <v>288</v>
       </c>
       <c r="F70" s="1">
         <v>1</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>195</v>
+        <v>289</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="I70" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A71" s="14">
+      <c r="A71" s="1">
         <v>2220</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>198</v>
+        <v>291</v>
       </c>
       <c r="F71" s="1">
         <v>1</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>199</v>
+        <v>292</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="I71" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="I71" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A72" s="14">
+      <c r="A72" s="1">
         <v>2221</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>201</v>
+        <v>294</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>202</v>
+        <v>295</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="I72" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A73" s="14">
+      <c r="A73" s="1">
         <v>2240</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>203</v>
+        <v>297</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>204</v>
+        <v>298</v>
       </c>
       <c r="F73" s="1">
         <v>3</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="I73" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="I73" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A74" s="14">
+      <c r="A74" s="1">
         <v>2246</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>207</v>
+        <v>300</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
       </c>
-      <c r="I74" s="16" t="s">
+      <c r="I74" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A75" s="14">
+      <c r="A75" s="1">
         <v>2265</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E75" s="7"/>
+        <v>302</v>
+      </c>
       <c r="F75" s="1">
         <v>3</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>210</v>
+        <v>303</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="I75" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="I75" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A76" s="14">
+      <c r="A76" s="1">
         <v>2266</v>
       </c>
       <c r="B76" s="1">
         <v>-12</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E76" s="7"/>
+        <v>305</v>
+      </c>
       <c r="F76" s="1">
         <v>1</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>213</v>
+        <v>306</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="I76" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="57" x14ac:dyDescent="0.2">
-      <c r="A77" s="14">
+      <c r="A77" s="1">
         <v>2269</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>215</v>
+        <v>308</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="F77" s="1">
         <v>0</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>216</v>
+        <v>310</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="I77" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A78" s="14">
+      <c r="A78" s="1">
         <v>2270</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E78" s="7"/>
+        <v>45</v>
+      </c>
       <c r="F78" s="1">
         <v>3</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>221</v>
+        <v>312</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="I78" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="I78" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A79" s="14">
+      <c r="A79" s="1">
         <v>2270</v>
       </c>
       <c r="B79" s="1">
         <v>-6</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="F79" s="1">
         <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I79" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="I79" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A80" s="14">
+      <c r="A80" s="1">
         <v>2270</v>
       </c>
       <c r="B80" s="1">
         <v>-8</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>332</v>
+        <v>318</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>319</v>
       </c>
       <c r="F80" s="1">
         <v>3</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="I80" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="I80" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A81" s="14">
+      <c r="A81" s="1">
         <v>2270</v>
       </c>
       <c r="B81" s="1">
         <v>11</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E81" s="7"/>
+        <v>322</v>
+      </c>
       <c r="F81" s="1">
         <v>3</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="I81" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="I81" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="100.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="17">
+    <row r="82" spans="1:9" ht="114" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
         <v>2270</v>
       </c>
-      <c r="B82" s="4">
+      <c r="B82" s="1">
         <v>11</v>
       </c>
-      <c r="C82" s="18">
+      <c r="C82" s="1">
         <v>-15</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4">
+      <c r="D82" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F82" s="1">
         <v>7</v>
       </c>
-      <c r="G82" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="I82" s="19" t="s">
-        <v>228</v>
+      <c r="G82" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="11">
+      <c r="A83" s="1">
         <v>2270</v>
       </c>
-      <c r="B83" s="2">
+      <c r="B83" s="1">
         <v>11</v>
       </c>
-      <c r="C83" s="12">
+      <c r="C83" s="1">
         <v>28</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2">
+      <c r="D83" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="F83" s="1">
         <v>6</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="I83" s="13" t="s">
-        <v>227</v>
+      <c r="G83" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A84" s="14">
+      <c r="A84" s="1">
         <v>2270</v>
       </c>
       <c r="B84" s="1">
         <v>12</v>
       </c>
-      <c r="C84" s="15">
+      <c r="C84" s="1">
         <v>2</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>231</v>
+        <v>331</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>230</v>
+        <v>332</v>
       </c>
       <c r="F84" s="1">
         <v>0</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="I84" s="16" t="s">
-        <v>227</v>
+        <v>333</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A85" s="14">
+      <c r="A85" s="1">
         <v>2270</v>
       </c>
       <c r="B85" s="1">
         <v>12</v>
       </c>
-      <c r="C85" s="15">
+      <c r="C85" s="1">
         <v>24</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>232</v>
+        <v>334</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>233</v>
+        <v>335</v>
       </c>
       <c r="F85" s="1">
         <v>0</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="I85" s="16" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A86" s="14">
+        <v>336</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
         <v>2271</v>
       </c>
       <c r="B86" s="1">
         <v>1</v>
       </c>
-      <c r="C86" s="15">
+      <c r="C86" s="1">
         <v>5</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>239</v>
+        <v>337</v>
       </c>
       <c r="F86" s="1">
         <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>240</v>
+        <v>338</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="I86" s="16" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="57" x14ac:dyDescent="0.2">
-      <c r="A87" s="14">
+        <v>339</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
         <v>2271</v>
       </c>
       <c r="B87" s="1">
         <v>1</v>
       </c>
-      <c r="C87" s="15">
+      <c r="C87" s="1">
         <v>8</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>242</v>
+        <v>340</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>243</v>
+        <v>341</v>
       </c>
       <c r="F87" s="1">
         <v>5</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>247</v>
+        <v>342</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I87" s="16" t="s">
-        <v>227</v>
+        <v>343</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A88" s="14">
+      <c r="A88" s="1">
         <v>2271</v>
       </c>
       <c r="B88" s="1">
         <v>7</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>245</v>
+        <v>344</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>246</v>
+        <v>345</v>
       </c>
       <c r="F88" s="1">
         <v>3</v>
       </c>
+      <c r="G88" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="H88" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="I88" s="16" t="s">
-        <v>227</v>
+        <v>347</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A89" s="14">
+      <c r="A89" s="1">
         <v>2271</v>
       </c>
       <c r="B89" s="1">
         <v>8</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>249</v>
+        <v>46</v>
       </c>
       <c r="F89" s="1">
         <v>0</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>250</v>
+        <v>348</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I89" s="16" t="s">
-        <v>227</v>
+        <v>349</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A90" s="14">
+      <c r="A90" s="1">
         <v>2271</v>
       </c>
       <c r="B90" s="1">
         <v>10</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>252</v>
+        <v>350</v>
       </c>
       <c r="F90" s="1">
         <v>1</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="I90" s="16" t="s">
-        <v>227</v>
+        <v>351</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A91" s="14">
+      <c r="A91" s="1">
         <v>2272</v>
       </c>
       <c r="B91" s="1">
         <v>1</v>
       </c>
-      <c r="C91" s="15">
+      <c r="C91" s="1">
         <v>5</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>254</v>
+        <v>352</v>
       </c>
       <c r="F91" s="1">
         <v>0</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>255</v>
+        <v>353</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="I91" s="16" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="17">
+        <v>354</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
         <v>2272</v>
       </c>
-      <c r="B92" s="4">
+      <c r="B92" s="1">
         <v>1</v>
       </c>
-      <c r="C92" s="18">
+      <c r="C92" s="1">
         <v>11</v>
       </c>
-      <c r="D92" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="F92" s="4">
+      <c r="D92" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F92" s="1">
         <v>5</v>
       </c>
-      <c r="G92" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="I92" s="19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A93" s="14">
+      <c r="G92" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
         <v>2272</v>
       </c>
       <c r="B93" s="1">
         <v>5</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>261</v>
+        <v>359</v>
       </c>
       <c r="F93" s="1">
         <v>0</v>
       </c>
-      <c r="I93" s="16" t="s">
+      <c r="G93" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A94" s="14">
+    <row r="94" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
         <v>2273</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>263</v>
+        <v>361</v>
       </c>
       <c r="F94" s="1">
         <v>3</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>264</v>
+        <v>362</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="I94" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A95" s="14">
+      <c r="A95" s="1">
         <v>2274</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>266</v>
+        <v>364</v>
       </c>
       <c r="F95" s="1">
         <v>0</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="I95" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="I95" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A96" s="14">
+      <c r="A96" s="1">
         <v>2274</v>
       </c>
       <c r="B96" s="1">
         <v>10</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>268</v>
+        <v>366</v>
       </c>
       <c r="F96" s="1">
         <v>5</v>
@@ -5094,421 +4647,417 @@
         <v>29</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="I96" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="I96" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A97" s="14">
+      <c r="A97" s="1">
         <v>2279</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>219</v>
+        <v>45</v>
       </c>
       <c r="F97" s="1">
         <v>1</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="I97" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="I97" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="142.5" x14ac:dyDescent="0.2">
-      <c r="A98" s="14">
+      <c r="A98" s="1">
         <v>2279</v>
       </c>
       <c r="B98" s="1">
         <v>-6</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>271</v>
+        <v>369</v>
       </c>
       <c r="F98" s="1">
         <v>7</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>272</v>
+        <v>370</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="I98" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="I98" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A99" s="14">
+      <c r="A99" s="1">
         <v>2280</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>273</v>
+        <v>372</v>
       </c>
       <c r="F99" s="1">
         <v>3</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>274</v>
+        <v>373</v>
       </c>
       <c r="H99" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="I99" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="I99" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="43.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="14">
+    <row r="100" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
         <v>2280</v>
       </c>
       <c r="B100" s="1">
         <v>-6</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>423</v>
+        <v>375</v>
       </c>
       <c r="F100" s="1">
         <v>5</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>277</v>
+        <v>376</v>
       </c>
       <c r="H100" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="I100" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="I100" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A101" s="11">
+    <row r="101" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
         <v>2333</v>
       </c>
-      <c r="B101" s="2"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2">
-        <v>0</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="I101" s="13" t="s">
-        <v>279</v>
+      <c r="D101" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F101" s="1">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A102" s="14">
+      <c r="A102" s="1">
         <v>2337</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>283</v>
+        <v>382</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>284</v>
+        <v>383</v>
       </c>
       <c r="F102" s="1">
         <v>3</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="I102" s="16" t="s">
-        <v>279</v>
+        <v>384</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A103" s="14">
+      <c r="A103" s="1">
         <v>2339</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>286</v>
+        <v>385</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>287</v>
+        <v>386</v>
       </c>
       <c r="F103" s="1">
         <v>0</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="I103" s="16" t="s">
-        <v>279</v>
+        <v>387</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A104" s="14">
+      <c r="A104" s="1">
         <v>2343</v>
       </c>
       <c r="B104" s="1">
         <v>5</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>289</v>
+        <v>389</v>
       </c>
       <c r="F104" s="1">
         <v>5</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>293</v>
+        <v>390</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="I104" s="16" t="s">
-        <v>302</v>
+        <v>391</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A105" s="14">
+      <c r="A105" s="1">
         <v>2343</v>
       </c>
       <c r="B105" s="1">
         <v>5</v>
       </c>
-      <c r="C105" s="15">
+      <c r="C105" s="1">
         <v>19</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>294</v>
+        <v>393</v>
       </c>
       <c r="F105" s="1">
         <v>3</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>292</v>
+        <v>394</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="I105" s="16" t="s">
-        <v>302</v>
+        <v>395</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A106" s="14">
+      <c r="A106" s="1">
         <v>2378</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>297</v>
+        <v>396</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>298</v>
+        <v>397</v>
       </c>
       <c r="F106" s="1">
         <v>3</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>296</v>
+        <v>398</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I106" s="16" t="s">
-        <v>303</v>
+        <v>399</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A107" s="14">
+      <c r="A107" s="1">
         <v>2390</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>301</v>
+        <v>401</v>
       </c>
       <c r="F107" s="1">
         <v>0</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>300</v>
+        <v>402</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="I107" s="16" t="s">
-        <v>279</v>
+        <v>403</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A108" s="14">
+      <c r="A108" s="1">
         <v>2397</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>307</v>
+        <v>404</v>
       </c>
       <c r="F108" s="1">
         <v>1</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>306</v>
+        <v>405</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="I108" s="16" t="s">
-        <v>279</v>
+        <v>406</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="57" x14ac:dyDescent="0.2">
-      <c r="A109" s="14">
+      <c r="A109" s="1">
         <v>2399</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>309</v>
+        <v>407</v>
       </c>
       <c r="F109" s="1">
         <v>3</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>310</v>
+        <v>408</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I109" s="16" t="s">
-        <v>329</v>
+        <v>409</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A110" s="14">
+      <c r="A110" s="1">
         <v>2400</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>313</v>
+        <v>411</v>
       </c>
       <c r="F110" s="1">
         <v>1</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="I110" s="16" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="142.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="17">
+        <v>413</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="171" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
         <v>2400</v>
       </c>
-      <c r="B111" s="4">
+      <c r="B111" s="1">
         <v>5</v>
       </c>
-      <c r="C111" s="18">
+      <c r="C111" s="1">
         <v>19</v>
       </c>
-      <c r="D111" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="E111" s="4"/>
-      <c r="F111" s="4">
+      <c r="D111" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="F111" s="1">
         <v>7</v>
       </c>
-      <c r="G111" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="I111" s="19" t="s">
-        <v>304</v>
+      <c r="G111" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A112" s="14">
+      <c r="A112" s="1">
         <v>2400</v>
       </c>
       <c r="B112" s="1">
         <v>-10</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>317</v>
+        <v>418</v>
       </c>
       <c r="F112" s="1">
         <v>0</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="I112" s="16" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A113" s="14">
+        <v>419</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
         <v>2500</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>324</v>
+        <v>421</v>
       </c>
       <c r="F113" s="1">
         <v>0</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>320</v>
+        <v>422</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="I113" s="16" t="s">
-        <v>316</v>
+        <v>423</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A114" s="14">
+      <c r="A114" s="1">
         <v>2687</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>322</v>
+        <v>424</v>
       </c>
       <c r="F114" s="1">
         <v>5</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>323</v>
+        <v>425</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="I114" s="16" t="s">
-        <v>316</v>
+        <v>426</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A115" s="14">
+      <c r="A115" s="1">
         <v>2687</v>
       </c>
       <c r="B115" s="1">
         <v>-2</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>325</v>
+        <v>427</v>
       </c>
       <c r="F115" s="1">
         <v>3</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>326</v>
+        <v>428</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="I115" s="16" t="s">
-        <v>327</v>
+        <v>429</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -5522,9 +5071,9 @@
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.75" style="14" customWidth="1"/>
+    <col min="1" max="1" width="4.75" style="2" customWidth="1"/>
     <col min="2" max="2" width="4.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="3.625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="3.625" style="3" customWidth="1"/>
     <col min="4" max="4" width="16" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="3.5" style="1" customWidth="1"/>
@@ -5534,568 +5083,568 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="22" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="14">
+      <c r="A2" s="2">
         <v>1690</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>383</v>
+        <v>91</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>382</v>
+        <v>90</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>381</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="14">
+      <c r="A3" s="2">
         <v>1704</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>386</v>
+        <v>94</v>
       </c>
       <c r="F3" s="1">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>385</v>
+        <v>93</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>384</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="14">
+      <c r="A4" s="2">
         <v>1807</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>379</v>
+        <v>87</v>
       </c>
       <c r="F4" s="1">
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>387</v>
+        <v>95</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>380</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="14">
+      <c r="A5" s="2">
         <v>1819</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>389</v>
+        <v>97</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>390</v>
+        <v>98</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>388</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+      <c r="A6" s="2">
         <v>1850</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="3">
         <v>6</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>392</v>
+        <v>100</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>393</v>
+        <v>101</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>391</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="14">
+      <c r="A7" s="2">
         <v>1861</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>396</v>
+        <v>104</v>
       </c>
       <c r="F7" s="1">
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>395</v>
+        <v>103</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>394</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="14">
+      <c r="A8" s="2">
         <v>1885</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>400</v>
+        <v>108</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>402</v>
+        <v>110</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>401</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="14">
+      <c r="A9" s="2">
         <v>1886</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>359</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>358</v>
+        <v>66</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>354</v>
+        <v>62</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>355</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="114" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
+      <c r="A10" s="2">
         <v>1887</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>340</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1">
         <v>3</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>339</v>
+        <v>47</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>353</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="14">
+      <c r="A11" s="2">
         <v>1895</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>343</v>
+        <v>51</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>342</v>
+        <v>50</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>341</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="14">
+      <c r="A12" s="2">
         <v>1896</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>346</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>345</v>
+        <v>53</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>344</v>
+        <v>52</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>361</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="14">
+      <c r="A13" s="2">
         <v>1897</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>348</v>
+        <v>56</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>349</v>
+        <v>57</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>347</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A14" s="14">
+      <c r="A14" s="2">
         <v>1899</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>351</v>
+        <v>59</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>352</v>
+        <v>60</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>350</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="114" x14ac:dyDescent="0.2">
-      <c r="A15" s="14">
+      <c r="A15" s="2">
         <v>1900</v>
       </c>
       <c r="B15" s="1">
         <v>4</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="3">
         <v>27</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>356</v>
+        <v>64</v>
       </c>
       <c r="F15" s="1">
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>357</v>
+        <v>65</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>360</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="171" x14ac:dyDescent="0.2">
-      <c r="A16" s="14">
+      <c r="A16" s="2">
         <v>1900</v>
       </c>
       <c r="B16" s="1">
         <v>10</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="3">
         <v>19</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>363</v>
+        <v>71</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>362</v>
+        <v>70</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>364</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="114" x14ac:dyDescent="0.2">
-      <c r="A17" s="14">
+      <c r="A17" s="2">
         <v>1900</v>
       </c>
       <c r="B17" s="1">
         <v>12</v>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="3">
         <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>365</v>
+        <v>73</v>
       </c>
       <c r="F17" s="1">
         <v>7</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>367</v>
+        <v>75</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>366</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="14">
+      <c r="A18" s="2">
         <v>1905</v>
       </c>
       <c r="B18" s="1">
         <v>3</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="3">
         <v>17</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>369</v>
+        <v>77</v>
       </c>
       <c r="F18" s="1">
         <v>3</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>375</v>
+        <v>83</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>368</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A19" s="14">
+      <c r="A19" s="2">
         <v>1905</v>
       </c>
       <c r="B19" s="1">
         <v>6</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="3">
         <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="F19" s="1">
         <v>7</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>372</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="14">
+      <c r="A20" s="2">
         <v>1905</v>
       </c>
       <c r="B20" s="1">
         <v>9</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="3">
         <v>27</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>373</v>
+        <v>81</v>
       </c>
       <c r="F20" s="1">
         <v>5</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>374</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A21" s="14">
+      <c r="A21" s="2">
         <v>1911</v>
       </c>
       <c r="B21" s="1">
         <v>10</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="3">
         <v>30</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>397</v>
+        <v>105</v>
       </c>
       <c r="F21" s="1">
         <v>3</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>399</v>
+        <v>107</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>398</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="114" x14ac:dyDescent="0.2">
-      <c r="A22" s="14">
+      <c r="A22" s="2">
         <v>1913</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>405</v>
+        <v>113</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>404</v>
+        <v>112</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>403</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A23" s="14">
+      <c r="A23" s="2">
         <v>1922</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>408</v>
+        <v>116</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>409</v>
+        <v>117</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>407</v>
+        <v>115</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>406</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="57" x14ac:dyDescent="0.2">
-      <c r="A24" s="14">
+      <c r="A24" s="2">
         <v>1923</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>377</v>
+        <v>85</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>378</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="71.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="14">
+      <c r="A25" s="2">
         <v>1923</v>
       </c>
       <c r="B25" s="1">
         <v>-6</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>416</v>
+        <v>124</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>417</v>
+        <v>125</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>415</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="99.75" x14ac:dyDescent="0.2">
-      <c r="A26" s="14">
+      <c r="A26" s="2">
         <v>1925</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>411</v>
+        <v>119</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>412</v>
+        <v>120</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>410</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="85.5" x14ac:dyDescent="0.2">
-      <c r="A27" s="14">
+      <c r="A27" s="2">
         <v>1925</v>
       </c>
       <c r="B27" s="1">
         <v>4</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="3">
         <v>27</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>419</v>
+        <v>127</v>
       </c>
       <c r="F27" s="1">
         <v>5</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>420</v>
+        <v>128</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>418</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A28" s="14">
+      <c r="A28" s="2">
         <v>1925</v>
       </c>
       <c r="B28" s="1">
         <v>-9</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>421</v>
+        <v>129</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>422</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
-      <c r="A29" s="14">
+      <c r="A29" s="2">
         <v>1927</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>414</v>
+        <v>122</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>413</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/CSV/Timelines.xlsx
+++ b/CSV/Timelines.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1Data\1study\WebLearn\Timeline\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19670D99-869C-49C4-83EE-22675266AA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7A8802-1BEE-4361-8EB2-AF50451E2FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5205" yWindow="2625" windowWidth="28800" windowHeight="15885" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" activeTab="1" xr2:uid="{A53E62BE-B75E-4C3C-A768-5CF0DB6D2C01}"/>
   </bookViews>
   <sheets>
     <sheet name="ThreeBody" sheetId="1" r:id="rId1"/>
-    <sheet name="Physics" sheetId="2" r:id="rId2"/>
+    <sheet name="ChineseHistory" sheetId="3" r:id="rId2"/>
+    <sheet name="WorldHistory" sheetId="4" r:id="rId3"/>
+    <sheet name="Physics" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="767">
   <si>
     <t>Year</t>
   </si>
@@ -1541,6 +1543,1014 @@
   </si>
   <si>
     <t>黑域纪元</t>
+  </si>
+  <si>
+    <t>夏朝建立</t>
+  </si>
+  <si>
+    <t>禹建立夏朝，中国历史上第一个王朝</t>
+  </si>
+  <si>
+    <t>禹建立夏朝，标志着中国从原始社会进入奴隶社会，是中国历史上第一个世袭制王朝。</t>
+  </si>
+  <si>
+    <t>上古</t>
+  </si>
+  <si>
+    <t>商朝建立</t>
+  </si>
+  <si>
+    <t>汤灭夏建立商朝，青铜器文明兴盛</t>
+  </si>
+  <si>
+    <t>汤灭夏建立商朝，商朝是中国历史上第二个王朝，青铜器文明高度发展，甲骨文出现。</t>
+  </si>
+  <si>
+    <t>西周建立</t>
+  </si>
+  <si>
+    <t>武王伐纣建立西周，分封制确立</t>
+  </si>
+  <si>
+    <t>周武王姬发伐纣灭商，建立西周，实行分封制和宗法制，奠定了中国古代政治制度基础。</t>
+  </si>
+  <si>
+    <t>先秦</t>
+  </si>
+  <si>
+    <t>东周开始</t>
+  </si>
+  <si>
+    <t>周平王东迁洛邑，春秋战国时期开始</t>
+  </si>
+  <si>
+    <t>周平王东迁洛邑，东周开始，分为春秋和战国两个时期，礼崩乐坏，诸侯争霸。</t>
+  </si>
+  <si>
+    <t>秦朝建立</t>
+  </si>
+  <si>
+    <t>秦始皇统一六国，建立中央集权帝国</t>
+  </si>
+  <si>
+    <t>秦始皇嬴政灭六国统一中国，废除分封制实行郡县制，统一文字、货币、度量衡，修筑长城。</t>
+  </si>
+  <si>
+    <t>秦汉</t>
+  </si>
+  <si>
+    <t>西汉建立</t>
+  </si>
+  <si>
+    <t>刘邦击败项羽建立西汉，定都长安</t>
+  </si>
+  <si>
+    <t>刘邦在楚汉之争中击败项羽，建立西汉王朝，定都长安，实行休养生息政策，开创文景之治。</t>
+  </si>
+  <si>
+    <t>王莽篡汉</t>
+  </si>
+  <si>
+    <t>王莽篡汉建立新朝，西汉灭亡</t>
+  </si>
+  <si>
+    <t>王莽篡汉建立新朝，推行新政改革，但改革失败引发社会动荡，绿林赤眉起义爆发。</t>
+  </si>
+  <si>
+    <t>东汉建立</t>
+  </si>
+  <si>
+    <t>刘秀建立东汉，定都洛阳，光武中兴</t>
+  </si>
+  <si>
+    <t>刘秀击败王莽和各路起义军，建立东汉，定都洛阳，开创光武中兴，东汉延续近两百年。</t>
+  </si>
+  <si>
+    <t>曹魏建立</t>
+  </si>
+  <si>
+    <t>曹丕篡汉建立曹魏，东汉灭亡</t>
+  </si>
+  <si>
+    <t>曹丕逼迫汉献帝禅位，建立曹魏，东汉灭亡，三国时代正式开始。</t>
+  </si>
+  <si>
+    <t>三国两晋南北朝</t>
+  </si>
+  <si>
+    <t>蜀汉建立</t>
+  </si>
+  <si>
+    <t>刘备在成都称帝建立蜀汉</t>
+  </si>
+  <si>
+    <t>刘备在成都称帝，国号汉，史称蜀汉，以兴复汉室为旗帜，诸葛亮辅政。</t>
+  </si>
+  <si>
+    <t>东吴建立</t>
+  </si>
+  <si>
+    <t>孙权称帝建立东吴</t>
+  </si>
+  <si>
+    <t>孙权在武昌称帝，国号吴，后迁都建业，三国鼎立局面正式形成。</t>
+  </si>
+  <si>
+    <t>西晋建立</t>
+  </si>
+  <si>
+    <t>司马炎篡魏建立西晋</t>
+  </si>
+  <si>
+    <t>司马炎逼迫魏元帝禅位，建立西晋，后灭东吴统一中国，结束三国分裂局面。</t>
+  </si>
+  <si>
+    <t>西晋灭亡</t>
+  </si>
+  <si>
+    <t>匈奴攻破长安，西晋灭亡</t>
+  </si>
+  <si>
+    <t>匈奴攻破长安，晋愍帝投降，西晋灭亡，司马氏南渡，中国北方进入五胡十六国时期。</t>
+  </si>
+  <si>
+    <t>东晋建立</t>
+  </si>
+  <si>
+    <t>司马睿建立东晋，定都建康</t>
+  </si>
+  <si>
+    <t>司马睿在建康称帝建立东晋，偏安江南，与北方五胡十六国对峙，门阀政治兴盛。</t>
+  </si>
+  <si>
+    <t>刘宋建立</t>
+  </si>
+  <si>
+    <t>刘裕篡晋建立刘宋，南朝开始</t>
+  </si>
+  <si>
+    <t>刘裕逼迫晋恭帝禅位，建立刘宋，南朝开始，南方进入宋齐梁陈四朝更替时期。</t>
+  </si>
+  <si>
+    <t>北魏统一北方</t>
+  </si>
+  <si>
+    <t>北魏统一</t>
+  </si>
+  <si>
+    <t>北魏统一北方，北朝开始</t>
+  </si>
+  <si>
+    <t>北魏太武帝拓跋焘统一北方，北朝开始，中国进入南北朝对峙时期。</t>
+  </si>
+  <si>
+    <t>隋朝建立</t>
+  </si>
+  <si>
+    <t>杨坚建立隋朝，北周灭亡</t>
+  </si>
+  <si>
+    <t>杨坚逼迫北周静帝禅位，建立隋朝，后灭南陈统一中国，结束近三百年的分裂局面。</t>
+  </si>
+  <si>
+    <t>隋唐</t>
+  </si>
+  <si>
+    <t>唐朝建立</t>
+  </si>
+  <si>
+    <t>李渊建立唐朝，开启中国古代最辉煌时代</t>
+  </si>
+  <si>
+    <t>李渊在晋阳起兵，攻入长安建立唐朝，唐朝是中国古代最强盛的朝代之一，开创贞观之治和开元盛世。</t>
+  </si>
+  <si>
+    <t>唐朝灭亡</t>
+  </si>
+  <si>
+    <t>朱温篡唐建立后梁，五代十国开始</t>
+  </si>
+  <si>
+    <t>朱温逼迫唐哀帝禅位，建立后梁，唐朝灭亡，中国进入五代十国分裂时期。</t>
+  </si>
+  <si>
+    <t>五代十国</t>
+  </si>
+  <si>
+    <t>北宋建立</t>
+  </si>
+  <si>
+    <t>赵匡胤发动陈桥兵变建立北宋</t>
+  </si>
+  <si>
+    <t>赵匡胤发动陈桥兵变，黄袍加身建立北宋，定都开封，后逐步统一全国（除辽和西夏）。</t>
+  </si>
+  <si>
+    <t>宋元</t>
+  </si>
+  <si>
+    <t>南宋建立</t>
+  </si>
+  <si>
+    <t>赵构建立南宋，定都临安</t>
+  </si>
+  <si>
+    <t>靖康之变后，赵构在南京应天府即位，后定都临安，偏安江南，与金朝对峙。</t>
+  </si>
+  <si>
+    <t>元朝建立</t>
+  </si>
+  <si>
+    <t>忽必烈建立元朝，定都大都</t>
+  </si>
+  <si>
+    <t>忽必烈改国号为大元，建立元朝，成为中国历史上第一个由少数民族建立的大一统王朝。</t>
+  </si>
+  <si>
+    <t>元朝统一中国</t>
+  </si>
+  <si>
+    <t>元朝统一</t>
+  </si>
+  <si>
+    <t>元军灭南宋，统一中国</t>
+  </si>
+  <si>
+    <t>元军在崖山海战中击败南宋军队，南宋灭亡，元朝统一中国，结束自唐末以来长期分裂局面。</t>
+  </si>
+  <si>
+    <t>明朝建立</t>
+  </si>
+  <si>
+    <t>朱元璋建立明朝，推翻元朝统治</t>
+  </si>
+  <si>
+    <t>朱元璋在应天府称帝建立明朝，后北伐推翻元朝统治，恢复汉人政权，永乐年间迁都北京。</t>
+  </si>
+  <si>
+    <t>明清</t>
+  </si>
+  <si>
+    <t>清朝入关</t>
+  </si>
+  <si>
+    <t>清军入关定都北京，建立全国性政权</t>
+  </si>
+  <si>
+    <t>李自成攻陷北京，明朝灭亡，吴三桂引清军入关，清军击败李自成后定都北京，建立全国性政权。</t>
+  </si>
+  <si>
+    <t>清朝灭亡</t>
+  </si>
+  <si>
+    <t>清帝退位，中国两千多年帝制终结</t>
+  </si>
+  <si>
+    <t>溥仪颁布退位诏书，清朝灭亡，中国延续两千多年的封建帝制终结。</t>
+  </si>
+  <si>
+    <t>近代</t>
+  </si>
+  <si>
+    <t>中华民国成立</t>
+  </si>
+  <si>
+    <t>民国成立</t>
+  </si>
+  <si>
+    <t>孙中山就任临时大总统，中华民国成立</t>
+  </si>
+  <si>
+    <t>孙中山在南京就任中华民国临时大总统，宣告中华民国成立，中国进入共和时代。</t>
+  </si>
+  <si>
+    <t>中华人民共和国成立</t>
+  </si>
+  <si>
+    <t>新中国成立</t>
+  </si>
+  <si>
+    <t>中华人民共和国成立，中国人民站起来</t>
+  </si>
+  <si>
+    <t>毛泽东在北京天安门宣告中华人民共和国成立，中国人民从此站起来了，中国历史进入新纪元。</t>
+  </si>
+  <si>
+    <t>现代</t>
+  </si>
+  <si>
+    <t>古埃及统一</t>
+  </si>
+  <si>
+    <t>美尼斯统一上下埃及，古埃及王朝开始</t>
+  </si>
+  <si>
+    <t>美尼斯（那尔迈）统一上下埃及，建立第一王朝，古埃及文明开始，成为世界最早的大一统国家之一。</t>
+  </si>
+  <si>
+    <t>古代文明</t>
+  </si>
+  <si>
+    <t>阿卡德帝国建立</t>
+  </si>
+  <si>
+    <t>阿卡德帝国</t>
+  </si>
+  <si>
+    <t>萨尔贡建立阿卡德帝国，两河流域首次统一</t>
+  </si>
+  <si>
+    <t>萨尔贡大帝建立阿卡德帝国，统一两河流域，是人类历史上第一个多民族帝国，使用阿卡德语。</t>
+  </si>
+  <si>
+    <t>汉谟拉比法典</t>
+  </si>
+  <si>
+    <t>古巴比伦颁布汉谟拉比法典，世界最早成文法典</t>
+  </si>
+  <si>
+    <t>古巴比伦国王汉谟拉比颁布法典，刻于石柱之上，是世界上现存最早的成文法典之一，以眼还眼以牙还牙。</t>
+  </si>
+  <si>
+    <t>雅利安人入印度</t>
+  </si>
+  <si>
+    <t>雅利安入印度</t>
+  </si>
+  <si>
+    <t>雅利安人进入印度，种姓制度开始形成</t>
+  </si>
+  <si>
+    <t>雅利安人从西北方进入印度次大陆，征服达罗毗荼人，建立吠陀文明，种姓制度开始形成。</t>
+  </si>
+  <si>
+    <t>第一届古代奥运会</t>
+  </si>
+  <si>
+    <t>古代奥运会</t>
+  </si>
+  <si>
+    <t>希腊举办第一届古代奥林匹克运动会</t>
+  </si>
+  <si>
+    <t>希腊奥林匹亚举办第一届古代奥林匹克运动会，成为希腊各城邦共同的宗教和体育盛会，四年一届。</t>
+  </si>
+  <si>
+    <t>罗马共和国建立</t>
+  </si>
+  <si>
+    <t>罗马共和国</t>
+  </si>
+  <si>
+    <t>罗马推翻王政建立共和国，元老院掌权</t>
+  </si>
+  <si>
+    <t>罗马人推翻塔克文王朝，建立罗马共和国，由元老院和执政官共同治理，持续近五百年。</t>
+  </si>
+  <si>
+    <t>亚历山大继位</t>
+  </si>
+  <si>
+    <t>亚历山大继位，开始东征建立帝国</t>
+  </si>
+  <si>
+    <t>亚历山大继位马其顿国王，开始十年东征，灭波斯建立地跨欧亚非三大洲的亚历山大帝国。</t>
+  </si>
+  <si>
+    <t>罗马帝国建立</t>
+  </si>
+  <si>
+    <t>罗马帝国</t>
+  </si>
+  <si>
+    <t>屋大维成为奥古斯都，罗马帝国开始</t>
+  </si>
+  <si>
+    <t>屋大维获得奥古斯都称号，罗马从共和国转变为帝国，开启罗马和平时期，疆域达到最大。</t>
+  </si>
+  <si>
+    <t>维苏威火山爆发</t>
+  </si>
+  <si>
+    <t>维苏威爆发</t>
+  </si>
+  <si>
+    <t>维苏威火山爆发，庞贝古城被掩埋</t>
+  </si>
+  <si>
+    <t>维苏威火山爆发，庞贝、赫库兰尼姆等古城被火山灰掩埋，成为研究古罗马生活的重要遗址。</t>
+  </si>
+  <si>
+    <t>米兰敕令颁布</t>
+  </si>
+  <si>
+    <t>米兰敕令</t>
+  </si>
+  <si>
+    <t>君士坦丁颁布米兰敕令，基督教合法化</t>
+  </si>
+  <si>
+    <t>罗马皇帝君士坦丁颁布米兰敕令，承认基督教合法地位，基督教逐渐成为罗马国教。</t>
+  </si>
+  <si>
+    <t>君士坦丁堡建立</t>
+  </si>
+  <si>
+    <t>君士坦丁堡</t>
+  </si>
+  <si>
+    <t>君士坦丁迁都拜占庭，建立君士坦丁堡</t>
+  </si>
+  <si>
+    <t>君士坦丁大帝迁都拜占庭，改名为君士坦丁堡，成为东罗马帝国首都，延续千年。</t>
+  </si>
+  <si>
+    <t>西罗马帝国灭亡</t>
+  </si>
+  <si>
+    <t>西罗马灭亡</t>
+  </si>
+  <si>
+    <t>西罗马帝国灭亡，欧洲进入中世纪</t>
+  </si>
+  <si>
+    <t>日耳曼雇佣兵首领奥多亚克废黜最后一位西罗马皇帝罗慕路斯，西罗马帝国灭亡。</t>
+  </si>
+  <si>
+    <t>法兰克王国建立</t>
+  </si>
+  <si>
+    <t>法兰克王国</t>
+  </si>
+  <si>
+    <t>克洛维建立法兰克王国，皈依基督教</t>
+  </si>
+  <si>
+    <t>克洛维统一法兰克各部，建立墨洛温王朝，皈依天主教，奠定西欧封建国家基础。</t>
+  </si>
+  <si>
+    <t>查士丁尼继位</t>
+  </si>
+  <si>
+    <t>查士丁尼成为东罗马皇帝，编纂罗马法典</t>
+  </si>
+  <si>
+    <t>查士丁尼一世继位，编纂《查士丁尼法典》，收复意大利和北非，重建罗马帝国疆域。</t>
+  </si>
+  <si>
+    <t>伊斯兰教创立</t>
+  </si>
+  <si>
+    <t>穆罕默德迁徙麦地那，伊斯兰教历开始</t>
+  </si>
+  <si>
+    <t>穆罕默德从麦加迁徙麦地那（希吉拉），伊斯兰教历元年，伊斯兰教在阿拉伯半岛迅速传播。</t>
+  </si>
+  <si>
+    <t>阿拔斯王朝建立</t>
+  </si>
+  <si>
+    <t>阿拔斯王朝</t>
+  </si>
+  <si>
+    <t>阿拔斯王朝建立，阿拉伯帝国黄金时代</t>
+  </si>
+  <si>
+    <t>阿拔斯推翻倭马亚王朝，建立新王朝，定都巴格达，阿拉伯帝国进入科学文化黄金时代。</t>
+  </si>
+  <si>
+    <t>查理曼加冕</t>
+  </si>
+  <si>
+    <t>查理曼加冕为罗马皇帝，法兰克帝国鼎盛</t>
+  </si>
+  <si>
+    <t>教皇利奥三世为查理曼加冕为"罗马人的皇帝"，西欧统一，加洛林文艺复兴开始。</t>
+  </si>
+  <si>
+    <t>凡尔登条约</t>
+  </si>
+  <si>
+    <t>凡尔登条约签订，查理曼帝国三分</t>
+  </si>
+  <si>
+    <t>查理曼三个孙子签订凡尔登条约，帝国分为西法兰克、中法兰克、东法兰克，奠定德法意雏形。</t>
+  </si>
+  <si>
+    <t>神圣罗马帝国建立</t>
+  </si>
+  <si>
+    <t>神圣罗马帝国</t>
+  </si>
+  <si>
+    <t>奥托一世加冕，神圣罗马帝国开始</t>
+  </si>
+  <si>
+    <t>德意志国王奥托一世被教皇约翰十二世加冕为罗马皇帝，神圣罗马帝国开始，持续至1806年。</t>
+  </si>
+  <si>
+    <t>东西教会大分裂</t>
+  </si>
+  <si>
+    <t>东西教会分裂</t>
+  </si>
+  <si>
+    <t>基督教正式分裂为天主教和东正教</t>
+  </si>
+  <si>
+    <t>罗马教皇与君士坦丁堡普世牧首互相绝罚，基督教正式分裂为西方天主教和东方东正教。</t>
+  </si>
+  <si>
+    <t>诺曼征服英格兰</t>
+  </si>
+  <si>
+    <t>诺曼征服</t>
+  </si>
+  <si>
+    <t>诺曼底公爵威廉征服英格兰</t>
+  </si>
+  <si>
+    <t>诺曼底公爵威廉在黑斯廷斯战役中击败哈罗德，成为英格兰国王，英格兰封建化开始。</t>
+  </si>
+  <si>
+    <t>十字军东征开始</t>
+  </si>
+  <si>
+    <t>十字军东征</t>
+  </si>
+  <si>
+    <t>第一次十字军东征开始，持续近两百年</t>
+  </si>
+  <si>
+    <t>教皇乌尔班二世号召收复耶路撒冷，第一次十字军东征开始，持续近两百年，共八次主要东征。</t>
+  </si>
+  <si>
+    <t>成吉思汗统一蒙古</t>
+  </si>
+  <si>
+    <t>成吉思汗统一</t>
+  </si>
+  <si>
+    <t>成吉思汗统一蒙古各部，蒙古帝国开始</t>
+  </si>
+  <si>
+    <t>铁木真统一蒙古各部，被推举为大汗，称成吉思汗，开始大规模对外扩张，建立世界最大帝国。</t>
+  </si>
+  <si>
+    <t>大宪章签署</t>
+  </si>
+  <si>
+    <t>英王约翰签署大宪章，限制王权</t>
+  </si>
+  <si>
+    <t>英格兰国王约翰在贵族压力下签署《大宪章》，确立王在法下原则，成为宪政主义源头。</t>
+  </si>
+  <si>
+    <t>黑死病爆发</t>
+  </si>
+  <si>
+    <t>黑死病席卷欧洲，造成数千万人死亡</t>
+  </si>
+  <si>
+    <t>鼠疫从克里米亚传入欧洲，在四年内造成约三分之一欧洲人口死亡，深刻改变欧洲社会。</t>
+  </si>
+  <si>
+    <t>奥斯曼攻陷君士坦丁堡，东罗马灭亡</t>
+  </si>
+  <si>
+    <t>奥斯曼土耳其攻陷君士坦丁堡，东罗马帝国灭亡，千年帝国终结，文艺复兴加速。</t>
+  </si>
+  <si>
+    <t>英法百年战争结束</t>
+  </si>
+  <si>
+    <t>百年战争结束</t>
+  </si>
+  <si>
+    <t>英法百年战争结束，法国统一</t>
+  </si>
+  <si>
+    <t>英法百年战争结束，英国失去大陆领土，法兰西民族国家形成，火炮改变战争方式。</t>
+  </si>
+  <si>
+    <t>哥伦布发现新大陆</t>
+  </si>
+  <si>
+    <t>哥伦布发现美洲</t>
+  </si>
+  <si>
+    <t>哥伦布抵达美洲，开启大航海时代</t>
+  </si>
+  <si>
+    <t>哥伦布率领船队抵达美洲，开启欧洲大航海时代和地理大发现，世界联系日益紧密。</t>
+  </si>
+  <si>
+    <t>近代早期</t>
+  </si>
+  <si>
+    <t>达·伽马抵达印度</t>
+  </si>
+  <si>
+    <t>达·伽马到印度</t>
+  </si>
+  <si>
+    <t>达·伽马开辟欧亚海上航线</t>
+  </si>
+  <si>
+    <t>葡萄牙航海家达·伽马绕过好望角抵达印度，开辟欧洲到亚洲的海上航线，开启欧洲殖民时代。</t>
+  </si>
+  <si>
+    <t>宗教改革开始</t>
+  </si>
+  <si>
+    <t>宗教改革</t>
+  </si>
+  <si>
+    <t>马丁·路德发表九十五条论纲</t>
+  </si>
+  <si>
+    <t>马丁·路德在维滕贝格教堂张贴九十五条论纲，挑战罗马教廷权威，欧洲宗教改革运动开始。</t>
+  </si>
+  <si>
+    <t>麦哲伦环球航行</t>
+  </si>
+  <si>
+    <t>麦哲伦环球</t>
+  </si>
+  <si>
+    <t>麦哲伦船队开始环球航行</t>
+  </si>
+  <si>
+    <t>麦哲伦率领船队从西班牙出发，寻找西行到亚洲的航线，虽麦哲伦死于菲律宾，但船队完成首次环球航行。</t>
+  </si>
+  <si>
+    <t>威斯特伐利亚和约</t>
+  </si>
+  <si>
+    <t>威斯特伐利亚</t>
+  </si>
+  <si>
+    <t>三十年战争结束，现代国际关系体系确立</t>
+  </si>
+  <si>
+    <t>三十年战争结束，签订威斯特伐利亚和约，确立国家主权平等原则，现代国际体系开端。</t>
+  </si>
+  <si>
+    <t>光荣革命</t>
+  </si>
+  <si>
+    <t>英国光荣革命，确立议会主权</t>
+  </si>
+  <si>
+    <t>英国爆发光荣革命，詹姆士二世被废，威廉和玛丽继位，确立议会高于王权，君主立宪制形成。</t>
+  </si>
+  <si>
+    <t>美国独立宣言</t>
+  </si>
+  <si>
+    <t>美国独立</t>
+  </si>
+  <si>
+    <t>美国发表独立宣言，脱离英国独立</t>
+  </si>
+  <si>
+    <t>北美十三州发表独立宣言，美利坚合众国诞生，启蒙思想首次在大国实践，影响世界历史进程。</t>
+  </si>
+  <si>
+    <t>法国大革命爆发</t>
+  </si>
+  <si>
+    <t>法国大革命</t>
+  </si>
+  <si>
+    <t>巴士底狱被攻占，法国大革命开始</t>
+  </si>
+  <si>
+    <t>巴黎民众攻占巴士底狱，法国大革命爆发，发表人权宣言，推翻封建专制，传播自由平等思想。</t>
+  </si>
+  <si>
+    <t>拿破仑称帝</t>
+  </si>
+  <si>
+    <t>拿破仑加冕为法兰西皇帝</t>
+  </si>
+  <si>
+    <t>拿破仑加冕为法兰西皇帝，建立法兰西第一帝国，颁布拿破仑法典，对外进行大规模军事扩张。</t>
+  </si>
+  <si>
+    <t>滑铁卢战役</t>
+  </si>
+  <si>
+    <t>拿破仑兵败滑铁卢，帝国终结</t>
+  </si>
+  <si>
+    <t>拿破仑在滑铁卢战役中惨败，被流放圣赫勒拿岛，法兰西第一帝国灭亡，维也纳体系建立。</t>
+  </si>
+  <si>
+    <t>欧洲革命浪潮</t>
+  </si>
+  <si>
+    <t>1848年革命</t>
+  </si>
+  <si>
+    <t>欧洲多国爆发革命，民族主义高涨</t>
+  </si>
+  <si>
+    <t>法国、德意志、意大利等多国爆发革命，要求宪政改革和民族统一，虽多失败但推动欧洲变革。</t>
+  </si>
+  <si>
+    <t>美国内战爆发</t>
+  </si>
+  <si>
+    <t>美国内战</t>
+  </si>
+  <si>
+    <t>美国南北战争爆发，维护国家统一</t>
+  </si>
+  <si>
+    <t>南方各州脱离联邦，美国内战爆发，林肯领导北方获胜，废除奴隶制，美国现代化加速。</t>
+  </si>
+  <si>
+    <t>明治维新开始</t>
+  </si>
+  <si>
+    <t>明治维新</t>
+  </si>
+  <si>
+    <t>日本明治维新开始，走向现代化</t>
+  </si>
+  <si>
+    <t>日本推翻幕府统治，明治天皇亲政，实行一系列现代化改革，日本迅速崛起为亚洲强国。</t>
+  </si>
+  <si>
+    <t>德意志帝国建立</t>
+  </si>
+  <si>
+    <t>德意志统一</t>
+  </si>
+  <si>
+    <t>德意志帝国建立，德国统一完成</t>
+  </si>
+  <si>
+    <t>普鲁士国王威廉一世在凡尔赛宫加冕为德意志皇帝，德意志统一完成，欧洲力量格局巨变。</t>
+  </si>
+  <si>
+    <t>一战爆发</t>
+  </si>
+  <si>
+    <t>一战全面爆发，人类首次世界大战</t>
+  </si>
+  <si>
+    <t>奥匈帝国向塞尔维亚宣战，第一次世界大战全面爆发，造成约1700万人死亡，四大帝国崩溃。</t>
+  </si>
+  <si>
+    <t>20世纪</t>
+  </si>
+  <si>
+    <t>十月革命</t>
+  </si>
+  <si>
+    <t>俄国十月革命，首个社会主义国家</t>
+  </si>
+  <si>
+    <t>列宁领导布尔什维克夺取政权，建立世界上第一个社会主义国家，对世界历史产生深远影响。</t>
+  </si>
+  <si>
+    <t>一战结束</t>
+  </si>
+  <si>
+    <t>德国投降，第一次世界大战结束</t>
+  </si>
+  <si>
+    <t>德国签署停战协定，一战结束，凡尔赛体系建立，为二战埋下隐患。</t>
+  </si>
+  <si>
+    <t>经济大萧条</t>
+  </si>
+  <si>
+    <t>华尔街股灾，全球经济大萧条开始</t>
+  </si>
+  <si>
+    <t>美国华尔街股市崩盘，引发全球经济大萧条，失业率飙升，法西斯主义趁机兴起。</t>
+  </si>
+  <si>
+    <t>二战爆发</t>
+  </si>
+  <si>
+    <t>德国入侵波兰，第二次世界大战爆发</t>
+  </si>
+  <si>
+    <t>德国入侵波兰，英法对德宣战，二战全面爆发，是人类历史上规模最大的战争。</t>
+  </si>
+  <si>
+    <t>珍珠港事件</t>
+  </si>
+  <si>
+    <t>日本偷袭珍珠港，美国参战</t>
+  </si>
+  <si>
+    <t>日本偷袭美国珍珠港，太平洋战争爆发，美国对日德意宣战，二战达到真正全球性规模。</t>
+  </si>
+  <si>
+    <t>二战欧洲胜利</t>
+  </si>
+  <si>
+    <t>二战欧战胜利</t>
+  </si>
+  <si>
+    <t>德国投降，二战欧洲战场结束</t>
+  </si>
+  <si>
+    <t>德国无条件投降，二战欧洲战场结束，纳粹德国覆灭，希特勒自杀身亡。</t>
+  </si>
+  <si>
+    <t>二战结束</t>
+  </si>
+  <si>
+    <t>日本投降，第二次世界大战结束</t>
+  </si>
+  <si>
+    <t>日本宣布无条件投降，二战结束，造成约7000万人死亡，联合国成立，冷战格局形成。</t>
+  </si>
+  <si>
+    <t>冷战开始</t>
+  </si>
+  <si>
+    <t>杜鲁门主义出台，美苏冷战开始</t>
+  </si>
+  <si>
+    <t>美国提出杜鲁门主义，遏制共产主义，标志着美苏冷战正式开始，世界分为两大阵营。</t>
+  </si>
+  <si>
+    <t>古巴导弹危机</t>
+  </si>
+  <si>
+    <t>美苏古巴对峙，核战争一触即发</t>
+  </si>
+  <si>
+    <t>美苏因古巴导弹陷入严重对峙，核战争一触即发，最终苏联撤除导弹，是冷战最接近核战争的危机。</t>
+  </si>
+  <si>
+    <t>柏林墙倒塌</t>
+  </si>
+  <si>
+    <t>柏林墙倒塌，冷战结束象征</t>
+  </si>
+  <si>
+    <t>东德开放柏林墙，民众自由穿越，成为冷战结束的象征，德国统一进程开始。</t>
+  </si>
+  <si>
+    <t>苏联解体</t>
+  </si>
+  <si>
+    <t>苏联解体，冷战结束，两极终结</t>
+  </si>
+  <si>
+    <t>苏联正式解体，冷战结束，美苏两极格局终结，世界进入多极化时代。</t>
+  </si>
+  <si>
+    <t>911事件</t>
+  </si>
+  <si>
+    <t>美国遭恐怖袭击，反恐战争开始</t>
+  </si>
+  <si>
+    <t>恐怖分子劫持飞机撞击世贸中心和五角大楼，近3000人死亡，美国发动全球反恐战争。</t>
+  </si>
+  <si>
+    <t>21世纪</t>
+  </si>
+  <si>
+    <t>抗美援朝战争开始</t>
+  </si>
+  <si>
+    <t>抗美援朝</t>
+  </si>
+  <si>
+    <t>中国人民志愿军入朝参战，抗美援朝战争开始</t>
+  </si>
+  <si>
+    <t>中国人民志愿军跨过鸭绿江入朝参战，与朝鲜人民军共同抗击美国为首的联合国军，保卫新中国安全。</t>
+  </si>
+  <si>
+    <t>朝鲜战争停战协定</t>
+  </si>
+  <si>
+    <t>朝鲜停战</t>
+  </si>
+  <si>
+    <t>朝鲜战争停战协定签署，抗美援朝战争结束</t>
+  </si>
+  <si>
+    <t>朝鲜战争停战协定在板门店签署，历时三年的抗美援朝战争结束，中国赢得和平发展环境。</t>
+  </si>
+  <si>
+    <t>三大改造完成</t>
+  </si>
+  <si>
+    <t>三大改造</t>
+  </si>
+  <si>
+    <t>三大改造完成，社会主义制度确立</t>
+  </si>
+  <si>
+    <t>对农业、手工业和资本主义工商业的社会主义改造基本完成，中国确立社会主义制度，进入社会主义初级阶段。</t>
+  </si>
+  <si>
+    <t>文化大革命开始</t>
+  </si>
+  <si>
+    <t>文革开始</t>
+  </si>
+  <si>
+    <t>文化大革命开始，中国社会十年动乱</t>
+  </si>
+  <si>
+    <t>文化大革命开始，中国进入长达十年的动乱时期，国民经济和社会发展遭受严重破坏。</t>
+  </si>
+  <si>
+    <t>文化大革命结束</t>
+  </si>
+  <si>
+    <t>文革结束</t>
+  </si>
+  <si>
+    <t>粉碎四人帮，文化大革命结束</t>
+  </si>
+  <si>
+    <t>华国锋、叶剑英等采取果断措施粉碎四人帮，持续十年的文化大革命结束，中国进入新的历史时期。</t>
+  </si>
+  <si>
+    <t>改革开放开始</t>
+  </si>
+  <si>
+    <t>改革开放</t>
+  </si>
+  <si>
+    <t>十一届三中全会召开，改革开放开始</t>
+  </si>
+  <si>
+    <t>十一届三中全会在北京召开，确立以经济建设为中心，开启改革开放伟大征程，中国进入现代化建设新时期。</t>
+  </si>
+  <si>
+    <t>香港回归祖国</t>
+  </si>
+  <si>
+    <t>香港回归</t>
+  </si>
+  <si>
+    <t>中国政府恢复对香港行使主权</t>
+  </si>
+  <si>
+    <t>中国政府对香港恢复行使主权，香港回归祖国怀抱，一国两制方针成功实践，洗雪百年国耻。</t>
+  </si>
+  <si>
+    <t>澳门回归祖国</t>
+  </si>
+  <si>
+    <t>澳门回归</t>
+  </si>
+  <si>
+    <t>中国政府恢复对澳门行使主权</t>
+  </si>
+  <si>
+    <t>中国政府对澳门恢复行使主权，澳门回归祖国，结束了葡萄牙在澳门的殖民统治。</t>
+  </si>
+  <si>
+    <t>中国加入WTO</t>
+  </si>
+  <si>
+    <t>加入WTO</t>
+  </si>
+  <si>
+    <t>中国正式加入世界贸易组织</t>
+  </si>
+  <si>
+    <t>中国正式加入世界贸易组织，全面融入全球经济体系，标志着中国对外开放进入新阶段。</t>
+  </si>
+  <si>
+    <t>北京奥运会举办</t>
+  </si>
+  <si>
+    <t>北京奥运会</t>
+  </si>
+  <si>
+    <t>北京成功举办夏季奥运会</t>
+  </si>
+  <si>
+    <t>北京成功举办第29届夏季奥林匹克运动会，展示了中国改革开放成就，是中国走向世界的重要标志。</t>
+  </si>
+  <si>
+    <t>新时代开始</t>
+  </si>
+  <si>
+    <t>新时代</t>
+  </si>
+  <si>
+    <t>中共十八大召开，中国特色社会主义进入新时代</t>
+  </si>
+  <si>
+    <t>中共十八大召开，提出实现中华民族伟大复兴的中国梦，中国特色社会主义进入新时代。</t>
   </si>
 </sst>
 </file>
@@ -5067,6 +6077,2324 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC43D79B-B707-4230-A67C-37C366F99C3A}">
+  <dimension ref="A1:I40"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="5.25" style="1" customWidth="1"/>
+    <col min="3" max="3" width="3.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="22.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="45.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>-2070</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F2" s="1">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>-1600</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="F3" s="1">
+        <v>5</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>-1046</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>-770</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>-221</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="F6" s="1">
+        <v>7</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>-206</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>25</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>220</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>221</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>229</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>266</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="F13" s="1">
+        <v>5</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>316</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>317</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>420</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>439</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>581</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F18" s="1">
+        <v>5</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>618</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="F19" s="1">
+        <v>7</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>907</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>960</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="F21" s="1">
+        <v>5</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>1127</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>1271</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>1279</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="F24" s="1">
+        <v>7</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>1368</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="F25" s="1">
+        <v>7</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>1644</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>1912</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2</v>
+      </c>
+      <c r="C27" s="1">
+        <v>12</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>1912</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>1949</v>
+      </c>
+      <c r="B29" s="1">
+        <v>10</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="F29" s="1">
+        <v>7</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>1950</v>
+      </c>
+      <c r="B30" s="1">
+        <v>10</v>
+      </c>
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="F30" s="1">
+        <v>5</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>1953</v>
+      </c>
+      <c r="B31" s="1">
+        <v>7</v>
+      </c>
+      <c r="C31" s="1">
+        <v>27</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>1956</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="F32" s="1">
+        <v>5</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>1966</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>1976</v>
+      </c>
+      <c r="B34" s="1">
+        <v>10</v>
+      </c>
+      <c r="C34" s="1">
+        <v>6</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>1978</v>
+      </c>
+      <c r="B35" s="1">
+        <v>12</v>
+      </c>
+      <c r="C35" s="1">
+        <v>18</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F35" s="1">
+        <v>7</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>1997</v>
+      </c>
+      <c r="B36" s="1">
+        <v>7</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F36" s="1">
+        <v>5</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>1999</v>
+      </c>
+      <c r="B37" s="1">
+        <v>12</v>
+      </c>
+      <c r="C37" s="1">
+        <v>20</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F37" s="1">
+        <v>5</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>2001</v>
+      </c>
+      <c r="B38" s="1">
+        <v>12</v>
+      </c>
+      <c r="C38" s="1">
+        <v>11</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>2008</v>
+      </c>
+      <c r="B39" s="1">
+        <v>8</v>
+      </c>
+      <c r="C39" s="1">
+        <v>8</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>2012</v>
+      </c>
+      <c r="B40" s="1">
+        <v>11</v>
+      </c>
+      <c r="C40" s="1">
+        <v>8</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F40" s="1">
+        <v>5</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7460648-6DE8-4DA1-B9C9-3FADADB7C7FF}">
+  <dimension ref="A1:I55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="15.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="27.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="47.375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>-3100</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>-2334</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>-1754</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>-1500</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>-776</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>-509</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F7" s="1">
+        <v>3</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>-336</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>-27</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>79</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>313</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>330</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>476</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>481</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>527</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>581</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>622</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>750</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>800</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>843</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>960</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>1054</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>1066</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>1096</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>1206</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>1215</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>1347</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>1453</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="1">
+        <v>5</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>1453</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>1492</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="F29" s="1">
+        <v>5</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>1498</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>1517</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>1519</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>1648</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>1688</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>1776</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="F35" s="1">
+        <v>5</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>1789</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="F36" s="1">
+        <v>5</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>1804</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>1815</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>1848</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>1861</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>1868</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>1871</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>1914</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="F43" s="1">
+        <v>7</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>1917</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>1918</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F45" s="1">
+        <v>3</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>1929</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>1939</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="F47" s="1">
+        <v>7</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>1941</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>1945</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>1945</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="F50" s="1">
+        <v>7</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>1947</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>1962</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>1989</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>1991</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="F54" s="1">
+        <v>7</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>2001</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>722</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32EFCE5F-2013-44CD-9DFE-6E90EE4F7B11}">
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
